--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="104">
   <si>
     <t>League</t>
   </si>
@@ -208,6 +208,9 @@
     <t>Israeli Premier League</t>
   </si>
   <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
@@ -265,12 +268,18 @@
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
+    <t>VMFD Zalgiris</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
     <t>Al Ahli</t>
   </si>
   <si>
@@ -298,19 +307,25 @@
     <t>Beitar Jerusalem</t>
   </si>
   <si>
+    <t>Fk Siauliai</t>
+  </si>
+  <si>
     <t>Dobrudzha</t>
   </si>
   <si>
     <t>Hapoel Beer Sheva</t>
   </si>
   <si>
+    <t>FK Suduva</t>
+  </si>
+  <si>
     <t>Al-Fateh (KSA)</t>
   </si>
   <si>
     <t>Paris St-G</t>
   </si>
   <si>
-    <t>2026-05-04 02:07:34</t>
+    <t>2026-05-04 04:18:46</t>
   </si>
 </sst>
 </file>
@@ -668,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -858,16 +873,16 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F2">
         <v>2.08</v>
@@ -876,13 +891,13 @@
         <v>2.32</v>
       </c>
       <c r="H2">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I2">
         <v>3.95</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
         <v>4.1</v>
@@ -900,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
         <v>1.81</v>
@@ -1032,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="BH2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1040,19 +1055,19 @@
         <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G3">
         <v>1.67</v>
@@ -1061,7 +1076,7 @@
         <v>5.8</v>
       </c>
       <c r="I3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
         <v>4.2</v>
@@ -1214,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="BH3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1222,19 +1237,19 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F4">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="G4">
         <v>1.76</v>
@@ -1396,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="BH4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1404,25 +1419,25 @@
         <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F5">
         <v>2.14</v>
       </c>
       <c r="G5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I5">
         <v>3.45</v>
@@ -1578,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="BH5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1586,28 +1601,28 @@
         <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F6">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G6">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="H6">
         <v>2.88</v>
       </c>
       <c r="I6">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="J6">
         <v>3.1</v>
@@ -1760,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="BH6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -1768,25 +1783,25 @@
         <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
         <v>1000</v>
@@ -1942,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="BH7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -1950,34 +1965,34 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F8">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="G8">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="H8">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="I8">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J8">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1992,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2124,42 +2139,42 @@
         <v>0</v>
       </c>
       <c r="BH8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:60">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F9">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2174,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2306,42 +2321,42 @@
         <v>0</v>
       </c>
       <c r="BH9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:60">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F10">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="G10">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="H10">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="I10">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="J10">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="K10">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2356,10 +2371,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q10">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2488,42 +2503,42 @@
         <v>0</v>
       </c>
       <c r="BH10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:60">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
         <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F11">
-        <v>1.34</v>
+        <v>4.2</v>
       </c>
       <c r="G11">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="H11">
-        <v>8.199999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>2.04</v>
       </c>
       <c r="J11">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2538,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="Q11">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2670,189 +2685,553 @@
         <v>0</v>
       </c>
       <c r="BH11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:60">
       <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12">
+        <v>1.04</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>1.04</v>
+      </c>
+      <c r="I12">
+        <v>1000</v>
+      </c>
+      <c r="J12">
+        <v>1.01</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.24</v>
+      </c>
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:60">
+      <c r="A13" t="s">
         <v>65</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13">
+        <v>1.31</v>
+      </c>
+      <c r="G13">
+        <v>1.4</v>
+      </c>
+      <c r="H13">
+        <v>9</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13">
+        <v>5.6</v>
+      </c>
+      <c r="K13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.72</v>
+      </c>
+      <c r="Q13">
+        <v>1.43</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:60">
+      <c r="A14" t="s">
         <v>66</v>
       </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F12">
-        <v>1.74</v>
-      </c>
-      <c r="G12">
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14">
         <v>1.75</v>
       </c>
-      <c r="H12">
+      <c r="G14">
+        <v>1.76</v>
+      </c>
+      <c r="H14">
         <v>4</v>
       </c>
-      <c r="I12">
+      <c r="I14">
         <v>4.1</v>
       </c>
-      <c r="J12">
+      <c r="J14">
         <v>5.5</v>
       </c>
-      <c r="K12">
+      <c r="K14">
         <v>5.6</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>1.01</v>
       </c>
-      <c r="N12">
+      <c r="N14">
         <v>13.5</v>
       </c>
-      <c r="O12">
+      <c r="O14">
         <v>1.07</v>
       </c>
-      <c r="P12">
-        <v>5.1</v>
-      </c>
-      <c r="Q12">
+      <c r="P14">
+        <v>5</v>
+      </c>
+      <c r="Q14">
         <v>1.24</v>
       </c>
-      <c r="R12">
-        <v>2.64</v>
-      </c>
-      <c r="S12">
+      <c r="R14">
+        <v>2.66</v>
+      </c>
+      <c r="S14">
         <v>1.57</v>
       </c>
-      <c r="T12">
+      <c r="T14">
         <v>1.3</v>
       </c>
-      <c r="U12">
+      <c r="U14">
         <v>4.1</v>
       </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
         <v>70</v>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <v>46</v>
       </c>
-      <c r="Z12">
+      <c r="Z14">
         <v>55</v>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <v>100</v>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <v>28</v>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <v>18</v>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <v>21</v>
       </c>
-      <c r="AE12">
+      <c r="AE14">
         <v>38</v>
       </c>
-      <c r="AF12">
+      <c r="AF14">
+        <v>23</v>
+      </c>
+      <c r="AG14">
+        <v>12.5</v>
+      </c>
+      <c r="AH14">
+        <v>15.5</v>
+      </c>
+      <c r="AI14">
+        <v>28</v>
+      </c>
+      <c r="AJ14">
+        <v>27</v>
+      </c>
+      <c r="AK14">
+        <v>16</v>
+      </c>
+      <c r="AL14">
+        <v>18</v>
+      </c>
+      <c r="AM14">
+        <v>32</v>
+      </c>
+      <c r="AN14">
+        <v>4.1</v>
+      </c>
+      <c r="AO14">
+        <v>13.5</v>
+      </c>
+      <c r="AP14">
+        <v>50</v>
+      </c>
+      <c r="AQ14">
+        <v>42</v>
+      </c>
+      <c r="AR14">
+        <v>48</v>
+      </c>
+      <c r="AS14">
+        <v>38</v>
+      </c>
+      <c r="AT14">
+        <v>26</v>
+      </c>
+      <c r="AU14">
+        <v>16</v>
+      </c>
+      <c r="AV14">
+        <v>19</v>
+      </c>
+      <c r="AW14">
+        <v>32</v>
+      </c>
+      <c r="AX14">
+        <v>21</v>
+      </c>
+      <c r="AY14">
+        <v>12</v>
+      </c>
+      <c r="AZ14">
+        <v>14.5</v>
+      </c>
+      <c r="BA14">
+        <v>26</v>
+      </c>
+      <c r="BB14">
         <v>24</v>
       </c>
-      <c r="AG12">
+      <c r="BC14">
+        <v>14.5</v>
+      </c>
+      <c r="BD14">
+        <v>16.5</v>
+      </c>
+      <c r="BE14">
+        <v>30</v>
+      </c>
+      <c r="BF14">
+        <v>3.9</v>
+      </c>
+      <c r="BG14">
         <v>12.5</v>
       </c>
-      <c r="AH12">
-        <v>16</v>
-      </c>
-      <c r="AI12">
-        <v>29</v>
-      </c>
-      <c r="AJ12">
-        <v>28</v>
-      </c>
-      <c r="AK12">
-        <v>16</v>
-      </c>
-      <c r="AL12">
-        <v>18</v>
-      </c>
-      <c r="AM12">
-        <v>32</v>
-      </c>
-      <c r="AN12">
-        <v>4.1</v>
-      </c>
-      <c r="AO12">
-        <v>13.5</v>
-      </c>
-      <c r="AP12">
-        <v>50</v>
-      </c>
-      <c r="AQ12">
-        <v>42</v>
-      </c>
-      <c r="AR12">
-        <v>50</v>
-      </c>
-      <c r="AS12">
-        <v>38</v>
-      </c>
-      <c r="AT12">
-        <v>27</v>
-      </c>
-      <c r="AU12">
-        <v>16.5</v>
-      </c>
-      <c r="AV12">
-        <v>19</v>
-      </c>
-      <c r="AW12">
-        <v>32</v>
-      </c>
-      <c r="AX12">
-        <v>21</v>
-      </c>
-      <c r="AY12">
-        <v>12</v>
-      </c>
-      <c r="AZ12">
-        <v>14.5</v>
-      </c>
-      <c r="BA12">
-        <v>26</v>
-      </c>
-      <c r="BB12">
-        <v>24</v>
-      </c>
-      <c r="BC12">
-        <v>14.5</v>
-      </c>
-      <c r="BD12">
-        <v>16.5</v>
-      </c>
-      <c r="BE12">
-        <v>30</v>
-      </c>
-      <c r="BF12">
-        <v>3.85</v>
-      </c>
-      <c r="BG12">
-        <v>12.5</v>
-      </c>
-      <c r="BH12" t="s">
-        <v>98</v>
+      <c r="BH14" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="106">
   <si>
     <t>League</t>
   </si>
@@ -202,15 +202,15 @@
     <t>Bulgarian A League</t>
   </si>
   <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
     <t>Romanian Liga II</t>
   </si>
   <si>
     <t>Israeli Premier League</t>
   </si>
   <si>
-    <t>Lithuanian A Lyga</t>
-  </si>
-  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
@@ -262,6 +262,9 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Hegelmann Litauen</t>
+  </si>
+  <si>
     <t>FC Hunedoara</t>
   </si>
   <si>
@@ -301,6 +304,9 @@
     <t>Septemvri</t>
   </si>
   <si>
+    <t>Panevezys</t>
+  </si>
+  <si>
     <t>FC Voluntari</t>
   </si>
   <si>
@@ -325,7 +331,7 @@
     <t>Paris St-G</t>
   </si>
   <si>
-    <t>2026-05-04 04:18:46</t>
+    <t>2026-05-04 06:32:04</t>
   </si>
 </sst>
 </file>
@@ -683,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BH15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -882,7 +888,7 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F2">
         <v>2.08</v>
@@ -918,7 +924,7 @@
         <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1047,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="BH2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1064,7 +1070,7 @@
         <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F3">
         <v>1.6</v>
@@ -1229,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="BH3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1246,19 +1252,19 @@
         <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F4">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G4">
         <v>1.76</v>
       </c>
       <c r="H4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J4">
         <v>4.2</v>
@@ -1279,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q4">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1411,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="BH4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1428,7 +1434,7 @@
         <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F5">
         <v>2.14</v>
@@ -1593,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="BH5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1610,19 +1616,19 @@
         <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="G6">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H6">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="I6">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J6">
         <v>3.1</v>
@@ -1775,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="BH6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -1792,7 +1798,7 @@
         <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F7">
         <v>1.04</v>
@@ -1957,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="BH7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -1968,31 +1974,31 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
         <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F8">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G8">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2007,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2139,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="BH8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -2156,25 +2162,25 @@
         <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2189,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2321,42 +2327,42 @@
         <v>0</v>
       </c>
       <c r="BH9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:60">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
         <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
         <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F10">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="G10">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="H10">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="I10">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K10">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2371,10 +2377,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2503,12 +2509,12 @@
         <v>0</v>
       </c>
       <c r="BH10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:60">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
@@ -2520,25 +2526,25 @@
         <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="G11">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="H11">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="I11">
-        <v>2.04</v>
+        <v>2.66</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="K11">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2553,10 +2559,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="Q11">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2685,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="BH11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:60">
@@ -2702,25 +2708,25 @@
         <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="J12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2735,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -2867,42 +2873,42 @@
         <v>0</v>
       </c>
       <c r="BH12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:60">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F13">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="G13">
-        <v>1.4</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="K13">
-        <v>8.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2917,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3049,189 +3055,371 @@
         <v>0</v>
       </c>
       <c r="BH13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:60">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="G14">
+        <v>1.39</v>
+      </c>
+      <c r="H14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I14">
+        <v>12.5</v>
+      </c>
+      <c r="J14">
+        <v>5.7</v>
+      </c>
+      <c r="K14">
+        <v>6.6</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>2.72</v>
+      </c>
+      <c r="Q14">
+        <v>1.43</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:60">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15">
         <v>1.76</v>
       </c>
-      <c r="H14">
+      <c r="G15">
+        <v>1.77</v>
+      </c>
+      <c r="H15">
+        <v>3.95</v>
+      </c>
+      <c r="I15">
         <v>4</v>
       </c>
-      <c r="I14">
+      <c r="J15">
+        <v>5.4</v>
+      </c>
+      <c r="K15">
+        <v>5.5</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>13.5</v>
+      </c>
+      <c r="O15">
+        <v>1.07</v>
+      </c>
+      <c r="P15">
+        <v>5</v>
+      </c>
+      <c r="Q15">
+        <v>1.24</v>
+      </c>
+      <c r="R15">
+        <v>2.66</v>
+      </c>
+      <c r="S15">
+        <v>1.57</v>
+      </c>
+      <c r="T15">
+        <v>1.3</v>
+      </c>
+      <c r="U15">
         <v>4.1</v>
       </c>
-      <c r="J14">
-        <v>5.5</v>
-      </c>
-      <c r="K14">
-        <v>5.6</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>1.01</v>
-      </c>
-      <c r="N14">
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>80</v>
+      </c>
+      <c r="Y15">
+        <v>46</v>
+      </c>
+      <c r="Z15">
+        <v>55</v>
+      </c>
+      <c r="AA15">
+        <v>95</v>
+      </c>
+      <c r="AB15">
+        <v>29</v>
+      </c>
+      <c r="AC15">
+        <v>18</v>
+      </c>
+      <c r="AD15">
+        <v>21</v>
+      </c>
+      <c r="AE15">
+        <v>38</v>
+      </c>
+      <c r="AF15">
+        <v>24</v>
+      </c>
+      <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>15.5</v>
+      </c>
+      <c r="AI15">
+        <v>29</v>
+      </c>
+      <c r="AJ15">
+        <v>27</v>
+      </c>
+      <c r="AK15">
+        <v>16</v>
+      </c>
+      <c r="AL15">
+        <v>18</v>
+      </c>
+      <c r="AM15">
+        <v>34</v>
+      </c>
+      <c r="AN15">
+        <v>4.1</v>
+      </c>
+      <c r="AO15">
         <v>13.5</v>
       </c>
-      <c r="O14">
-        <v>1.07</v>
-      </c>
-      <c r="P14">
-        <v>5</v>
-      </c>
-      <c r="Q14">
-        <v>1.24</v>
-      </c>
-      <c r="R14">
-        <v>2.66</v>
-      </c>
-      <c r="S14">
-        <v>1.57</v>
-      </c>
-      <c r="T14">
-        <v>1.3</v>
-      </c>
-      <c r="U14">
-        <v>4.1</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>70</v>
-      </c>
-      <c r="Y14">
-        <v>46</v>
-      </c>
-      <c r="Z14">
-        <v>55</v>
-      </c>
-      <c r="AA14">
-        <v>100</v>
-      </c>
-      <c r="AB14">
-        <v>28</v>
-      </c>
-      <c r="AC14">
-        <v>18</v>
-      </c>
-      <c r="AD14">
+      <c r="AP15">
+        <v>50</v>
+      </c>
+      <c r="AQ15">
+        <v>42</v>
+      </c>
+      <c r="AR15">
+        <v>48</v>
+      </c>
+      <c r="AS15">
+        <v>38</v>
+      </c>
+      <c r="AT15">
+        <v>26</v>
+      </c>
+      <c r="AU15">
+        <v>16</v>
+      </c>
+      <c r="AV15">
+        <v>19</v>
+      </c>
+      <c r="AW15">
+        <v>32</v>
+      </c>
+      <c r="AX15">
         <v>21</v>
       </c>
-      <c r="AE14">
-        <v>38</v>
-      </c>
-      <c r="AF14">
-        <v>23</v>
-      </c>
-      <c r="AG14">
+      <c r="AY15">
+        <v>12</v>
+      </c>
+      <c r="AZ15">
+        <v>14.5</v>
+      </c>
+      <c r="BA15">
+        <v>26</v>
+      </c>
+      <c r="BB15">
+        <v>24</v>
+      </c>
+      <c r="BC15">
+        <v>14.5</v>
+      </c>
+      <c r="BD15">
+        <v>16.5</v>
+      </c>
+      <c r="BE15">
+        <v>30</v>
+      </c>
+      <c r="BF15">
+        <v>3.9</v>
+      </c>
+      <c r="BG15">
         <v>12.5</v>
       </c>
-      <c r="AH14">
-        <v>15.5</v>
-      </c>
-      <c r="AI14">
-        <v>28</v>
-      </c>
-      <c r="AJ14">
-        <v>27</v>
-      </c>
-      <c r="AK14">
-        <v>16</v>
-      </c>
-      <c r="AL14">
-        <v>18</v>
-      </c>
-      <c r="AM14">
-        <v>32</v>
-      </c>
-      <c r="AN14">
-        <v>4.1</v>
-      </c>
-      <c r="AO14">
-        <v>13.5</v>
-      </c>
-      <c r="AP14">
-        <v>50</v>
-      </c>
-      <c r="AQ14">
-        <v>42</v>
-      </c>
-      <c r="AR14">
-        <v>48</v>
-      </c>
-      <c r="AS14">
-        <v>38</v>
-      </c>
-      <c r="AT14">
-        <v>26</v>
-      </c>
-      <c r="AU14">
-        <v>16</v>
-      </c>
-      <c r="AV14">
-        <v>19</v>
-      </c>
-      <c r="AW14">
-        <v>32</v>
-      </c>
-      <c r="AX14">
-        <v>21</v>
-      </c>
-      <c r="AY14">
-        <v>12</v>
-      </c>
-      <c r="AZ14">
-        <v>14.5</v>
-      </c>
-      <c r="BA14">
-        <v>26</v>
-      </c>
-      <c r="BB14">
-        <v>24</v>
-      </c>
-      <c r="BC14">
-        <v>14.5</v>
-      </c>
-      <c r="BD14">
-        <v>16.5</v>
-      </c>
-      <c r="BE14">
-        <v>30</v>
-      </c>
-      <c r="BF14">
-        <v>3.9</v>
-      </c>
-      <c r="BG14">
-        <v>12.5</v>
-      </c>
-      <c r="BH14" t="s">
-        <v>103</v>
+      <c r="BH15" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -331,7 +331,7 @@
     <t>Paris St-G</t>
   </si>
   <si>
-    <t>2026-05-04 06:32:04</t>
+    <t>2026-05-04 08:43:55</t>
   </si>
 </sst>
 </file>
@@ -891,7 +891,7 @@
         <v>91</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G2">
         <v>2.32</v>
@@ -900,157 +900,157 @@
         <v>3.35</v>
       </c>
       <c r="I2">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2">
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P2">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="s">
         <v>105</v>
@@ -1073,13 +1073,13 @@
         <v>92</v>
       </c>
       <c r="F3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I3">
         <v>6.4</v>
@@ -1088,7 +1088,7 @@
         <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>93</v>
       </c>
       <c r="F4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G4">
         <v>1.76</v>
@@ -1619,10 +1619,10 @@
         <v>95</v>
       </c>
       <c r="F6">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G6">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="H6">
         <v>2.78</v>
@@ -1986,16 +1986,16 @@
         <v>1.04</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>1.04</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2174,10 +2174,10 @@
         <v>2.2</v>
       </c>
       <c r="I9">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K9">
         <v>4.2</v>
@@ -2532,7 +2532,7 @@
         <v>3.2</v>
       </c>
       <c r="G11">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="H11">
         <v>2.36</v>
@@ -2544,7 +2544,7 @@
         <v>3.05</v>
       </c>
       <c r="K11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2562,7 +2562,7 @@
         <v>1.67</v>
       </c>
       <c r="Q11">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2714,10 +2714,10 @@
         <v>4.2</v>
       </c>
       <c r="G12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H12">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I12">
         <v>1.88</v>
@@ -2744,7 +2744,7 @@
         <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3075,16 +3075,16 @@
         <v>103</v>
       </c>
       <c r="F14">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G14">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="H14">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I14">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J14">
         <v>5.7</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="Q14">
         <v>1.43</v>
@@ -3257,22 +3257,22 @@
         <v>104</v>
       </c>
       <c r="F15">
+        <v>1.75</v>
+      </c>
+      <c r="G15">
         <v>1.76</v>
       </c>
-      <c r="G15">
-        <v>1.77</v>
-      </c>
       <c r="H15">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3314,7 +3314,7 @@
         <v>80</v>
       </c>
       <c r="Y15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z15">
         <v>55</v>
@@ -3329,7 +3329,7 @@
         <v>18</v>
       </c>
       <c r="AD15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE15">
         <v>38</v>
@@ -3341,7 +3341,7 @@
         <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI15">
         <v>29</v>
@@ -3365,7 +3365,7 @@
         <v>13.5</v>
       </c>
       <c r="AP15">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AQ15">
         <v>42</v>
@@ -3377,7 +3377,7 @@
         <v>38</v>
       </c>
       <c r="AT15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU15">
         <v>16</v>
@@ -3395,7 +3395,7 @@
         <v>12</v>
       </c>
       <c r="AZ15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA15">
         <v>26</v>
@@ -3410,13 +3410,13 @@
         <v>16.5</v>
       </c>
       <c r="BE15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF15">
         <v>3.9</v>
       </c>
       <c r="BG15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH15" t="s">
         <v>105</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -775,7 +775,7 @@
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -990,7 +990,7 @@
         <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T3" t="n">
         <v>1.72</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
         <v>1.76</v>
@@ -1154,7 +1154,7 @@
         <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
         <v>4.2</v>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
@@ -1184,7 +1184,7 @@
         <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="T4" t="n">
         <v>1.5</v>
@@ -1193,122 +1193,122 @@
         <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
         <v>2.3</v>
       </c>
       <c r="X4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE4" t="n">
         <v>55</v>
       </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
         <v>18</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AI4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AD4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2.48</v>
-      </c>
       <c r="BC4" t="n">
-        <v>2.46</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.54</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.66</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.74</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1363,28 +1363,28 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V5" t="n">
         <v>1.41</v>
@@ -1423,19 +1423,19 @@
         <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ5" t="n">
         <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM5" t="n">
         <v>60</v>
@@ -1444,7 +1444,7 @@
         <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP5" t="n">
         <v>21</v>
@@ -1456,7 +1456,7 @@
         <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>13.5</v>
@@ -1468,7 +1468,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1480,19 +1480,19 @@
         <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
         <v>8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1536,167 +1536,167 @@
         <v>2.52</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
         <v>2.88</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
         <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
         <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR6" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>14</v>
-      </c>
       <c r="AS6" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.97</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.87</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.08</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.28</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.28</v>
+        <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.28</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.38</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J8" t="n">
         <v>1.02</v>
@@ -1945,7 +1945,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>5.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.48</v>
+        <v>5.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
         <v>2.48</v>
@@ -2151,134 +2151,134 @@
         <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
         <v>2.66</v>
       </c>
       <c r="X9" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>17</v>
       </c>
-      <c r="AC9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX9" t="n">
+      <c r="BA9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE9" t="n">
         <v>7</v>
       </c>
-      <c r="AY9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H10" t="n">
         <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
         <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,34 +2333,34 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
         <v>1.97</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
@@ -2402,10 +2402,10 @@
         <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
@@ -2414,31 +2414,31 @@
         <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP10" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
         <v>8.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV10" t="n">
         <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
         <v>15</v>
@@ -2459,20 +2459,20 @@
         <v>12</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
         <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>48</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -2596,10 +2596,10 @@
         <v>48</v>
       </c>
       <c r="AK11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM11" t="n">
         <v>85</v>
@@ -2620,7 +2620,7 @@
         <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
@@ -2644,29 +2644,29 @@
         <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
         <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
         <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
         <v>2.26</v>
@@ -2712,19 +2712,19 @@
         <v>2.92</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
@@ -2733,19 +2733,19 @@
         <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
         <v>1.79</v>
@@ -2754,43 +2754,43 @@
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -2808,43 +2808,43 @@
         <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
         <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
         <v>1.03</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -2909,16 +2909,16 @@
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
         <v>2.1</v>
@@ -2927,134 +2927,134 @@
         <v>1.71</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3097,158 +3097,158 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3285,164 +3285,164 @@
         <v>3.7</v>
       </c>
       <c r="H15" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P15" t="n">
         <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>4.2</v>
       </c>
       <c r="G16" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
         <v>1.74</v>
@@ -3491,16 +3491,16 @@
         <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P16" t="n">
         <v>2.5</v>
@@ -3509,134 +3509,134 @@
         <v>1.47</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3679,158 +3679,158 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
         <v>950</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>10.5</v>
       </c>
       <c r="I18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
         <v>6.2</v>
@@ -3879,16 +3879,16 @@
         <v>7.4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P18" t="n">
         <v>2.96</v>
@@ -3897,134 +3897,134 @@
         <v>1.38</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
         <v>5.6</v>
@@ -4091,7 +4091,7 @@
         <v>1.24</v>
       </c>
       <c r="R19" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="S19" t="n">
         <v>1.58</v>
@@ -4133,7 +4133,7 @@
         <v>38</v>
       </c>
       <c r="AF19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
         <v>12.5</v>
@@ -4160,7 +4160,7 @@
         <v>4.1</v>
       </c>
       <c r="AO19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP19" t="n">
         <v>55</v>
@@ -4172,13 +4172,13 @@
         <v>48</v>
       </c>
       <c r="AS19" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AT19" t="n">
         <v>27</v>
       </c>
       <c r="AU19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AV19" t="n">
         <v>19.5</v>
@@ -4193,10 +4193,10 @@
         <v>12</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB19" t="n">
         <v>24</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 13:30:59</t>
+          <t>2026-05-04 15:42:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
         <v>3.8</v>
@@ -775,7 +775,7 @@
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -787,7 +787,7 @@
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
         <v>1.81</v>
@@ -808,7 +808,7 @@
         <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
@@ -832,7 +832,7 @@
         <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
         <v>15.5</v>
@@ -847,7 +847,7 @@
         <v>48</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK2" t="n">
         <v>24</v>
@@ -862,7 +862,7 @@
         <v>15.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP2" t="n">
         <v>14.5</v>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
         <v>7.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>1.59</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I3" t="n">
         <v>6.4</v>
@@ -984,7 +984,7 @@
         <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
@@ -993,7 +993,7 @@
         <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
         <v>2.16</v>
@@ -1002,7 +1002,7 @@
         <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
         <v>25</v>
@@ -1056,7 +1056,7 @@
         <v>7.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="n">
         <v>6.4</v>
@@ -1068,7 +1068,7 @@
         <v>36</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
         <v>8.4</v>
@@ -1077,7 +1077,7 @@
         <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="AW3" t="n">
         <v>7.8</v>
@@ -1101,10 +1101,10 @@
         <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
         <v>6.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
         <v>1.76</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
         <v>4.2</v>
@@ -1166,31 +1166,31 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
         <v>1.22</v>
@@ -1289,7 +1289,7 @@
         <v>7.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>2.16</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>3.4</v>
@@ -1369,7 +1369,7 @@
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q5" t="n">
         <v>1.5</v>
@@ -1390,85 +1390,85 @@
         <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF5" t="n">
         <v>19.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
         <v>13.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1480,29 +1480,29 @@
         <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC5" t="n">
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
         <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.52</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
         <v>2.88</v>
@@ -1563,7 +1563,7 @@
         <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
         <v>1.98</v>
@@ -1584,7 +1584,7 @@
         <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
@@ -1614,43 +1614,43 @@
         <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1662,7 +1662,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -1671,32 +1671,32 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
         <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>1.23</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
         <v>5.3</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G10" t="n">
         <v>1.72</v>
@@ -2351,13 +2351,13 @@
         <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
         <v>2.38</v>
@@ -2393,7 +2393,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>80</v>
@@ -2402,7 +2402,7 @@
         <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>29</v>
@@ -2411,22 +2411,22 @@
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP10" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
         <v>8.4</v>
@@ -2438,7 +2438,7 @@
         <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX10" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
         <v>15</v>
@@ -2462,17 +2462,17 @@
         <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2557,10 +2557,10 @@
         <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
         <v>20</v>
@@ -2569,13 +2569,13 @@
         <v>40</v>
       </c>
       <c r="AB11" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>32</v>
@@ -2584,10 +2584,10 @@
         <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
         <v>38</v>
@@ -2647,7 +2647,7 @@
         <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BC11" t="n">
         <v>1.03</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
         <v>3.65</v>
@@ -2745,7 +2745,7 @@
         <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
         <v>1.79</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -2897,13 +2897,13 @@
         <v>3.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I13" t="n">
         <v>2.48</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
         <v>4.2</v>
@@ -2924,13 +2924,13 @@
         <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="T13" t="n">
         <v>1.62</v>
@@ -2945,116 +2945,116 @@
         <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA13" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AB13" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF13" t="n">
         <v>20</v>
       </c>
-      <c r="AH13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3109,13 +3109,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.15</v>
       </c>
       <c r="P14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q14" t="n">
         <v>1.15</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>3.15</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H15" t="n">
         <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
@@ -3312,7 +3312,7 @@
         <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
@@ -3387,10 +3387,10 @@
         <v>36</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR15" t="n">
         <v>11</v>
@@ -3399,13 +3399,13 @@
         <v>3.85</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW15" t="n">
         <v>3.8</v>
@@ -3414,13 +3414,13 @@
         <v>16.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>34</v>
+        <v>3.95</v>
       </c>
       <c r="BB15" t="n">
         <v>4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="R16" t="n">
         <v>1.6</v>
@@ -3515,10 +3515,10 @@
         <v>2.38</v>
       </c>
       <c r="T16" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
         <v>2.12</v>
@@ -3536,7 +3536,7 @@
         <v>16.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB16" t="n">
         <v>28</v>
@@ -3584,7 +3584,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR16" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
         <v>16.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>7.8</v>
@@ -3605,7 +3605,7 @@
         <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
         <v>13.5</v>
@@ -3614,29 +3614,29 @@
         <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
         <v>5.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3691,13 +3691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q17" t="n">
         <v>1.29</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>1.28</v>
       </c>
       <c r="G18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H18" t="n">
         <v>10.5</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="J18" t="n">
         <v>6.2</v>
@@ -3879,7 +3879,7 @@
         <v>7.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.02</v>
@@ -3888,7 +3888,7 @@
         <v>2.96</v>
       </c>
       <c r="O18" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P18" t="n">
         <v>2.96</v>
@@ -3897,22 +3897,22 @@
         <v>1.38</v>
       </c>
       <c r="R18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S18" t="n">
         <v>1.39</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
         <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3969,52 +3969,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>5.7</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
@@ -4088,97 +4088,97 @@
         <v>5.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S19" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="U19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
         <v>80</v>
       </c>
       <c r="Y19" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA19" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC19" t="n">
         <v>18</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ19" t="n">
         <v>27</v>
       </c>
       <c r="AK19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AN19" t="n">
         <v>4.1</v>
       </c>
       <c r="AO19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AQ19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AR19" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS19" t="n">
         <v>50</v>
       </c>
       <c r="AT19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AU19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV19" t="n">
         <v>19.5</v>
@@ -4193,32 +4193,32 @@
         <v>12</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
         <v>25</v>
       </c>
       <c r="BB19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC19" t="n">
         <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BE19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 15:42:18</t>
+          <t>2026-05-04 17:51:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -901,13 +901,13 @@
         <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
         <v>8.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
         <v>1.66</v>
@@ -1059,40 +1059,40 @@
         <v>80</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR3" t="n">
         <v>36</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
         <v>8.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY3" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
@@ -1101,20 +1101,20 @@
         <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
         <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
         <v>1.76</v>
@@ -1190,7 +1190,7 @@
         <v>1.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
         <v>1.22</v>
@@ -1253,13 +1253,13 @@
         <v>44</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
         <v>8.199999999999999</v>
@@ -1289,13 +1289,13 @@
         <v>7.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="BE4" t="n">
         <v>7.8</v>
@@ -1304,11 +1304,11 @@
         <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1447,16 +1447,16 @@
         <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
         <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AT5" t="n">
         <v>13.5</v>
@@ -1468,7 +1468,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1480,16 +1480,16 @@
         <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BE5" t="n">
         <v>7.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1551,16 +1551,16 @@
         <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
         <v>1.86</v>
@@ -1569,16 +1569,16 @@
         <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
         <v>1.45</v>
@@ -1608,7 +1608,7 @@
         <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
         <v>18</v>
@@ -1662,7 +1662,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -1677,26 +1677,26 @@
         <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
         <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1769,10 +1769,10 @@
         <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1954,19 +1954,19 @@
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R8" t="n">
         <v>1.15</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G10" t="n">
         <v>1.72</v>
@@ -2357,7 +2357,7 @@
         <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
         <v>2.38</v>
@@ -2420,7 +2420,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR10" t="n">
         <v>7.8</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
         <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V11" t="n">
         <v>1.54</v>
@@ -2620,7 +2620,7 @@
         <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
         <v>9.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX11" t="n">
         <v>15</v>
@@ -2644,29 +2644,29 @@
         <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
         <v>30</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG11" t="n">
         <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
         <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
         <v>2.9</v>
@@ -2730,7 +2730,7 @@
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="R12" t="n">
         <v>1.23</v>
@@ -2739,13 +2739,13 @@
         <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U12" t="n">
         <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
         <v>1.79</v>
@@ -2805,7 +2805,7 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.4</v>
@@ -2814,7 +2814,7 @@
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="AT12" t="n">
         <v>5.3</v>
@@ -2826,7 +2826,7 @@
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
@@ -2838,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BB12" t="n">
         <v>17.5</v>
@@ -2847,20 +2847,20 @@
         <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -2897,13 +2897,13 @@
         <v>3.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I13" t="n">
         <v>2.48</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>4.2</v>
@@ -2924,7 +2924,7 @@
         <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
@@ -2942,7 +2942,7 @@
         <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2999,62 +2999,62 @@
         <v>17.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY13" t="n">
         <v>11.5</v>
       </c>
-      <c r="AU13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
         <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3109,13 +3109,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O14" t="n">
         <v>1.15</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Q14" t="n">
         <v>1.15</v>
@@ -3124,13 +3124,13 @@
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>3.15</v>
       </c>
       <c r="G15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H15" t="n">
         <v>2.36</v>
@@ -3318,10 +3318,10 @@
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
         <v>1.9</v>
@@ -3348,7 +3348,7 @@
         <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
         <v>14.5</v>
@@ -3363,7 +3363,7 @@
         <v>18</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
         <v>60</v>
@@ -3387,62 +3387,62 @@
         <v>36</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AT15" t="n">
         <v>9.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AX15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
       <c r="BA15" t="n">
-        <v>3.95</v>
+        <v>34</v>
       </c>
       <c r="BB15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>4.2</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="H16" t="n">
         <v>1.74</v>
@@ -3581,62 +3581,62 @@
         <v>9.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>18.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW16" t="n">
         <v>14.5</v>
       </c>
-      <c r="AT16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>12</v>
-      </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H17" t="n">
         <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K17" t="n">
         <v>950</v>
@@ -3691,13 +3691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.29</v>
@@ -3709,10 +3709,10 @@
         <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
         <v>2.96</v>
       </c>
       <c r="O18" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P18" t="n">
         <v>2.96</v>
@@ -3900,13 +3900,13 @@
         <v>1.69</v>
       </c>
       <c r="S18" t="n">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
         <v>1.08</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
@@ -4079,19 +4079,19 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="O19" t="n">
         <v>1.07</v>
       </c>
       <c r="P19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R19" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="S19" t="n">
         <v>1.56</v>
@@ -4124,16 +4124,16 @@
         <v>30</v>
       </c>
       <c r="AC19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
         <v>36</v>
       </c>
       <c r="AF19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
@@ -4142,7 +4142,7 @@
         <v>15.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ19" t="n">
         <v>27</v>
@@ -4151,7 +4151,7 @@
         <v>15</v>
       </c>
       <c r="AL19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AM19" t="n">
         <v>34</v>
@@ -4160,52 +4160,52 @@
         <v>4.1</v>
       </c>
       <c r="AO19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AQ19" t="n">
         <v>44</v>
       </c>
       <c r="AR19" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS19" t="n">
         <v>50</v>
       </c>
       <c r="AT19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU19" t="n">
         <v>17</v>
       </c>
       <c r="AV19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>32</v>
       </c>
       <c r="AX19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB19" t="n">
         <v>25</v>
       </c>
       <c r="BC19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BE19" t="n">
         <v>29</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
         <v>2.28</v>
@@ -772,7 +772,7 @@
         <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
         <v>1.66</v>
@@ -966,7 +966,7 @@
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.33</v>
@@ -984,7 +984,7 @@
         <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
@@ -993,10 +993,10 @@
         <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
         <v>1.18</v>
@@ -1005,10 +1005,10 @@
         <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
         <v>60</v>
@@ -1023,7 +1023,7 @@
         <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
         <v>75</v>
@@ -1035,7 +1035,7 @@
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>70</v>
@@ -1062,13 +1062,13 @@
         <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
         <v>36</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>8.4</v>
@@ -1077,7 +1077,7 @@
         <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
         <v>8.4</v>
@@ -1104,7 +1104,7 @@
         <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
         <v>6.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>1.76</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
         <v>5.7</v>
@@ -1160,7 +1160,7 @@
         <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,13 +1169,13 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I5" t="n">
         <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
         <v>4.5</v>
@@ -1369,28 +1369,28 @@
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
         <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V5" t="n">
         <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1429,7 +1429,7 @@
         <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="n">
         <v>21</v>
@@ -1441,19 +1441,19 @@
         <v>55</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO5" t="n">
         <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS5" t="n">
         <v>42</v>
@@ -1468,7 +1468,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1480,19 +1480,19 @@
         <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE5" t="n">
         <v>8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
         <v>8.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2169,10 +2169,10 @@
         <v>2.66</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>70</v>
@@ -2187,7 +2187,7 @@
         <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
         <v>95</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G10" t="n">
         <v>1.72</v>
@@ -2327,7 +2327,7 @@
         <v>4.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
@@ -2357,7 +2357,7 @@
         <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
         <v>2.38</v>
@@ -2366,7 +2366,7 @@
         <v>21</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
         <v>55</v>
@@ -2393,7 +2393,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>80</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
         <v>9.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
         <v>15</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="K12" t="n">
         <v>3.65</v>
@@ -2727,10 +2727,10 @@
         <v>1.44</v>
       </c>
       <c r="P12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R12" t="n">
         <v>1.23</v>
@@ -2739,16 +2739,16 @@
         <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
         <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2781,7 +2781,7 @@
         <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2793,19 +2793,19 @@
         <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.4</v>
@@ -2814,7 +2814,7 @@
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="AT12" t="n">
         <v>5.3</v>
@@ -2826,7 +2826,7 @@
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="AX12" t="n">
         <v>8.199999999999999</v>
@@ -2838,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="BB12" t="n">
         <v>17.5</v>
@@ -2847,20 +2847,20 @@
         <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.22</v>
+        <v>15.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I13" t="n">
         <v>2.48</v>
@@ -2924,7 +2924,7 @@
         <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
@@ -2936,13 +2936,13 @@
         <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
         <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2999,7 +2999,7 @@
         <v>17.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
@@ -3050,11 +3050,11 @@
         <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.15</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -3312,13 +3312,13 @@
         <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
         <v>1.89</v>
@@ -3366,16 +3366,16 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AK15" t="n">
         <v>60</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
         <v>160</v>
@@ -3396,7 +3396,7 @@
         <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT15" t="n">
         <v>9.4</v>
@@ -3408,7 +3408,7 @@
         <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX15" t="n">
         <v>19</v>
@@ -3420,29 +3420,29 @@
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>34</v>
+        <v>4.5</v>
       </c>
       <c r="BB15" t="n">
         <v>4.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
         <v>4.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
         <v>2.12</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
         <v>32</v>
@@ -3581,10 +3581,10 @@
         <v>9.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.1</v>
+        <v>18.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AR16" t="n">
         <v>11.5</v>
@@ -3599,7 +3599,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AW16" t="n">
         <v>14.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -3775,52 +3775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
         <v>1.69</v>
       </c>
       <c r="S18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
         <v>5.6</v>
@@ -4085,16 +4085,16 @@
         <v>1.07</v>
       </c>
       <c r="P19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R19" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="S19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T19" t="n">
         <v>1.3</v>
@@ -4106,7 +4106,7 @@
         <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X19" t="n">
         <v>80</v>
@@ -4130,7 +4130,7 @@
         <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
         <v>24</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI19" t="n">
         <v>27</v>
@@ -4157,19 +4157,19 @@
         <v>34</v>
       </c>
       <c r="AN19" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AO19" t="n">
         <v>13.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AQ19" t="n">
         <v>44</v>
       </c>
       <c r="AR19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS19" t="n">
         <v>50</v>
@@ -4202,7 +4202,7 @@
         <v>25</v>
       </c>
       <c r="BC19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
         <v>16.5</v>
@@ -4211,14 +4211,14 @@
         <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG19" t="n">
         <v>12</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 20:01:00</t>
+          <t>2026-05-04 22:09:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -784,31 +784,31 @@
         <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X2" t="n">
         <v>17.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H3" t="n">
         <v>5.7</v>
@@ -1002,7 +1002,7 @@
         <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X3" t="n">
         <v>24</v>
@@ -1080,7 +1080,7 @@
         <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX3" t="n">
         <v>9.4</v>
@@ -1089,10 +1089,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G4" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
@@ -1187,16 +1187,16 @@
         <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
         <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
         <v>30</v>
@@ -1289,7 +1289,7 @@
         <v>7.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G5" t="n">
         <v>2.32</v>
@@ -1348,10 +1348,10 @@
         <v>3.05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>4.5</v>
@@ -1363,19 +1363,19 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
         <v>2.18</v>
@@ -1384,10 +1384,10 @@
         <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="V5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
         <v>1.75</v>
@@ -1447,16 +1447,16 @@
         <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
         <v>13.5</v>
@@ -1480,7 +1480,7 @@
         <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
         <v>7.8</v>
@@ -1489,7 +1489,7 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
         <v>8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1560,7 +1560,7 @@
         <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
         <v>1.86</v>
@@ -1632,7 +1632,7 @@
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
         <v>26</v>
@@ -1650,7 +1650,7 @@
         <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1662,7 +1662,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -1692,11 +1692,11 @@
         <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>4.6</v>
@@ -2271,14 +2271,14 @@
         <v>7</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
         <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
         <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
@@ -2327,7 +2327,7 @@
         <v>4.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
@@ -2357,7 +2357,7 @@
         <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
         <v>2.38</v>
@@ -2420,7 +2420,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
         <v>7.8</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aris FC Limassol</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.98</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS11" t="n">
         <v>2.5</v>
       </c>
-      <c r="I11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>2.46</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Aris FC Limassol</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Apollon Limassol</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>2.84</v>
       </c>
       <c r="J12" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.9</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="W12" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT12" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG12" t="n">
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX12" t="n">
         <v>15</v>
       </c>
-      <c r="AH12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB12" t="n">
         <v>30</v>
       </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BC12" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.46</v>
+        <v>6.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
@@ -2942,7 +2942,7 @@
         <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
@@ -3327,7 +3327,7 @@
         <v>1.9</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W15" t="n">
         <v>1.37</v>
@@ -3366,16 +3366,16 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="n">
         <v>60</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM15" t="n">
         <v>160</v>
@@ -3396,7 +3396,7 @@
         <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.4</v>
+        <v>26</v>
       </c>
       <c r="AT15" t="n">
         <v>9.4</v>
@@ -3408,10 +3408,10 @@
         <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AY15" t="n">
         <v>12.5</v>
@@ -3420,13 +3420,13 @@
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB15" t="n">
         <v>4.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
         <v>4.5</v>
@@ -3438,11 +3438,11 @@
         <v>4.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>4.2</v>
       </c>
       <c r="G16" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
         <v>1.74</v>
@@ -3506,7 +3506,7 @@
         <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="R16" t="n">
         <v>1.6</v>
@@ -3524,7 +3524,7 @@
         <v>2.12</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X16" t="n">
         <v>32</v>
@@ -3581,10 +3581,10 @@
         <v>9.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>18.5</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
         <v>11.5</v>
@@ -3599,13 +3599,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16" t="n">
         <v>14.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY16" t="n">
         <v>16</v>
@@ -3614,29 +3614,29 @@
         <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>19.5</v>
+        <v>4.1</v>
       </c>
       <c r="BB16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.2</v>
       </c>
       <c r="BD16" t="n">
         <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
         <v>4.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
         <v>4.1</v>
       </c>
-      <c r="I19" t="n">
-        <v>4.2</v>
-      </c>
       <c r="J19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.15</v>
@@ -4091,7 +4091,7 @@
         <v>1.23</v>
       </c>
       <c r="R19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S19" t="n">
         <v>1.57</v>
@@ -4106,13 +4106,13 @@
         <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X19" t="n">
         <v>80</v>
       </c>
       <c r="Y19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Z19" t="n">
         <v>60</v>
@@ -4139,7 +4139,7 @@
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI19" t="n">
         <v>27</v>
@@ -4157,7 +4157,7 @@
         <v>34</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AO19" t="n">
         <v>13.5</v>
@@ -4166,7 +4166,7 @@
         <v>60</v>
       </c>
       <c r="AQ19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AR19" t="n">
         <v>48</v>
@@ -4175,7 +4175,7 @@
         <v>50</v>
       </c>
       <c r="AT19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU19" t="n">
         <v>17</v>
@@ -4214,11 +4214,399 @@
         <v>3.85</v>
       </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-04 22:09:33</t>
+          <t>2026-05-05 00:18:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:18:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23:15:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CD Olimpia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CD Marathon</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>950</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:18:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>3.9</v>
@@ -778,7 +778,7 @@
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
         <v>4.1</v>
@@ -826,7 +826,7 @@
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>15.5</v>
@@ -874,53 +874,53 @@
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
         <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
         <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
@@ -993,7 +993,7 @@
         <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="n">
         <v>2.12</v>
@@ -1059,7 +1059,7 @@
         <v>80</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
         <v>20</v>
@@ -1080,7 +1080,7 @@
         <v>19</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX3" t="n">
         <v>9.4</v>
@@ -1089,10 +1089,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
         <v>12</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
         <v>4.8</v>
@@ -1169,43 +1169,43 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
         <v>1.61</v>
       </c>
       <c r="U4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W4" t="n">
         <v>2.38</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.2</v>
-      </c>
       <c r="X4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y4" t="n">
         <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AA4" t="n">
         <v>120</v>
@@ -1223,92 +1223,92 @@
         <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
         <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR4" t="n">
         <v>28</v>
       </c>
-      <c r="AM4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AS4" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BB4" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>2.22</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -1372,10 +1372,10 @@
         <v>2.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S5" t="n">
         <v>2.18</v>
@@ -1390,7 +1390,7 @@
         <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1408,10 +1408,10 @@
         <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1420,7 +1420,7 @@
         <v>19.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
         <v>15</v>
@@ -1447,43 +1447,43 @@
         <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
         <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
         <v>17.5</v>
@@ -1492,17 +1492,17 @@
         <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
         <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>2.88</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
@@ -1563,19 +1563,19 @@
         <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
         <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
         <v>2.12</v>
@@ -1596,7 +1596,7 @@
         <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
         <v>11</v>
@@ -1620,7 +1620,7 @@
         <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>40</v>
@@ -1638,7 +1638,7 @@
         <v>26</v>
       </c>
       <c r="AO6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
@@ -1674,29 +1674,29 @@
         <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF6" t="n">
         <v>18</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
         <v>1.54</v>
@@ -2157,10 +2157,10 @@
         <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
         <v>1.14</v>
@@ -2217,22 +2217,22 @@
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
         <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2241,10 +2241,10 @@
         <v>10</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX9" t="n">
         <v>9.6</v>
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
         <v>12.5</v>
@@ -2265,20 +2265,20 @@
         <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
         <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K10" t="n">
         <v>4.9</v>
@@ -2330,40 +2330,40 @@
         <v>1.27</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
         <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y10" t="n">
         <v>950</v>
@@ -2375,13 +2375,13 @@
         <v>150</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
         <v>70</v>
@@ -2420,25 +2420,25 @@
         <v>18.5</v>
       </c>
       <c r="AQ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS10" t="n">
         <v>7</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
         <v>8.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV10" t="n">
         <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
         <v>9.6</v>
@@ -2450,10 +2450,10 @@
         <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC10" t="n">
         <v>12</v>
@@ -2462,17 +2462,17 @@
         <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2503,28 +2503,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
         <v>2.9</v>
@@ -2533,10 +2533,10 @@
         <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
         <v>1.23</v>
@@ -2545,16 +2545,16 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2572,7 +2572,7 @@
         <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>24</v>
@@ -2611,7 +2611,7 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.4</v>
@@ -2635,10 +2635,10 @@
         <v>2.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ11" t="n">
         <v>14</v>
@@ -2647,7 +2647,7 @@
         <v>2.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>17.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.62</v>
       </c>
       <c r="G12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>2.5</v>
@@ -2709,7 +2709,7 @@
         <v>2.84</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
@@ -2739,7 +2739,7 @@
         <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
         <v>2.28</v>
@@ -2826,7 +2826,7 @@
         <v>9.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX12" t="n">
         <v>15</v>
@@ -2838,7 +2838,7 @@
         <v>12</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB12" t="n">
         <v>30</v>
@@ -2847,7 +2847,7 @@
         <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE12" t="n">
         <v>7.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>3.75</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I13" t="n">
         <v>2.48</v>
@@ -2909,7 +2909,7 @@
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -2921,10 +2921,10 @@
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
@@ -2936,13 +2936,13 @@
         <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
         <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3026,7 +3026,7 @@
         <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
         <v>13.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>3.15</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H15" t="n">
         <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
@@ -3297,43 +3297,43 @@
         <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O15" t="n">
         <v>1.41</v>
       </c>
       <c r="P15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
         <v>1.9</v>
       </c>
       <c r="V15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
         <v>1.37</v>
       </c>
       <c r="X15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
         <v>11</v>
@@ -3342,22 +3342,22 @@
         <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB15" t="n">
         <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
         <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>18</v>
@@ -3366,7 +3366,7 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
         <v>80</v>
@@ -3381,19 +3381,19 @@
         <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
         <v>26</v>
@@ -3408,10 +3408,10 @@
         <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AY15" t="n">
         <v>12.5</v>
@@ -3420,29 +3420,29 @@
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB15" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BC15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE15" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>4.2</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="H16" t="n">
         <v>1.74</v>
       </c>
       <c r="I16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
@@ -3491,55 +3491,55 @@
         <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W16" t="n">
         <v>1.26</v>
       </c>
       <c r="X16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
         <v>24</v>
       </c>
       <c r="AB16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC16" t="n">
         <v>13</v>
@@ -3551,7 +3551,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG16" t="n">
         <v>23</v>
@@ -3572,46 +3572,46 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO16" t="n">
         <v>9.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>4</v>
+        <v>19.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
         <v>4.3</v>
       </c>
       <c r="AY16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>4.1</v>
@@ -3620,23 +3620,23 @@
         <v>4.3</v>
       </c>
       <c r="BC16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE16" t="n">
         <v>4.1</v>
       </c>
-      <c r="BD16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>990</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="I17" t="n">
         <v>990</v>
@@ -3718,7 +3718,7 @@
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="G18" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="H18" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="I18" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="K18" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,146 +3885,146 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>2.96</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="P18" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S18" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY18" t="n">
         <v>4</v>
       </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -4067,10 +4067,10 @@
         <v>4.1</v>
       </c>
       <c r="J19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K19" t="n">
         <v>5.7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.15</v>
@@ -4085,7 +4085,7 @@
         <v>1.07</v>
       </c>
       <c r="P19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q19" t="n">
         <v>1.23</v>
@@ -4112,13 +4112,13 @@
         <v>80</v>
       </c>
       <c r="Y19" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA19" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB19" t="n">
         <v>30</v>
@@ -4142,7 +4142,7 @@
         <v>15.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ19" t="n">
         <v>27</v>
@@ -4154,10 +4154,10 @@
         <v>17</v>
       </c>
       <c r="AM19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AN19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AO19" t="n">
         <v>13.5</v>
@@ -4166,16 +4166,16 @@
         <v>60</v>
       </c>
       <c r="AQ19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AR19" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS19" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AT19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU19" t="n">
         <v>17</v>
@@ -4196,7 +4196,7 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB19" t="n">
         <v>25</v>
@@ -4211,14 +4211,14 @@
         <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG19" t="n">
         <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -4267,13 +4267,13 @@
         <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.25</v>
@@ -4285,134 +4285,134 @@
         <v>1.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
         <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
         <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
         <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K21" t="n">
         <v>950</v>
@@ -4467,7 +4467,7 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
         <v>1.23</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 00:18:01</t>
+          <t>2026-05-05 02:26:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -760,13 +760,13 @@
         <v>2.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H2" t="n">
         <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -787,43 +787,43 @@
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
         <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
         <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
@@ -835,7 +835,7 @@
         <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -847,13 +847,13 @@
         <v>48</v>
       </c>
       <c r="AJ2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK2" t="n">
         <v>29</v>
       </c>
-      <c r="AK2" t="n">
-        <v>24</v>
-      </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
         <v>85</v>
@@ -862,7 +862,7 @@
         <v>15.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
         <v>14.5</v>
@@ -874,10 +874,10 @@
         <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -886,7 +886,7 @@
         <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="BC2" t="n">
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -951,82 +951,82 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="X3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Y3" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AA3" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
@@ -1035,86 +1035,86 @@
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
       </c>
       <c r="AN3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF3" t="n">
         <v>7.8</v>
       </c>
-      <c r="AO3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1178,16 +1178,16 @@
         <v>2.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
         <v>2.48</v>
@@ -1304,11 +1304,11 @@
         <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I5" t="n">
         <v>3.25</v>
@@ -1354,10 +1354,10 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
@@ -1369,16 +1369,16 @@
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="R5" t="n">
         <v>1.73</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.5</v>
@@ -1390,7 +1390,7 @@
         <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1447,19 +1447,19 @@
         <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
         <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU5" t="n">
         <v>9.199999999999999</v>
@@ -1480,7 +1480,7 @@
         <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB5" t="n">
         <v>8.6</v>
@@ -1489,7 +1489,7 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
         <v>8.800000000000001</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1563,7 +1563,7 @@
         <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
         <v>1.92</v>
@@ -1575,7 +1575,7 @@
         <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
         <v>2.12</v>
@@ -1662,7 +1662,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -1677,13 +1677,13 @@
         <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC6" t="n">
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
         <v>9.4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I10" t="n">
         <v>6.2</v>
@@ -2327,10 +2327,10 @@
         <v>4.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
         <v>4.7</v>
@@ -2339,16 +2339,16 @@
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
         <v>1.74</v>
@@ -2357,10 +2357,10 @@
         <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
         <v>2.28</v>
@@ -2512,7 +2512,7 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
@@ -2527,16 +2527,16 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O11" t="n">
         <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.23</v>
@@ -2545,7 +2545,7 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
         <v>1.83</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>2.62</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H12" t="n">
         <v>2.5</v>
       </c>
       <c r="I12" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J12" t="n">
         <v>3.45</v>
@@ -2787,7 +2787,7 @@
         <v>38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK12" t="n">
         <v>34</v>
@@ -2844,13 +2844,13 @@
         <v>30</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
         <v>6.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I13" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
         <v>4.2</v>
@@ -2924,7 +2924,7 @@
         <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
         <v>1.44</v>
@@ -2939,10 +2939,10 @@
         <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2951,25 +2951,25 @@
         <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC13" t="n">
         <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG13" t="n">
         <v>16.5</v>
@@ -2984,19 +2984,19 @@
         <v>65</v>
       </c>
       <c r="AK13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM13" t="n">
         <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP13" t="n">
         <v>14</v>
@@ -3008,13 +3008,13 @@
         <v>13.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV13" t="n">
         <v>9.800000000000001</v>
@@ -3023,7 +3023,7 @@
         <v>19.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY13" t="n">
         <v>12</v>
@@ -3035,26 +3035,26 @@
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
         <v>3.75</v>
       </c>
       <c r="H15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J15" t="n">
         <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>1.41</v>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V15" t="n">
         <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
@@ -3342,7 +3342,7 @@
         <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB15" t="n">
         <v>13.5</v>
@@ -3354,7 +3354,7 @@
         <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF15" t="n">
         <v>27</v>
@@ -3366,7 +3366,7 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
         <v>80</v>
@@ -3381,10 +3381,10 @@
         <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP15" t="n">
         <v>9.199999999999999</v>
@@ -3420,19 +3420,19 @@
         <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.4</v>
+        <v>46</v>
       </c>
       <c r="BC15" t="n">
         <v>32</v>
       </c>
       <c r="BD15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF15" t="n">
         <v>4.3</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>4.2</v>
       </c>
       <c r="G16" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
         <v>1.74</v>
@@ -3485,40 +3485,40 @@
         <v>1.86</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
         <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V16" t="n">
         <v>2.16</v>
@@ -3542,13 +3542,13 @@
         <v>29</v>
       </c>
       <c r="AC16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF16" t="n">
         <v>48</v>
@@ -3572,71 +3572,71 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO16" t="n">
         <v>9.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT16" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV16" t="n">
         <v>9.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ16" t="n">
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB16" t="n">
         <v>4.3</v>
       </c>
       <c r="BC16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD16" t="n">
         <v>32</v>
       </c>
-      <c r="BD16" t="n">
-        <v>4</v>
-      </c>
       <c r="BE16" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>990</v>
+        <v>2.52</v>
       </c>
       <c r="H17" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="I17" t="n">
         <v>990</v>
       </c>
       <c r="J17" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="K17" t="n">
         <v>950</v>
@@ -3718,7 +3718,7 @@
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="H18" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>5.8</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,146 +3885,146 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>2.42</v>
       </c>
       <c r="O18" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P18" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="X18" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>1.23</v>
       </c>
       <c r="R19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="S19" t="n">
         <v>1.57</v>
@@ -4109,7 +4109,7 @@
         <v>2.34</v>
       </c>
       <c r="X19" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Y19" t="n">
         <v>50</v>
@@ -4118,7 +4118,7 @@
         <v>55</v>
       </c>
       <c r="AA19" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB19" t="n">
         <v>30</v>
@@ -4154,7 +4154,7 @@
         <v>17</v>
       </c>
       <c r="AM19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AN19" t="n">
         <v>4</v>
@@ -4163,13 +4163,13 @@
         <v>13.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AQ19" t="n">
         <v>44</v>
       </c>
       <c r="AR19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AS19" t="n">
         <v>80</v>
@@ -4214,11 +4214,11 @@
         <v>3.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G20" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="H20" t="n">
         <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>3.55</v>
@@ -4297,10 +4297,10 @@
         <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
         <v>21</v>
@@ -4309,7 +4309,7 @@
         <v>16.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA20" t="n">
         <v>60</v>
@@ -4342,7 +4342,7 @@
         <v>38</v>
       </c>
       <c r="AK20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL20" t="n">
         <v>40</v>
@@ -4354,7 +4354,7 @@
         <v>19.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP20" t="n">
         <v>13.5</v>
@@ -4408,11 +4408,11 @@
         <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>
@@ -4446,13 +4446,13 @@
         <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H21" t="n">
         <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J21" t="n">
         <v>1.04</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 02:26:21</t>
+          <t>2026-05-05 04:34:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G2" t="n">
         <v>2.22</v>
@@ -781,34 +781,34 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
         <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X2" t="n">
         <v>17</v>
@@ -820,34 +820,34 @@
         <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AK2" t="n">
         <v>29</v>
@@ -856,19 +856,19 @@
         <v>70</v>
       </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
         <v>21</v>
@@ -880,10 +880,10 @@
         <v>9.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
         <v>23</v>
@@ -892,13 +892,13 @@
         <v>12.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
         <v>17.5</v>
@@ -907,7 +907,7 @@
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
         <v>36</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>1.69</v>
       </c>
       <c r="G3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.34</v>
@@ -978,34 +978,34 @@
         <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U3" t="n">
         <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X3" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1020,7 +1020,7 @@
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
@@ -1029,13 +1029,13 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
         <v>65</v>
@@ -1044,10 +1044,10 @@
         <v>18.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -1059,7 +1059,7 @@
         <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>14.5</v>
@@ -1074,28 +1074,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW3" t="n">
         <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BB3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>14.5</v>
@@ -1110,11 +1110,11 @@
         <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
         <v>1.72</v>
@@ -1154,7 +1154,7 @@
         <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>4.5</v>
@@ -1181,13 +1181,13 @@
         <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U4" t="n">
         <v>2.48</v>
@@ -1199,7 +1199,7 @@
         <v>2.38</v>
       </c>
       <c r="X4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
         <v>24</v>
@@ -1211,7 +1211,7 @@
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
@@ -1235,7 +1235,7 @@
         <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
         <v>16.5</v>
@@ -1247,13 +1247,13 @@
         <v>70</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AP4" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AQ4" t="n">
         <v>17</v>
@@ -1265,7 +1265,7 @@
         <v>40</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
         <v>9.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="I5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.24</v>
@@ -1366,73 +1366,73 @@
         <v>6.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
         <v>2.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
         <v>1.73</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U5" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
         <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
         <v>15</v>
       </c>
       <c r="AE5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
         <v>27</v>
@@ -1441,22 +1441,22 @@
         <v>55</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR5" t="n">
         <v>18</v>
       </c>
-      <c r="AP5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9</v>
-      </c>
       <c r="AS5" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
@@ -1468,41 +1468,41 @@
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY5" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
         <v>2.78</v>
@@ -1542,10 +1542,10 @@
         <v>2.88</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.7</v>
@@ -1560,7 +1560,7 @@
         <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
         <v>1.89</v>
@@ -1569,7 +1569,7 @@
         <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3.45</v>
@@ -1578,55 +1578,55 @@
         <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.56</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK6" t="n">
         <v>36</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>30</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
@@ -1635,75 +1635,75 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>34</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="AX6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>H Slavia Kromeriz</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Panevezys</t>
+          <t>Slavia Praha B</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M7" t="n">
         <v>1.04</v>
       </c>
-      <c r="G7" t="n">
-        <v>990</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I7" t="n">
-        <v>990</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="K7" t="n">
-        <v>950</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,33 +1907,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Hunedoara</t>
+          <t>Ceske Budejovice</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Vysocina Jihlava</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>990</v>
+        <v>2.74</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="I8" t="n">
-        <v>990</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1945,34 +1945,34 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.25</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.15</v>
-      </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sparta Prague B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Prostejov</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>2.96</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>2.92</v>
       </c>
       <c r="K9" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>2.66</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Banik Ostrava B</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.63</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>1.92</v>
       </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>2.62</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="K10" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.28</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.23</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>2.68</v>
+        <v>1.86</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="W10" t="n">
-        <v>2.42</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Apollon Limassol</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28</v>
+        <v>990</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>990</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.92</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1.37</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aris FC Limassol</t>
+          <t>FC Hunedoara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.98</v>
+        <v>990</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.82</v>
+        <v>990</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>1.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>1.41</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.15</v>
+        <v>1.49</v>
       </c>
       <c r="G13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X13" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD13" t="n">
         <v>3.9</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="BE13" t="n">
         <v>4.2</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X13" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF13" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fk Siauliai</t>
+          <t>FK Pribram</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="G14" t="n">
-        <v>990</v>
+        <v>1.91</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>990</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,34 +3109,34 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="O14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.15</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FC Sellier &amp; Bellot Vlasim</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>Zizkov</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="H15" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="I15" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>1.84</v>
       </c>
       <c r="O15" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.89</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.93</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>MFK Chrudim</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>1.74</v>
       </c>
       <c r="H16" t="n">
-        <v>1.74</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.86</v>
+        <v>7.2</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.17</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.16</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
         <v>24</v>
       </c>
-      <c r="AB16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>48</v>
-      </c>
       <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
         <v>23</v>
       </c>
-      <c r="AH16" t="n">
-        <v>21</v>
-      </c>
       <c r="AI16" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
-        <v>60</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>40</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO16" t="n">
-        <v>9.4</v>
+        <v>95</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M17" t="n">
         <v>1.04</v>
       </c>
-      <c r="G17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>990</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="N17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X17" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y17" t="n">
         <v>950</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Aris FC Limassol</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.3</v>
+        <v>2.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU18" t="n">
         <v>7.2</v>
       </c>
-      <c r="I18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>2.28</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>14</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X19" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH19" t="n">
+      <c r="BA19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF19" t="n">
         <v>15.5</v>
       </c>
-      <c r="AI19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>44</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,51 +4235,51 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Usti Nad Labem</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Paso Locomotive FC</t>
+          <t>SFC Opava</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
         <v>1.75</v>
@@ -4288,325 +4288,1877 @@
         <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
         <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA20" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG20" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>19</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 04:34:24</t>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X21" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:43:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VMFD Zalgiris</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Fk Siauliai</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>990</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>990</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K22" t="n">
+        <v>950</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:43:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Spartak Varna</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Dobrudzha</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:43:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Hapoel Beer Sheva</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:43:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TransINVEST Vilnius</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FK Suduva</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I25" t="n">
+        <v>990</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K25" t="n">
+        <v>950</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:43:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Al-Fateh (KSA)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X26" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:43:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>14</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X27" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:43:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X28" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:43:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>23:15:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>CD Olimpia</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>CD Marathon</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F29" t="n">
         <v>1.04</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G29" t="n">
         <v>110</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H29" t="n">
         <v>1.04</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I29" t="n">
         <v>110</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J29" t="n">
         <v>1.04</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K29" t="n">
         <v>950</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O29" t="n">
         <v>1.23</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S29" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-05-05 04:34:24</t>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:43:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,22 +760,22 @@
         <v>2.16</v>
       </c>
       <c r="G2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -787,13 +787,13 @@
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>3.2</v>
@@ -808,28 +808,28 @@
         <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X2" t="n">
         <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>48</v>
@@ -841,7 +841,7 @@
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
         <v>50</v>
@@ -850,13 +850,13 @@
         <v>30</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
         <v>15</v>
@@ -865,7 +865,7 @@
         <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
@@ -895,13 +895,13 @@
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>19</v>
@@ -910,17 +910,17 @@
         <v>22</v>
       </c>
       <c r="BE2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
         <v>23</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.69</v>
       </c>
       <c r="G3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -963,40 +963,40 @@
         <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
         <v>1.23</v>
@@ -1011,28 +1011,28 @@
         <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
         <v>140</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
         <v>20</v>
@@ -1041,10 +1041,10 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK3" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>34</v>
@@ -1059,7 +1059,7 @@
         <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
         <v>14.5</v>
@@ -1089,10 +1089,10 @@
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
         <v>13</v>
@@ -1101,7 +1101,7 @@
         <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
         <v>38</v>
@@ -1110,11 +1110,11 @@
         <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
         <v>1.72</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.8</v>
@@ -1178,31 +1178,31 @@
         <v>2.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.44</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.48</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
         <v>2.38</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
         <v>110</v>
@@ -1217,40 +1217,40 @@
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL4" t="n">
         <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AP4" t="n">
         <v>22</v>
@@ -1259,7 +1259,7 @@
         <v>17</v>
       </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AS4" t="n">
         <v>40</v>
@@ -1268,13 +1268,13 @@
         <v>11</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
@@ -1289,7 +1289,7 @@
         <v>27</v>
       </c>
       <c r="BB4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
@@ -1301,14 +1301,14 @@
         <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
         <v>32</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -1363,16 +1363,16 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
         <v>2.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
         <v>1.73</v>
@@ -1384,13 +1384,13 @@
         <v>1.49</v>
       </c>
       <c r="U5" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X5" t="n">
         <v>34</v>
@@ -1402,43 +1402,43 @@
         <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
         <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>14.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
         <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN5" t="n">
         <v>10.5</v>
@@ -1450,10 +1450,10 @@
         <v>19</v>
       </c>
       <c r="AQ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR5" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>18</v>
       </c>
       <c r="AS5" t="n">
         <v>28</v>
@@ -1483,10 +1483,10 @@
         <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
         <v>21</v>
@@ -1495,14 +1495,14 @@
         <v>26</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1536,22 @@
         <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1563,10 +1563,10 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
@@ -1581,64 +1581,64 @@
         <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
         <v>13</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
         <v>18.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
         <v>46</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP6" t="n">
         <v>10</v>
@@ -1647,10 +1647,10 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="AT6" t="n">
         <v>9.199999999999999</v>
@@ -1662,16 +1662,16 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY6" t="n">
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
         <v>32</v>
@@ -1680,23 +1680,23 @@
         <v>27</v>
       </c>
       <c r="BC6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF6" t="n">
         <v>20</v>
       </c>
-      <c r="BD6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG6" t="n">
-        <v>23</v>
+        <v>5.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="H7" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>4.3</v>
@@ -1751,22 +1751,22 @@
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
         <v>1.52</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="T7" t="n">
         <v>1.57</v>
@@ -1775,10 +1775,10 @@
         <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="X7" t="n">
         <v>25</v>
@@ -1799,7 +1799,7 @@
         <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
         <v>38</v>
@@ -1835,52 +1835,52 @@
         <v>28</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF7" t="n">
         <v>9.6</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
@@ -1954,13 +1954,13 @@
         <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H9" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
@@ -2130,7 +2130,7 @@
         <v>2.92</v>
       </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,22 +2139,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O9" t="n">
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -2318,13 +2318,13 @@
         <v>1.92</v>
       </c>
       <c r="I10" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>2.92</v>
       </c>
       <c r="K10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,7 +2333,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>1.76</v>
       </c>
       <c r="O10" t="n">
         <v>1.28</v>
@@ -2342,13 +2342,13 @@
         <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2357,7 +2357,7 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
         <v>1.25</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>990</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
         <v>990</v>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q11" t="n">
         <v>1.38</v>
@@ -2542,7 +2542,7 @@
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>990</v>
+        <v>380</v>
       </c>
       <c r="J12" t="n">
         <v>1.04</v>
@@ -2721,22 +2721,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R12" t="n">
         <v>1.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.49</v>
       </c>
       <c r="G13" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="H13" t="n">
         <v>6.2</v>
@@ -2903,7 +2903,7 @@
         <v>8.6</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
         <v>5.4</v>
@@ -2924,7 +2924,7 @@
         <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R13" t="n">
         <v>1.6</v>
@@ -2942,7 +2942,7 @@
         <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="X13" t="n">
         <v>32</v>
@@ -3026,7 +3026,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ13" t="n">
         <v>14.5</v>
@@ -3035,13 +3035,13 @@
         <v>4.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC13" t="n">
         <v>11</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
         <v>4.2</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.96</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
         <v>1.59</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP14" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ14" t="n">
         <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC14" t="n">
         <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
         <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="H15" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.1</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7.4</v>
-      </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.84</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="T15" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -3473,64 +3473,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G16" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="U16" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
         <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
         <v>60</v>
@@ -3539,104 +3539,104 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
         <v>24</v>
       </c>
       <c r="AE16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI16" t="n">
         <v>90</v>
       </c>
-      <c r="AF16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>85</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AK16" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO16" t="n">
         <v>120</v>
       </c>
-      <c r="AN16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>95</v>
-      </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="BF16" t="n">
         <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.28</v>
@@ -3706,7 +3706,7 @@
         <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
         <v>1.74</v>
@@ -3721,7 +3721,7 @@
         <v>2.42</v>
       </c>
       <c r="X17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
         <v>950</v>
@@ -3736,7 +3736,7 @@
         <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -3745,10 +3745,10 @@
         <v>70</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
         <v>24</v>
@@ -3760,7 +3760,7 @@
         <v>17.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL17" t="n">
         <v>36</v>
@@ -3775,16 +3775,16 @@
         <v>80</v>
       </c>
       <c r="AP17" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>16.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>32</v>
+        <v>5.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT17" t="n">
         <v>7.4</v>
@@ -3793,13 +3793,13 @@
         <v>9.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
         <v>8.6</v>
@@ -3808,7 +3808,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>44</v>
+        <v>5.2</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -3820,17 +3820,17 @@
         <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
         <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.62</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H18" t="n">
         <v>2.5</v>
@@ -3873,7 +3873,7 @@
         <v>2.82</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
         <v>4.1</v>
@@ -3912,13 +3912,13 @@
         <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X18" t="n">
         <v>21</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
         <v>22</v>
@@ -3957,7 +3957,7 @@
         <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
         <v>85</v>
@@ -3966,19 +3966,19 @@
         <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>10.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT18" t="n">
         <v>11</v>
@@ -3987,44 +3987,44 @@
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
         <v>5.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>5.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
         <v>2.28</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T19" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="V19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF19" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BG19" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="G20" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H20" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="I20" t="n">
         <v>3.1</v>
@@ -4267,52 +4267,52 @@
         <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
         <v>1.54</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB20" t="n">
         <v>16</v>
@@ -4321,13 +4321,13 @@
         <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
         <v>15.5</v>
@@ -4339,80 +4339,80 @@
         <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
         <v>90</v>
       </c>
       <c r="AN20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF20" t="n">
-        <v>16</v>
+        <v>3.55</v>
       </c>
       <c r="BG20" t="n">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -4452,13 +4452,13 @@
         <v>2.14</v>
       </c>
       <c r="I21" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>3.6</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.34</v>
@@ -4488,10 +4488,10 @@
         <v>1.62</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W21" t="n">
         <v>1.38</v>
@@ -4551,62 +4551,62 @@
         <v>17</v>
       </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT21" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX21" t="n">
         <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF21" t="n">
         <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>3.2</v>
       </c>
       <c r="G23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H23" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I23" t="n">
         <v>2.68</v>
@@ -4846,7 +4846,7 @@
         <v>3.1</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L23" t="n">
         <v>1.47</v>
@@ -4864,13 +4864,13 @@
         <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T23" t="n">
         <v>1.89</v>
@@ -4879,10 +4879,10 @@
         <v>1.93</v>
       </c>
       <c r="V23" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W23" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X23" t="n">
         <v>13</v>
@@ -4900,7 +4900,7 @@
         <v>13.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
         <v>14.5</v>
@@ -4915,7 +4915,7 @@
         <v>18</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>55</v>
@@ -4939,7 +4939,7 @@
         <v>36</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ23" t="n">
         <v>7.6</v>
@@ -4948,7 +4948,7 @@
         <v>13</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="AT23" t="n">
         <v>9.4</v>
@@ -4960,10 +4960,10 @@
         <v>10</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.3</v>
+        <v>22</v>
       </c>
       <c r="AX23" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AY23" t="n">
         <v>12.5</v>
@@ -4972,29 +4972,29 @@
         <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>34</v>
+        <v>4.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BC23" t="n">
-        <v>32</v>
+        <v>4.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.3</v>
+        <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG23" t="n">
         <v>21</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>4.2</v>
       </c>
       <c r="G24" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="H24" t="n">
         <v>1.74</v>
@@ -5058,7 +5058,7 @@
         <v>2.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="R24" t="n">
         <v>1.66</v>
@@ -5157,7 +5157,7 @@
         <v>12</v>
       </c>
       <c r="AX24" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AY24" t="n">
         <v>13.5</v>
@@ -5172,23 +5172,23 @@
         <v>4.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BG24" t="n">
         <v>5.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
@@ -5225,13 +5225,13 @@
         <v>2.52</v>
       </c>
       <c r="H25" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
         <v>990</v>
       </c>
       <c r="J25" t="n">
-        <v>1.68</v>
+        <v>1.09</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5243,19 +5243,19 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="O25" t="n">
         <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q25" t="n">
         <v>1.29</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S25" t="n">
         <v>1.29</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>1.46</v>
+        <v>990</v>
       </c>
       <c r="H26" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="P26" t="n">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>2.24</v>
+        <v>1.05</v>
       </c>
       <c r="T26" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>1.73</v>
+        <v>110</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>110</v>
       </c>
       <c r="J27" t="n">
-        <v>5.7</v>
+        <v>1.02</v>
       </c>
       <c r="K27" t="n">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L27" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>14</v>
+        <v>1.24</v>
       </c>
       <c r="O27" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="P27" t="n">
-        <v>5.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="R27" t="n">
-        <v>2.72</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="T27" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AR27" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="AS27" t="n">
-        <v>80</v>
+        <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AV27" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AW27" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AY27" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA27" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BC27" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD27" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE27" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,378 +5787,960 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Juventus B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Paso Locomotive FC</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>2.56</v>
+        <v>990</v>
       </c>
       <c r="H28" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>3.25</v>
+        <v>990</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>1.24</v>
       </c>
       <c r="O28" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>2.84</v>
+        <v>1.39</v>
       </c>
       <c r="T28" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
         <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
         <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
         <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 06:43:40</t>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Al-Fateh (KSA)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-05-05 08:54:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>14</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X30" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-05-05 08:54:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X31" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-05-05 08:54:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>23:15:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>CD Olimpia</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>CD Marathon</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F32" t="n">
         <v>1.04</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G32" t="n">
         <v>110</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H32" t="n">
         <v>1.04</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I32" t="n">
         <v>110</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J32" t="n">
         <v>1.04</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K32" t="n">
         <v>950</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O29" t="n">
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O32" t="n">
         <v>1.23</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="P32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1.23</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R32" t="n">
         <v>1.18</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S32" t="n">
         <v>1.24</v>
       </c>
-      <c r="T29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-05-05 06:43:40</t>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-05-05 08:54:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>2.16</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H2" t="n">
         <v>3.55</v>
@@ -775,7 +775,7 @@
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -790,7 +790,7 @@
         <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R2" t="n">
         <v>1.42</v>
@@ -802,19 +802,19 @@
         <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X2" t="n">
         <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
         <v>38</v>
@@ -829,10 +829,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
         <v>14.5</v>
@@ -841,10 +841,10 @@
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
         <v>30</v>
@@ -859,13 +859,13 @@
         <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO2" t="n">
         <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
@@ -895,7 +895,7 @@
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>38</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G3" t="n">
         <v>1.73</v>
@@ -990,7 +990,7 @@
         <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
         <v>1.78</v>
@@ -999,7 +999,7 @@
         <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
         <v>2.36</v>
@@ -1029,22 +1029,22 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AL3" t="n">
         <v>34</v>
@@ -1059,10 +1059,10 @@
         <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>24</v>
@@ -1071,7 +1071,7 @@
         <v>42</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
@@ -1083,25 +1083,25 @@
         <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="n">
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC3" t="n">
         <v>14.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
         <v>38</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
         <v>5.3</v>
@@ -1169,7 +1169,7 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
@@ -1190,25 +1190,25 @@
         <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V4" t="n">
         <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
         <v>27</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="Z4" t="n">
         <v>110</v>
       </c>
       <c r="AA4" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB4" t="n">
         <v>12.5</v>
@@ -1223,7 +1223,7 @@
         <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
@@ -1235,10 +1235,10 @@
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL4" t="n">
         <v>40</v>
@@ -1247,7 +1247,7 @@
         <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO4" t="n">
         <v>120</v>
@@ -1256,10 +1256,10 @@
         <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
         <v>40</v>
@@ -1271,10 +1271,10 @@
         <v>9.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
@@ -1286,13 +1286,13 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD4" t="n">
         <v>19</v>
@@ -1304,11 +1304,11 @@
         <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>3.15</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
@@ -1369,22 +1369,22 @@
         <v>1.17</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
         <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="V5" t="n">
         <v>1.46</v>
@@ -1393,13 +1393,13 @@
         <v>1.73</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
         <v>55</v>
@@ -1414,7 +1414,7 @@
         <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
         <v>20</v>
@@ -1426,10 +1426,10 @@
         <v>14.5</v>
       </c>
       <c r="AI5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>32</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>36</v>
       </c>
       <c r="AK5" t="n">
         <v>21</v>
@@ -1444,7 +1444,7 @@
         <v>10.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
         <v>19</v>
@@ -1462,7 +1462,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV5" t="n">
         <v>12.5</v>
@@ -1474,10 +1474,10 @@
         <v>17.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
         <v>20</v>
@@ -1495,14 +1495,14 @@
         <v>26</v>
       </c>
       <c r="BF5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1536,22 @@
         <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H6" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="I6" t="n">
         <v>3.15</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1563,10 +1563,10 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
@@ -1578,28 +1578,28 @@
         <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
         <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
@@ -1608,22 +1608,22 @@
         <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF6" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>48</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>46</v>
       </c>
       <c r="AK6" t="n">
         <v>32</v>
@@ -1650,7 +1650,7 @@
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>34</v>
+        <v>5.5</v>
       </c>
       <c r="AT6" t="n">
         <v>9.199999999999999</v>
@@ -1671,32 +1671,32 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>5.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>3.55</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>4.3</v>
@@ -1751,7 +1751,7 @@
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.21</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>25</v>
+        <v>4.4</v>
       </c>
       <c r="AX7" t="n">
         <v>12.5</v>
@@ -1868,7 +1868,7 @@
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>28</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
         <v>21</v>
@@ -1877,7 +1877,7 @@
         <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>22</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
         <v>4.7</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -1927,49 +1927,49 @@
         <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>2.68</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
         <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
         <v>1.58</v>
@@ -1978,34 +1978,34 @@
         <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2014,7 +2014,7 @@
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2032,10 +2032,10 @@
         <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
         <v>1.03</v>
@@ -2044,22 +2044,22 @@
         <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
         <v>1.03</v>
@@ -2068,7 +2068,7 @@
         <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
         <v>1.03</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -2130,37 +2130,37 @@
         <v>2.92</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.72</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
         <v>1.92</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.27</v>
@@ -2172,43 +2172,43 @@
         <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2226,43 +2226,43 @@
         <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD9" t="n">
         <v>1.03</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -2309,91 +2309,91 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="J10" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG10" t="n">
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2420,31 +2420,31 @@
         <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
         <v>1.03</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>990</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>2.94</v>
       </c>
       <c r="I11" t="n">
-        <v>990</v>
+        <v>3.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>2.74</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>2.96</v>
       </c>
       <c r="O11" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.38</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>380</v>
+        <v>870</v>
       </c>
       <c r="J12" t="n">
         <v>1.04</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Krka</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="G13" t="n">
-        <v>1.59</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>1.24</v>
       </c>
       <c r="O13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.18</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.6</v>
-      </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>1.02</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,94 +3076,94 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FK Pribram</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="G14" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.04</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="X14" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y14" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Z14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE14" t="n">
         <v>95</v>
       </c>
       <c r="AF14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG14" t="n">
         <v>12.5</v>
@@ -3172,83 +3172,83 @@
         <v>25</v>
       </c>
       <c r="AI14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO14" t="n">
         <v>90</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK14" t="n">
+      <c r="AP14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>20</v>
       </c>
-      <c r="AL14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY14" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Sellier &amp; Bellot Vlasim</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zizkov</t>
+          <t>FK Pribram</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="G15" t="n">
-        <v>2.28</v>
+        <v>1.73</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.98</v>
+        <v>2.58</v>
       </c>
       <c r="T15" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="U15" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y15" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AA15" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AB15" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK15" t="n">
         <v>20</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>27</v>
       </c>
       <c r="AL15" t="n">
         <v>40</v>
       </c>
       <c r="AM15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO15" t="n">
         <v>100</v>
       </c>
-      <c r="AN15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>46</v>
-      </c>
       <c r="AP15" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
         <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC15" t="n">
         <v>12</v>
       </c>
-      <c r="BA15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BD15" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
         <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BG15" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>FC Sellier &amp; Bellot Vlasim</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MFK Chrudim</t>
+          <t>Zizkov</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="G16" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.79</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="X16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH16" t="n">
         <v>20</v>
       </c>
-      <c r="Y16" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>26</v>
-      </c>
       <c r="AI16" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO16" t="n">
         <v>42</v>
       </c>
-      <c r="AM16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>120</v>
-      </c>
       <c r="AP16" t="n">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>MFK Chrudim</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="G17" t="n">
         <v>1.7</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="U17" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
         <v>2.42</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Z17" t="n">
         <v>60</v>
       </c>
       <c r="AA17" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AF17" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AK17" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO17" t="n">
         <v>120</v>
       </c>
-      <c r="AN17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>80</v>
-      </c>
       <c r="AP17" t="n">
-        <v>18.5</v>
+        <v>4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16.5</v>
+        <v>4.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>14.5</v>
+        <v>3.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aris FC Limassol</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.62</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
-        <v>2.96</v>
+        <v>1.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>950</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="AA18" t="n">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AH18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU18" t="n">
+      <c r="BC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF18" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BG18" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Aris FC Limassol</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Apollon Limassol</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="G19" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X19" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
         <v>5</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>13</v>
-      </c>
       <c r="AW19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX19" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX19" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY19" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BE19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF19" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BG19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Usti Nad Labem</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SFC Opava</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.15</v>
+        <v>2.32</v>
       </c>
       <c r="H20" t="n">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.25</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.48</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="X20" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="BA20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF20" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BG20" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Usti Nad Labem</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>SFC Opava</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="H21" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="O21" t="n">
         <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
         <v>1.73</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="T21" t="n">
         <v>1.62</v>
       </c>
       <c r="U21" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AA21" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AF21" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK21" t="n">
         <v>38</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>42</v>
-      </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AP21" t="n">
-        <v>15.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.6</v>
+        <v>3.05</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>19</v>
+        <v>3.75</v>
       </c>
       <c r="AX21" t="n">
-        <v>19</v>
+        <v>3.65</v>
       </c>
       <c r="AY21" t="n">
-        <v>12</v>
+        <v>3.35</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13.5</v>
+        <v>3.55</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BF21" t="n">
-        <v>21</v>
+        <v>3.65</v>
       </c>
       <c r="BG21" t="n">
-        <v>12</v>
+        <v>3.75</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fk Siauliai</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G22" t="n">
-        <v>990</v>
+        <v>3.6</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="I22" t="n">
-        <v>990</v>
+        <v>2.48</v>
       </c>
       <c r="J22" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.15</v>
+        <v>1.71</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>1.14</v>
+        <v>2.66</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>Fk Siauliai</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>1.43</v>
       </c>
       <c r="G23" t="n">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="H23" t="n">
-        <v>2.36</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S23" t="n">
         <v>2.12</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T23" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="V23" t="n">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>2.8</v>
       </c>
       <c r="X23" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.5</v>
+        <v>75</v>
       </c>
       <c r="AA23" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AD23" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AF23" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AG23" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>70</v>
+        <v>970</v>
       </c>
       <c r="AK23" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AM23" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AN23" t="n">
-        <v>65</v>
+        <v>6.2</v>
       </c>
       <c r="AO23" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AP23" t="n">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="AR23" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>26</v>
+        <v>4.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.4</v>
+        <v>3.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>10</v>
+        <v>3.95</v>
       </c>
       <c r="AW23" t="n">
-        <v>22</v>
+        <v>4.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>16.5</v>
+        <v>3.7</v>
       </c>
       <c r="AY23" t="n">
-        <v>12.5</v>
+        <v>3.65</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD23" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>42</v>
-      </c>
       <c r="BE23" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="BG23" t="n">
-        <v>21</v>
+        <v>4.3</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="G24" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="H24" t="n">
-        <v>1.74</v>
+        <v>3.15</v>
       </c>
       <c r="I24" t="n">
-        <v>1.86</v>
+        <v>3.85</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>2.92</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>2.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="T24" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="V24" t="n">
-        <v>2.16</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="X24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK24" t="n">
         <v>34</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>55</v>
       </c>
       <c r="AL24" t="n">
         <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>8.800000000000001</v>
+        <v>65</v>
       </c>
       <c r="AP24" t="n">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>14.5</v>
+        <v>4</v>
       </c>
       <c r="AT24" t="n">
-        <v>17</v>
+        <v>3.05</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>2.92</v>
       </c>
       <c r="AV24" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="AW24" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="AY24" t="n">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="BA24" t="n">
-        <v>18.5</v>
+        <v>3.95</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="G25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H25" t="n">
         <v>2.52</v>
       </c>
-      <c r="H25" t="n">
-        <v>1.04</v>
-      </c>
       <c r="I25" t="n">
-        <v>990</v>
+        <v>2.88</v>
       </c>
       <c r="J25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M25" t="n">
         <v>1.09</v>
       </c>
-      <c r="K25" t="n">
-        <v>950</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N25" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>1.29</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W25" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G26" t="n">
-        <v>990</v>
+        <v>5.4</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>1.86</v>
       </c>
       <c r="J26" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>2.64</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.66</v>
       </c>
       <c r="S26" t="n">
-        <v>1.05</v>
+        <v>2.06</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -5598,28 +5598,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H27" t="n">
         <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K27" t="n">
         <v>950</v>
@@ -5631,28 +5631,28 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="P27" t="n">
         <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
@@ -5792,12 +5792,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Juventus B</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>US Pianese</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -5825,22 +5825,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O28" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R28" t="n">
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Juventus B</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>1.45</v>
+        <v>990</v>
       </c>
       <c r="H29" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>8.800000000000001</v>
+        <v>990</v>
       </c>
       <c r="J29" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="P29" t="n">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="R29" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>2.24</v>
+        <v>1.41</v>
       </c>
       <c r="T29" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>1.73</v>
+        <v>160</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>4.2</v>
+        <v>110</v>
       </c>
       <c r="J30" t="n">
-        <v>5.7</v>
+        <v>1.02</v>
       </c>
       <c r="K30" t="n">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>14</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="P30" t="n">
-        <v>5.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="R30" t="n">
-        <v>2.74</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="T30" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AR30" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AS30" t="n">
-        <v>80</v>
+        <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AU30" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AW30" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA30" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BB30" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BC30" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD30" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE30" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Paso Locomotive FC</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.32</v>
+        <v>1.39</v>
       </c>
       <c r="G31" t="n">
-        <v>2.64</v>
+        <v>1.45</v>
       </c>
       <c r="H31" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="I31" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="M31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N31" t="n">
+        <v>6</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X31" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF31" t="n">
         <v>3.9</v>
       </c>
-      <c r="O31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X31" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG31" t="n">
-        <v>18.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-05 08:54:04</t>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,33 +6563,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD Marathon</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1.04</v>
       </c>
       <c r="G32" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="H32" t="n">
         <v>1.04</v>
       </c>
       <c r="I32" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="J32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="K32" t="n">
         <v>950</v>
@@ -6601,146 +6601,728 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:04:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K33" t="n">
+        <v>6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>14</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X33" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>48</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:04:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X34" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:04:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>23:15:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CD Olimpia</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CD Marathon</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G35" t="n">
+        <v>990</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I35" t="n">
+        <v>990</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K35" t="n">
+        <v>950</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S35" t="n">
         <v>1.24</v>
       </c>
-      <c r="T32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-05-05 08:54:04</t>
+      <c r="T35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:04:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH35"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I2" t="n">
         <v>3.55</v>
       </c>
-      <c r="I2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
@@ -784,91 +784,91 @@
         <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
         <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH2" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
         <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
         <v>21</v>
@@ -877,19 +877,19 @@
         <v>32</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
         <v>7.4</v>
       </c>
       <c r="AV2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX2" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -898,29 +898,29 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
         <v>34</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>1.68</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -990,10 +990,10 @@
         <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
         <v>2.18</v>
@@ -1002,7 +1002,7 @@
         <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1041,7 +1041,7 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
         <v>17.5</v>
@@ -1056,16 +1056,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP3" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
         <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AS3" t="n">
         <v>42</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>5.3</v>
@@ -1160,7 +1160,7 @@
         <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1181,7 +1181,7 @@
         <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
         <v>2.42</v>
@@ -1190,13 +1190,13 @@
         <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X4" t="n">
         <v>27</v>
@@ -1223,7 +1223,7 @@
         <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
@@ -1238,7 +1238,7 @@
         <v>19</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>40</v>
@@ -1247,13 +1247,13 @@
         <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
         <v>120</v>
       </c>
       <c r="AP4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AQ4" t="n">
         <v>20</v>
@@ -1274,7 +1274,7 @@
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
@@ -1283,7 +1283,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
         <v>42</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="H5" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="I5" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
@@ -1366,31 +1366,31 @@
         <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S5" t="n">
         <v>2.26</v>
       </c>
       <c r="T5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.5</v>
       </c>
-      <c r="U5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.46</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="X5" t="n">
         <v>30</v>
@@ -1399,7 +1399,7 @@
         <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AA5" t="n">
         <v>55</v>
@@ -1411,22 +1411,22 @@
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
         <v>14.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
         <v>32</v>
@@ -1444,10 +1444,10 @@
         <v>10.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>18</v>
@@ -1456,10 +1456,10 @@
         <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU5" t="n">
         <v>9</v>
@@ -1468,7 +1468,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1477,32 +1477,32 @@
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BE5" t="n">
         <v>26</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="H6" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
@@ -1596,10 +1596,10 @@
         <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
@@ -1608,7 +1608,7 @@
         <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
         <v>21</v>
@@ -1617,31 +1617,31 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
         <v>9.199999999999999</v>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
         <v>14.5</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>36</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
         <v>17.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>H Slavia Kromeriz</t>
+          <t>Banik Ostrava B</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha B</t>
+          <t>FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>2.34</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="W7" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE7" t="n">
         <v>30</v>
       </c>
-      <c r="AA7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>38</v>
-      </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -1912,55 +1912,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ceske Budejovice</t>
+          <t>Sparta Prague B</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vysocina Jihlava</t>
+          <t>Prostejov</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -1969,19 +1969,19 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -1990,101 +1990,101 @@
         <v>13</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
         <v>20</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>21</v>
-      </c>
       <c r="AG8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR8" t="n">
         <v>16</v>
       </c>
-      <c r="AH8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -2106,55 +2106,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sparta Prague B</t>
+          <t>Ceske Budejovice</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prostejov</t>
+          <t>Vysocina Jihlava</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.68</v>
       </c>
-      <c r="H9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
         <v>1.92</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2163,53 +2163,53 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
         <v>21</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>20</v>
-      </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK9" t="n">
         <v>42</v>
       </c>
-      <c r="AK9" t="n">
-        <v>36</v>
-      </c>
       <c r="AL9" t="n">
         <v>1000</v>
       </c>
@@ -2226,43 +2226,43 @@
         <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
         <v>1.03</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,100 +2300,100 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Banik Ostrava B</t>
+          <t>Gandzasar Kapan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Zbrojovka Brno</t>
+          <t>FC Noah</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.06</v>
+        <v>1.26</v>
       </c>
       <c r="I10" t="n">
-        <v>2.42</v>
+        <v>1.58</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>16</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="O10" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.74</v>
+        <v>2.74</v>
       </c>
       <c r="W10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2417,25 +2417,25 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
         <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
         <v>1.01</v>
@@ -2447,22 +2447,22 @@
         <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Ararat Armenia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panevezys</t>
+          <t>FC Pyunik</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
         <v>2.74</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
         <v>2.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Hunedoara</t>
+          <t>H Slavia Kromeriz</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Slavia Praha B</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M12" t="n">
         <v>1.04</v>
       </c>
-      <c r="G12" t="n">
-        <v>990</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I12" t="n">
-        <v>870</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K12" t="n">
-        <v>950</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>1.37</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Krka</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>FC Hunedoara</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.64</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>8.6</v>
+        <v>190</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>1.37</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Krka</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Pribram</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="G15" t="n">
-        <v>1.73</v>
+        <v>990</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>990</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>2.58</v>
+        <v>1.34</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
         <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
         <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
         <v>2.28</v>
@@ -3482,16 +3482,16 @@
         <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
@@ -3500,19 +3500,19 @@
         <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
         <v>1.68</v>
@@ -3521,16 +3521,16 @@
         <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z16" t="n">
         <v>34</v>
@@ -3545,7 +3545,7 @@
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>48</v>
@@ -3566,19 +3566,19 @@
         <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP16" t="n">
         <v>12.5</v>
@@ -3587,22 +3587,22 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -3614,36 +3614,36 @@
         <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB16" t="n">
         <v>19.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MFK Chrudim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.58</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.7</v>
-      </c>
       <c r="H17" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
         <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="U17" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Y17" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Z17" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AE17" t="n">
         <v>100</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
         <v>25</v>
       </c>
       <c r="AI17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO17" t="n">
         <v>90</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN17" t="n">
+      <c r="AP17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="BC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE17" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ17" t="n">
+      <c r="BF17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG17" t="n">
         <v>4.1</v>
       </c>
-      <c r="BA17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>FK Pribram</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.28</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W18" t="n">
         <v>2.16</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.42</v>
-      </c>
       <c r="X18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aris FC Limassol</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>MFK Chrudim</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2.84</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y19" t="n">
         <v>21</v>
       </c>
-      <c r="Y19" t="n">
-        <v>15</v>
-      </c>
       <c r="Z19" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AA19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC19" t="n">
         <v>970</v>
       </c>
-      <c r="AC19" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
         <v>970</v>
       </c>
       <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>970</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL19" t="n">
         <v>38</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>40</v>
-      </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="AT19" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AW19" t="n">
         <v>4.9</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BG19" t="n">
         <v>5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Usti Nad Labem</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Apollon Limassol</t>
+          <t>SFC Opava</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.32</v>
+        <v>2.76</v>
       </c>
       <c r="H20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X20" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP20" t="n">
         <v>3.9</v>
       </c>
-      <c r="I20" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="AQ20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX20" t="n">
         <v>3.9</v>
       </c>
-      <c r="T20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="X20" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>10</v>
-      </c>
       <c r="AY20" t="n">
-        <v>8.6</v>
+        <v>3.55</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>15.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Usti Nad Labem</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SFC Opava</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W21" t="n">
         <v>2.42</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.54</v>
-      </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z21" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AE21" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH21" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
-        <v>46</v>
+        <v>17.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>38</v>
+        <v>16.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AM21" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO21" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.6</v>
+        <v>18.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.45</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.05</v>
+        <v>9.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.35</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.55</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.75</v>
+        <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>4</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.65</v>
+        <v>7.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.75</v>
+        <v>9.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Aris FC Limassol</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="G22" t="n">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="H22" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="I22" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="T22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z22" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA22" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AB22" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AF22" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AG22" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI22" t="n">
         <v>38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AK22" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
         <v>85</v>
       </c>
       <c r="AN22" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AP22" t="n">
-        <v>15.5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>13.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW22" t="n">
         <v>5</v>
       </c>
-      <c r="AT22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>19</v>
-      </c>
       <c r="AX22" t="n">
-        <v>19</v>
+        <v>4.7</v>
       </c>
       <c r="AY22" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF22" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF22" t="n">
-        <v>21</v>
-      </c>
       <c r="BG22" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fk Siauliai</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.55</v>
+        <v>2.24</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="K23" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="R23" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="V23" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="X23" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="Y23" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AF23" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AK23" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AL23" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AM23" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="AO23" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.8</v>
+        <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>3.95</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.9</v>
+        <v>14.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P24" t="n">
         <v>2.12</v>
       </c>
-      <c r="G24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.68</v>
-      </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="W24" t="n">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="X24" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AF24" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AK24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN24" t="n">
         <v>34</v>
       </c>
-      <c r="AL24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>28</v>
-      </c>
       <c r="AO24" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.3</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.05</v>
+        <v>13</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.92</v>
+        <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.9</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>3.35</v>
+        <v>21</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.55</v>
+        <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BE24" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.6</v>
+        <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dobrudzha</t>
+          <t>Fk Siauliai</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.96</v>
+        <v>1.41</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4</v>
+        <v>1.52</v>
       </c>
       <c r="H25" t="n">
-        <v>2.52</v>
+        <v>6.8</v>
       </c>
       <c r="I25" t="n">
-        <v>2.88</v>
+        <v>9.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="O25" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.54</v>
+        <v>1.12</v>
       </c>
       <c r="W25" t="n">
-        <v>1.42</v>
+        <v>2.92</v>
       </c>
       <c r="X25" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.5</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG25" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI25" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AJ25" t="n">
-        <v>70</v>
+        <v>970</v>
       </c>
       <c r="AK25" t="n">
-        <v>50</v>
+        <v>970</v>
       </c>
       <c r="AL25" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AM25" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AN25" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT25" t="n">
         <v>9</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>3.85</v>
       </c>
       <c r="AY25" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>4.3</v>
       </c>
       <c r="BA25" t="n">
-        <v>40</v>
+        <v>4.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF25" t="n">
         <v>4.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="G26" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="H26" t="n">
-        <v>1.74</v>
+        <v>2.54</v>
       </c>
       <c r="I26" t="n">
-        <v>1.86</v>
+        <v>2.84</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="K26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB26" t="n">
         <v>4.8</v>
       </c>
-      <c r="L26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X26" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI26" t="n">
+      <c r="BC26" t="n">
         <v>32</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD26" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G27" t="n">
-        <v>990</v>
+        <v>5.1</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="I27" t="n">
-        <v>990</v>
+        <v>1.85</v>
       </c>
       <c r="J27" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>2.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.66</v>
       </c>
       <c r="S27" t="n">
-        <v>1.05</v>
+        <v>2.28</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U27" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G28" t="n">
-        <v>990</v>
+        <v>2.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I28" t="n">
-        <v>990</v>
+        <v>3.85</v>
       </c>
       <c r="J28" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X28" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH28" t="n">
         <v>950</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,179 +5986,179 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Juventus B</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>US Pianese</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G29" t="n">
-        <v>990</v>
+        <v>1.44</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="I29" t="n">
-        <v>990</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S29" t="n">
-        <v>1.41</v>
+        <v>2.24</v>
       </c>
       <c r="T29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.11</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="H30" t="n">
         <v>1.04</v>
@@ -6201,7 +6201,7 @@
         <v>110</v>
       </c>
       <c r="J30" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K30" t="n">
         <v>950</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>1.45</v>
+        <v>990</v>
       </c>
       <c r="H31" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>8.800000000000001</v>
+        <v>990</v>
       </c>
       <c r="J31" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="R31" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>2.22</v>
+        <v>1.05</v>
       </c>
       <c r="T31" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU31" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC31" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD31" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
@@ -6563,33 +6563,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1.04</v>
       </c>
       <c r="G32" t="n">
-        <v>160</v>
+        <v>990</v>
       </c>
       <c r="H32" t="n">
         <v>1.04</v>
       </c>
       <c r="I32" t="n">
-        <v>160</v>
+        <v>990</v>
       </c>
       <c r="J32" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K32" t="n">
         <v>950</v>
@@ -6604,25 +6604,25 @@
         <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P32" t="n">
         <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Juventus B</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>1.69</v>
+        <v>990</v>
       </c>
       <c r="H33" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I33" t="n">
-        <v>4.3</v>
+        <v>990</v>
       </c>
       <c r="J33" t="n">
-        <v>5.9</v>
+        <v>1.05</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>14</v>
+        <v>1.25</v>
       </c>
       <c r="O33" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="P33" t="n">
-        <v>5.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="R33" t="n">
-        <v>2.76</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="T33" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="AR33" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AS33" t="n">
-        <v>80</v>
+        <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AU33" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AV33" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AW33" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AY33" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA33" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,378 +6951,766 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Paso Locomotive FC</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
-        <v>2.56</v>
+        <v>990</v>
       </c>
       <c r="H34" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>3.25</v>
+        <v>990</v>
       </c>
       <c r="J34" t="n">
-        <v>3.3</v>
+        <v>1.06</v>
       </c>
       <c r="K34" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L34" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>4.3</v>
+        <v>1.26</v>
       </c>
       <c r="O34" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P34" t="n">
-        <v>2.14</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.73</v>
+        <v>1.02</v>
       </c>
       <c r="R34" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>2.86</v>
+        <v>1.53</v>
       </c>
       <c r="T34" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR34" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
         <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
         <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-05 11:04:01</t>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K35" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>32</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>48</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:13:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:13:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>23:15:00</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>CD Olimpia</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>CD Marathon</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>1.04</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G37" t="n">
         <v>990</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H37" t="n">
         <v>1.04</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I37" t="n">
         <v>990</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J37" t="n">
         <v>1.04</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K37" t="n">
         <v>950</v>
       </c>
-      <c r="L35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N35" t="n">
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
         <v>1.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O37" t="n">
         <v>1.23</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P37" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q37" t="n">
         <v>1.22</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R37" t="n">
         <v>1.18</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S37" t="n">
         <v>1.24</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T37" t="n">
         <v>1.11</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U37" t="n">
         <v>1.11</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH35" t="inlineStr">
-        <is>
-          <t>2026-05-05 11:04:01</t>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:13:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -784,16 +784,16 @@
         <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>3.15</v>
@@ -802,25 +802,25 @@
         <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
         <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
         <v>11.5</v>
@@ -829,13 +829,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -844,37 +844,37 @@
         <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
         <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
         <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -898,13 +898,13 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
         <v>19</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
         <v>30</v>
@@ -913,14 +913,14 @@
         <v>34</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -966,10 +966,10 @@
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -981,19 +981,19 @@
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R3" t="n">
         <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
         <v>2.18</v>
@@ -1002,7 +1002,7 @@
         <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1011,7 +1011,7 @@
         <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AA3" t="n">
         <v>140</v>
@@ -1032,7 +1032,7 @@
         <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3" t="n">
         <v>21</v>
@@ -1044,16 +1044,16 @@
         <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO3" t="n">
         <v>65</v>
@@ -1062,10 +1062,10 @@
         <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
         <v>42</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
@@ -1181,16 +1181,16 @@
         <v>1.57</v>
       </c>
       <c r="R4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.65</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>2.42</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.23</v>
@@ -1217,7 +1217,7 @@
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>60</v>
@@ -1238,7 +1238,7 @@
         <v>19</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AL4" t="n">
         <v>40</v>
@@ -1271,7 +1271,7 @@
         <v>9.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
         <v>28</v>
@@ -1286,7 +1286,7 @@
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -1369,28 +1369,28 @@
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="Q5" t="n">
         <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
         <v>1.49</v>
       </c>
       <c r="U5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V5" t="n">
         <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X5" t="n">
         <v>30</v>
@@ -1480,10 +1480,10 @@
         <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
         <v>18</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>2.68</v>
       </c>
       <c r="I6" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
@@ -1557,13 +1557,13 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
         <v>1.82</v>
@@ -1575,13 +1575,13 @@
         <v>3.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U6" t="n">
         <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.54</v>
@@ -1590,10 +1590,10 @@
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
         <v>44</v>
@@ -1605,10 +1605,10 @@
         <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
         <v>21</v>
@@ -1617,7 +1617,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
         <v>48</v>
@@ -1629,16 +1629,16 @@
         <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
         <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP6" t="n">
         <v>13.5</v>
@@ -1650,22 +1650,22 @@
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY6" t="n">
         <v>10</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG6" t="n">
         <v>19.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
         <v>2.06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
@@ -1757,7 +1757,7 @@
         <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
         <v>1.79</v>
@@ -1769,7 +1769,7 @@
         <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
         <v>2.08</v>
@@ -1778,7 +1778,7 @@
         <v>1.74</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
         <v>2.72</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="I9" t="n">
         <v>3.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K9" t="n">
         <v>4.7</v>
@@ -2139,19 +2139,19 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
         <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -2163,22 +2163,22 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
         <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
         <v>970</v>
@@ -2187,98 +2187,98 @@
         <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>5.1</v>
       </c>
-      <c r="AV9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>1.26</v>
       </c>
       <c r="I10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J10" t="n">
         <v>4.5</v>
@@ -2327,28 +2327,28 @@
         <v>16</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2357,7 +2357,7 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W10" t="n">
         <v>1.01</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -2518,7 +2518,7 @@
         <v>2.74</v>
       </c>
       <c r="K11" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
         <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -2700,97 +2700,97 @@
         <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
         <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="T12" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U12" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
         <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE12" t="n">
         <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ12" t="n">
         <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>34</v>
@@ -2799,37 +2799,37 @@
         <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AP12" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
         <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
         <v>8.800000000000001</v>
@@ -2838,29 +2838,29 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="G13" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Q13" t="n">
         <v>1.98</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
         <v>970</v>
@@ -2954,7 +2954,7 @@
         <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
@@ -2978,7 +2978,7 @@
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
         <v>44</v>
@@ -2987,10 +2987,10 @@
         <v>36</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
         <v>32</v>
@@ -3002,59 +3002,59 @@
         <v>9.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
         <v>6</v>
       </c>
       <c r="AV13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX13" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AY13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA13" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BB13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC13" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB13" t="n">
+      <c r="BD13" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G15" t="n">
         <v>990</v>
@@ -3312,7 +3312,7 @@
         <v>1.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>1.23</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>3.6</v>
@@ -3491,7 +3491,7 @@
         <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
@@ -3506,13 +3506,13 @@
         <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>1.68</v>
@@ -3521,10 +3521,10 @@
         <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -3545,10 +3545,10 @@
         <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF16" t="n">
         <v>18</v>
@@ -3557,16 +3557,16 @@
         <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
         <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AL16" t="n">
         <v>42</v>
@@ -3575,7 +3575,7 @@
         <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AO16" t="n">
         <v>44</v>
@@ -3590,7 +3590,7 @@
         <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AT16" t="n">
         <v>8.199999999999999</v>
@@ -3602,7 +3602,7 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -3614,7 +3614,7 @@
         <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BB16" t="n">
         <v>19.5</v>
@@ -3623,20 +3623,20 @@
         <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BF16" t="n">
         <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
         <v>8.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K17" t="n">
         <v>5.4</v>
@@ -3706,7 +3706,7 @@
         <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
         <v>1.72</v>
@@ -3715,7 +3715,7 @@
         <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
         <v>2.72</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
         <v>4.5</v>
@@ -3891,7 +3891,7 @@
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1.75</v>
@@ -3900,7 +3900,7 @@
         <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
         <v>1.75</v>
@@ -3912,13 +3912,13 @@
         <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X18" t="n">
         <v>21</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
         <v>50</v>
@@ -3927,10 +3927,10 @@
         <v>150</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>25</v>
@@ -3939,13 +3939,13 @@
         <v>80</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI18" t="n">
         <v>75</v>
@@ -3954,7 +3954,7 @@
         <v>970</v>
       </c>
       <c r="AK18" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AL18" t="n">
         <v>40</v>
@@ -3963,7 +3963,7 @@
         <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AO18" t="n">
         <v>80</v>
@@ -3984,7 +3984,7 @@
         <v>7.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
         <v>1.01</v>
@@ -3999,7 +3999,7 @@
         <v>7.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
         <v>1.01</v>
@@ -4011,20 +4011,20 @@
         <v>12</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
         <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG18" t="n">
         <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
         <v>6</v>
@@ -4070,7 +4070,7 @@
         <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.32</v>
@@ -4079,7 +4079,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
@@ -4088,16 +4088,16 @@
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R19" t="n">
         <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U19" t="n">
         <v>2</v>
@@ -4106,7 +4106,7 @@
         <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -4157,68 +4157,68 @@
         <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
         <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX19" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AY19" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB19" t="n">
         <v>12</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="BF19" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="G20" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="H20" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
         <v>4.3</v>
@@ -4279,10 +4279,10 @@
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R20" t="n">
         <v>1.43</v>
@@ -4291,16 +4291,16 @@
         <v>2.84</v>
       </c>
       <c r="T20" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U20" t="n">
         <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
         <v>22</v>
@@ -4327,7 +4327,7 @@
         <v>36</v>
       </c>
       <c r="AF20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
         <v>970</v>
@@ -4339,10 +4339,10 @@
         <v>46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK20" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL20" t="n">
         <v>40</v>
@@ -4354,65 +4354,65 @@
         <v>22</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AR20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV20" t="n">
         <v>4</v>
       </c>
-      <c r="AS20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AW20" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.3</v>
+        <v>2.34</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.3</v>
+        <v>2.32</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.95</v>
+        <v>2.78</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G21" t="n">
         <v>1.7</v>
@@ -4476,7 +4476,7 @@
         <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R21" t="n">
         <v>1.5</v>
@@ -4497,7 +4497,7 @@
         <v>2.42</v>
       </c>
       <c r="X21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y21" t="n">
         <v>950</v>
@@ -4506,16 +4506,16 @@
         <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB21" t="n">
         <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
         <v>70</v>
@@ -4527,28 +4527,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH21" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
         <v>29</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO21" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP21" t="n">
         <v>18.5</v>
@@ -4557,56 +4557,56 @@
         <v>20</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU21" t="n">
         <v>9.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BB21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC21" t="n">
         <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BF21" t="n">
         <v>7.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.4</v>
+        <v>46</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G22" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J22" t="n">
         <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.31</v>
@@ -4664,10 +4664,10 @@
         <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
         <v>1.75</v>
@@ -4679,7 +4679,7 @@
         <v>2.92</v>
       </c>
       <c r="T22" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U22" t="n">
         <v>2.3</v>
@@ -4688,31 +4688,31 @@
         <v>1.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X22" t="n">
         <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
         <v>970</v>
       </c>
       <c r="AA22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB22" t="n">
         <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF22" t="n">
         <v>24</v>
@@ -4727,10 +4727,10 @@
         <v>38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL22" t="n">
         <v>40</v>
@@ -4742,19 +4742,19 @@
         <v>26</v>
       </c>
       <c r="AO22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ22" t="n">
         <v>10.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT22" t="n">
         <v>11</v>
@@ -4763,44 +4763,44 @@
         <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I23" t="n">
         <v>4.9</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
         <v>3.8</v>
@@ -4864,25 +4864,25 @@
         <v>1.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
         <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T23" t="n">
         <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="V23" t="n">
         <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X23" t="n">
         <v>14</v>
@@ -4945,7 +4945,7 @@
         <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AS23" t="n">
         <v>4.9</v>
@@ -4975,13 +4975,13 @@
         <v>4.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>20</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
         <v>4.9</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H24" t="n">
         <v>2.2</v>
       </c>
       <c r="I24" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
         <v>1.34</v>
@@ -5049,34 +5049,34 @@
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T24" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U24" t="n">
         <v>2.32</v>
       </c>
       <c r="V24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X24" t="n">
         <v>22</v>
@@ -5133,7 +5133,7 @@
         <v>17</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>10</v>
@@ -5184,11 +5184,11 @@
         <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G25" t="n">
         <v>1.52</v>
@@ -5228,10 +5228,10 @@
         <v>6.8</v>
       </c>
       <c r="I25" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J25" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="K25" t="n">
         <v>5.9</v>
@@ -5249,7 +5249,7 @@
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
         <v>1.46</v>
@@ -5261,10 +5261,10 @@
         <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V25" t="n">
         <v>1.12</v>
@@ -5324,16 +5324,16 @@
         <v>6</v>
       </c>
       <c r="AO25" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP25" t="n">
         <v>4.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS25" t="n">
         <v>5</v>
@@ -5351,25 +5351,25 @@
         <v>4.9</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD25" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.9</v>
       </c>
       <c r="BE25" t="n">
         <v>4.9</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G26" t="n">
         <v>3.25</v>
@@ -5425,7 +5425,7 @@
         <v>2.84</v>
       </c>
       <c r="J26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>3.4</v>
@@ -5437,13 +5437,13 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O26" t="n">
         <v>1.41</v>
       </c>
       <c r="P26" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q26" t="n">
         <v>2.2</v>
@@ -5455,22 +5455,22 @@
         <v>4.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U26" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V26" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X26" t="n">
         <v>13</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z26" t="n">
         <v>18.5</v>
@@ -5482,7 +5482,7 @@
         <v>12.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD26" t="n">
         <v>14.5</v>
@@ -5506,7 +5506,7 @@
         <v>70</v>
       </c>
       <c r="AK26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL26" t="n">
         <v>70</v>
@@ -5527,22 +5527,22 @@
         <v>8</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS26" t="n">
-        <v>26</v>
+        <v>4.9</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU26" t="n">
         <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX26" t="n">
         <v>17</v>
@@ -5551,32 +5551,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>4.9</v>
       </c>
       <c r="BA26" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC26" t="n">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="H27" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="I27" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>1.22</v>
@@ -5631,34 +5631,34 @@
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O27" t="n">
         <v>1.17</v>
       </c>
       <c r="P27" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R27" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S27" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T27" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U27" t="n">
         <v>2.48</v>
       </c>
       <c r="V27" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="W27" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
         <v>34</v>
@@ -5667,25 +5667,25 @@
         <v>16.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB27" t="n">
         <v>29</v>
       </c>
       <c r="AC27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
         <v>13</v>
       </c>
       <c r="AE27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG27" t="n">
         <v>23</v>
@@ -5700,7 +5700,7 @@
         <v>110</v>
       </c>
       <c r="AK27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL27" t="n">
         <v>55</v>
@@ -5712,65 +5712,65 @@
         <v>40</v>
       </c>
       <c r="AO27" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="AQ27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR27" t="n">
         <v>10</v>
       </c>
-      <c r="AR27" t="n">
-        <v>12</v>
-      </c>
       <c r="AS27" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AV27" t="n">
         <v>8</v>
       </c>
       <c r="AW27" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AX27" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA27" t="n">
         <v>18.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -5801,55 +5801,55 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="G28" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H28" t="n">
         <v>3.35</v>
       </c>
       <c r="I28" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L28" t="n">
         <v>1.36</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U28" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
         <v>1.71</v>
@@ -5861,10 +5861,10 @@
         <v>970</v>
       </c>
       <c r="Z28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA28" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB28" t="n">
         <v>970</v>
@@ -5909,62 +5909,62 @@
         <v>60</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AR28" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AT28" t="n">
         <v>6.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AY28" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -5998,58 +5998,58 @@
         <v>1.39</v>
       </c>
       <c r="G29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H29" t="n">
         <v>7.6</v>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>5.3</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L29" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M29" t="n">
         <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
         <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R29" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="S29" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U29" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V29" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W29" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y29" t="n">
         <v>42</v>
@@ -6064,7 +6064,7 @@
         <v>13.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD29" t="n">
         <v>36</v>
@@ -6076,7 +6076,7 @@
         <v>12</v>
       </c>
       <c r="AG29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH29" t="n">
         <v>26</v>
@@ -6085,7 +6085,7 @@
         <v>95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK29" t="n">
         <v>16</v>
@@ -6097,22 +6097,22 @@
         <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AO29" t="n">
         <v>120</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT29" t="n">
         <v>10</v>
@@ -6121,10 +6121,10 @@
         <v>11.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX29" t="n">
         <v>9.199999999999999</v>
@@ -6133,10 +6133,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB29" t="n">
         <v>11.5</v>
@@ -6148,17 +6148,17 @@
         <v>21</v>
       </c>
       <c r="BE29" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG29" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -6189,112 +6189,112 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G30" t="n">
-        <v>110</v>
+        <v>2.36</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I30" t="n">
-        <v>110</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S30" t="n">
-        <v>1.47</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP30" t="n">
         <v>1.03</v>
@@ -6345,14 +6345,14 @@
         <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -6383,145 +6383,145 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>990</v>
+        <v>3.5</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="I31" t="n">
-        <v>990</v>
+        <v>2.72</v>
       </c>
       <c r="J31" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AS31" t="n">
         <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA31" t="n">
         <v>1.03</v>
@@ -6539,14 +6539,14 @@
         <v>1.03</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -6577,46 +6577,46 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>990</v>
+        <v>2.48</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I32" t="n">
-        <v>990</v>
+        <v>4.9</v>
       </c>
       <c r="J32" t="n">
-        <v>1.06</v>
+        <v>2.96</v>
       </c>
       <c r="K32" t="n">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M32" t="n">
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -6625,10 +6625,10 @@
         <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -6771,46 +6771,46 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="G33" t="n">
-        <v>990</v>
+        <v>2.56</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I33" t="n">
-        <v>990</v>
+        <v>5.2</v>
       </c>
       <c r="J33" t="n">
-        <v>1.05</v>
+        <v>2.94</v>
       </c>
       <c r="K33" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="O33" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>1.41</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
         <v>1.11</v>
@@ -6819,52 +6819,52 @@
         <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE33" t="n">
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI33" t="n">
         <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL33" t="n">
         <v>1000</v>
@@ -6882,7 +6882,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AR33" t="n">
         <v>1.03</v>
@@ -6891,22 +6891,22 @@
         <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW33" t="n">
         <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ33" t="n">
         <v>1.03</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
@@ -7004,7 +7004,7 @@
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G35" t="n">
         <v>1.67</v>
       </c>
       <c r="H35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K35" t="n">
         <v>5.9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>6</v>
       </c>
       <c r="L35" t="n">
         <v>1.15</v>
@@ -7192,13 +7192,13 @@
         <v>5.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R35" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="S35" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T35" t="n">
         <v>1.3</v>
@@ -7207,13 +7207,13 @@
         <v>4.2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W35" t="n">
         <v>2.5</v>
       </c>
       <c r="X35" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Y35" t="n">
         <v>55</v>
@@ -7225,16 +7225,16 @@
         <v>110</v>
       </c>
       <c r="AB35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AC35" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AD35" t="n">
         <v>22</v>
       </c>
       <c r="AE35" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF35" t="n">
         <v>23</v>
@@ -7246,43 +7246,43 @@
         <v>16</v>
       </c>
       <c r="AI35" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AJ35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK35" t="n">
         <v>14.5</v>
       </c>
       <c r="AL35" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AM35" t="n">
         <v>32</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AO35" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AQ35" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AR35" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS35" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AT35" t="n">
         <v>28</v>
       </c>
       <c r="AU35" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AV35" t="n">
         <v>20</v>
@@ -7291,7 +7291,7 @@
         <v>34</v>
       </c>
       <c r="AX35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY35" t="n">
         <v>12</v>
@@ -7300,7 +7300,7 @@
         <v>15</v>
       </c>
       <c r="BA35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB35" t="n">
         <v>24</v>
@@ -7315,14 +7315,14 @@
         <v>30</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BG35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
         <v>1.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-05 13:13:41</t>
+          <t>2026-05-05 15:23:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,28 +757,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
         <v>4.1</v>
@@ -787,19 +787,19 @@
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
         <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
         <v>2.28</v>
@@ -808,7 +808,7 @@
         <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X2" t="n">
         <v>15</v>
@@ -826,7 +826,7 @@
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
@@ -859,10 +859,10 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP2" t="n">
         <v>14</v>
@@ -871,7 +871,7 @@
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
         <v>30</v>
@@ -886,7 +886,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -904,7 +904,7 @@
         <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
         <v>30</v>
@@ -916,11 +916,11 @@
         <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H4" t="n">
         <v>5.1</v>
@@ -1175,13 +1175,13 @@
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
         <v>2.9</v>
@@ -1196,7 +1196,7 @@
         <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
@@ -1226,7 +1226,7 @@
         <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
@@ -1253,7 +1253,7 @@
         <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
         <v>1.73</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
         <v>5.3</v>
@@ -1369,7 +1369,7 @@
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q5" t="n">
         <v>1.57</v>
@@ -1384,7 +1384,7 @@
         <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
         <v>1.23</v>
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
         <v>110</v>
       </c>
       <c r="AA5" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
         <v>12.5</v>
@@ -1417,10 +1417,10 @@
         <v>60</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
@@ -1432,7 +1432,7 @@
         <v>19</v>
       </c>
       <c r="AK5" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
         <v>40</v>
@@ -1444,7 +1444,7 @@
         <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP5" t="n">
         <v>18</v>
@@ -1468,13 +1468,13 @@
         <v>17.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
         <v>15.5</v>
@@ -1495,14 +1495,14 @@
         <v>32</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
         <v>25</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
         <v>2.28</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.23</v>
@@ -1569,22 +1569,22 @@
         <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T6" t="n">
         <v>1.49</v>
       </c>
       <c r="U6" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X6" t="n">
         <v>30</v>
@@ -1593,7 +1593,7 @@
         <v>23</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA6" t="n">
         <v>55</v>
@@ -1611,10 +1611,10 @@
         <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>14.5</v>
@@ -1635,34 +1635,34 @@
         <v>50</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO6" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>28</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU6" t="n">
         <v>9.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
         <v>16.5</v>
@@ -1674,10 +1674,10 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC6" t="n">
         <v>17</v>
@@ -1689,14 +1689,14 @@
         <v>26</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6" t="n">
         <v>15</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1736,13 +1736,13 @@
         <v>7.2</v>
       </c>
       <c r="I7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7" t="n">
         <v>4.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.32</v>
@@ -1853,7 +1853,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW7" t="n">
         <v>5.9</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="G8" t="n">
         <v>990</v>
@@ -2080,11 +2080,11 @@
         <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.3</v>
@@ -2157,7 +2157,7 @@
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
         <v>2.14</v>
@@ -2184,7 +2184,7 @@
         <v>14.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
         <v>15</v>
@@ -2232,7 +2232,7 @@
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2244,7 +2244,7 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
         <v>14</v>
@@ -2256,19 +2256,19 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>30</v>
+        <v>4.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
         <v>19</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
         <v>2.92</v>
@@ -2348,10 +2348,10 @@
         <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
         <v>2.26</v>
@@ -2411,7 +2411,7 @@
         <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>26</v>
@@ -2438,7 +2438,7 @@
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
         <v>15.5</v>
@@ -2450,7 +2450,7 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
         <v>29</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="G12" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.32</v>
@@ -2721,16 +2721,16 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
         <v>1.26</v>
@@ -2739,7 +2739,7 @@
         <v>2.82</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
         <v>1.11</v>
@@ -2748,16 +2748,16 @@
         <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
         <v>18.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2775,7 +2775,7 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG12" t="n">
         <v>15.5</v>
@@ -2787,10 +2787,10 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -2805,31 +2805,31 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.87</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
         <v>5.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY12" t="n">
         <v>7.2</v>
@@ -2838,29 +2838,29 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BB12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
         <v>2.72</v>
       </c>
       <c r="H13" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="I13" t="n">
         <v>3.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2.72</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.36</v>
@@ -2945,7 +2945,7 @@
         <v>1.58</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
         <v>970</v>
@@ -3005,7 +3005,7 @@
         <v>4.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AS13" t="n">
         <v>4.3</v>
@@ -3014,7 +3014,7 @@
         <v>4.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AV13" t="n">
         <v>4.8</v>
@@ -3035,7 +3035,7 @@
         <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.94</v>
+        <v>4.1</v>
       </c>
       <c r="BC13" t="n">
         <v>4</v>
@@ -3044,7 +3044,7 @@
         <v>6</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="BF13" t="n">
         <v>5.7</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -3091,55 +3091,55 @@
         <v>4.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I14" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
@@ -3193,19 +3193,19 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14" t="n">
         <v>6.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
         <v>5.6</v>
@@ -3214,41 +3214,41 @@
         <v>7.4</v>
       </c>
       <c r="AW14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>1.85</v>
       </c>
-      <c r="AX14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BA14" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I15" t="n">
         <v>1.56</v>
@@ -3294,7 +3294,7 @@
         <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L15" t="n">
         <v>1.27</v>
@@ -3303,7 +3303,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
@@ -3312,19 +3312,19 @@
         <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>2.78</v>
@@ -3435,14 +3435,14 @@
         <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="G16" t="n">
-        <v>2.76</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="I16" t="n">
-        <v>970</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,37 +3497,37 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.08</v>
+        <v>2.44</v>
       </c>
       <c r="O16" t="n">
         <v>1.02</v>
       </c>
       <c r="P16" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="Q16" t="n">
         <v>2.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y16" t="n">
         <v>1000</v>
@@ -3584,49 +3584,49 @@
         <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -3682,37 +3682,37 @@
         <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="R17" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="T17" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="V17" t="n">
         <v>1.4</v>
@@ -3721,13 +3721,13 @@
         <v>1.73</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA17" t="n">
         <v>65</v>
@@ -3736,7 +3736,7 @@
         <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
         <v>17</v>
@@ -3745,10 +3745,10 @@
         <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
         <v>17.5</v>
@@ -3766,13 +3766,13 @@
         <v>34</v>
       </c>
       <c r="AM17" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN17" t="n">
         <v>13.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
         <v>18</v>
@@ -3784,10 +3784,10 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU17" t="n">
         <v>7.6</v>
@@ -3796,7 +3796,7 @@
         <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
         <v>13</v>
@@ -3808,7 +3808,7 @@
         <v>11.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
         <v>21</v>
@@ -3817,10 +3817,10 @@
         <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
         <v>9.800000000000001</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J18" t="n">
         <v>2.96</v>
@@ -3894,7 +3894,7 @@
         <v>1.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>1.31</v>
@@ -3909,7 +3909,7 @@
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
         <v>1.6</v>
@@ -3936,7 +3936,7 @@
         <v>970</v>
       </c>
       <c r="AE18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF18" t="n">
         <v>970</v>
@@ -3954,7 +3954,7 @@
         <v>44</v>
       </c>
       <c r="AK18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
         <v>50</v>
@@ -3963,10 +3963,10 @@
         <v>120</v>
       </c>
       <c r="AN18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP18" t="n">
         <v>9.4</v>
@@ -3993,7 +3993,7 @@
         <v>4.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY18" t="n">
         <v>3.75</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G19" t="n">
         <v>990</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>190</v>
+        <v>870</v>
       </c>
       <c r="J19" t="n">
         <v>1.09</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="G20" t="n">
         <v>990</v>
       </c>
       <c r="H20" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="I20" t="n">
         <v>990</v>
@@ -4264,7 +4264,7 @@
         <v>1.09</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4282,13 +4282,13 @@
         <v>1.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R20" t="n">
         <v>1.23</v>
       </c>
       <c r="S20" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -4303,7 +4303,7 @@
         <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y20" t="n">
         <v>1000</v>
@@ -4360,49 +4360,49 @@
         <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -4646,13 +4646,13 @@
         <v>3.95</v>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
         <v>1.34</v>
@@ -4685,7 +4685,7 @@
         <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
         <v>1.83</v>
@@ -4694,22 +4694,22 @@
         <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA22" t="n">
         <v>110</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
         <v>70</v>
@@ -4718,28 +4718,28 @@
         <v>14.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK22" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
         <v>150</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
         <v>85</v>
@@ -4754,7 +4754,7 @@
         <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AT22" t="n">
         <v>7</v>
@@ -4766,7 +4766,7 @@
         <v>14.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX22" t="n">
         <v>10.5</v>
@@ -4778,7 +4778,7 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB22" t="n">
         <v>22</v>
@@ -4787,20 +4787,20 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>2.64</v>
       </c>
       <c r="G23" t="n">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="H23" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="I23" t="n">
         <v>2.82</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
         <v>1.31</v>
@@ -4882,7 +4882,7 @@
         <v>1.55</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="X23" t="n">
         <v>21</v>
@@ -4909,7 +4909,7 @@
         <v>29</v>
       </c>
       <c r="AF23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG23" t="n">
         <v>970</v>
@@ -4921,7 +4921,7 @@
         <v>38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK23" t="n">
         <v>32</v>
@@ -4933,22 +4933,22 @@
         <v>85</v>
       </c>
       <c r="AN23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO23" t="n">
         <v>21</v>
       </c>
       <c r="AP23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23" t="n">
         <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT23" t="n">
         <v>11</v>
@@ -4957,44 +4957,44 @@
         <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX23" t="n">
         <v>6</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.9</v>
       </c>
       <c r="AY23" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD23" t="n">
         <v>6.8</v>
       </c>
-      <c r="BD23" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE23" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG23" t="n">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G24" t="n">
         <v>1.7</v>
@@ -5034,7 +5034,7 @@
         <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>4.3</v>
@@ -5067,19 +5067,19 @@
         <v>2.72</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U24" t="n">
         <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W24" t="n">
         <v>2.42</v>
       </c>
       <c r="X24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y24" t="n">
         <v>950</v>
@@ -5112,7 +5112,7 @@
         <v>19.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
         <v>17</v>
@@ -5124,28 +5124,28 @@
         <v>29</v>
       </c>
       <c r="AM24" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO24" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU24" t="n">
         <v>9.4</v>
@@ -5154,19 +5154,19 @@
         <v>19</v>
       </c>
       <c r="AW24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ24" t="n">
         <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB24" t="n">
         <v>15</v>
@@ -5178,17 +5178,17 @@
         <v>25</v>
       </c>
       <c r="BE24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BF24" t="n">
         <v>7.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G25" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H25" t="n">
         <v>2.84</v>
@@ -5234,7 +5234,7 @@
         <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>1.29</v>
@@ -5258,28 +5258,28 @@
         <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T25" t="n">
         <v>1.64</v>
       </c>
       <c r="U25" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V25" t="n">
         <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X25" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="Y25" t="n">
         <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
         <v>50</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="AF25" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG25" t="n">
         <v>970</v>
@@ -5327,62 +5327,62 @@
         <v>30</v>
       </c>
       <c r="AP25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AR25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.2</v>
+        <v>2.78</v>
       </c>
       <c r="AT25" t="n">
         <v>9.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY25" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="BB25" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="BF25" t="n">
         <v>4.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -5527,10 +5527,10 @@
         <v>15.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AT26" t="n">
         <v>4.7</v>
@@ -5566,7 +5566,7 @@
         <v>6.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="BF26" t="n">
         <v>4.7</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
         <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X27" t="n">
         <v>21</v>
@@ -5715,62 +5715,62 @@
         <v>44</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.1</v>
+        <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU27" t="n">
         <v>7.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW27" t="n">
         <v>28</v>
       </c>
       <c r="AX27" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY27" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.1</v>
+        <v>20</v>
       </c>
       <c r="BC27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE27" t="n">
         <v>4</v>
       </c>
-      <c r="BD27" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BF27" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
         <v>2.2</v>
       </c>
       <c r="X28" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="Y28" t="n">
         <v>21</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>3.75</v>
       </c>
       <c r="L29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>1.41</v>
       </c>
       <c r="G30" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H30" t="n">
         <v>7</v>
@@ -6210,7 +6210,7 @@
         <v>1.23</v>
       </c>
       <c r="M30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N30" t="n">
         <v>5.7</v>
@@ -6231,19 +6231,19 @@
         <v>2.3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U30" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V30" t="n">
         <v>1.11</v>
       </c>
       <c r="W30" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y30" t="n">
         <v>950</v>
@@ -6297,10 +6297,10 @@
         <v>110</v>
       </c>
       <c r="AP30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>5</v>
       </c>
       <c r="AR30" t="n">
         <v>4.8</v>
@@ -6327,7 +6327,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BA30" t="n">
         <v>4.9</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -6386,13 +6386,13 @@
         <v>3.35</v>
       </c>
       <c r="G31" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H31" t="n">
         <v>2.22</v>
       </c>
       <c r="I31" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>3.65</v>
@@ -6401,52 +6401,52 @@
         <v>3.95</v>
       </c>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.24</v>
       </c>
       <c r="P31" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
         <v>1.73</v>
       </c>
       <c r="R31" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U31" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W31" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X31" t="n">
         <v>22</v>
       </c>
       <c r="Y31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA31" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB31" t="n">
         <v>18</v>
@@ -6458,7 +6458,7 @@
         <v>13</v>
       </c>
       <c r="AE31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF31" t="n">
         <v>29</v>
@@ -6488,7 +6488,7 @@
         <v>34</v>
       </c>
       <c r="AO31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP31" t="n">
         <v>15.5</v>
@@ -6500,7 +6500,7 @@
         <v>13.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT31" t="n">
         <v>13</v>
@@ -6524,19 +6524,19 @@
         <v>13.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF31" t="n">
         <v>21</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="Y32" t="n">
         <v>10</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.47</v>
       </c>
       <c r="G33" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H33" t="n">
         <v>6.4</v>
@@ -6795,7 +6795,7 @@
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O33" t="n">
         <v>1.19</v>
@@ -6804,16 +6804,16 @@
         <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R33" t="n">
         <v>1.6</v>
       </c>
       <c r="S33" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T33" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U33" t="n">
         <v>2.24</v>
@@ -6876,7 +6876,7 @@
         <v>7</v>
       </c>
       <c r="AO33" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP33" t="n">
         <v>18.5</v>
@@ -6885,19 +6885,19 @@
         <v>21</v>
       </c>
       <c r="AR33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS33" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>4.3</v>
       </c>
       <c r="AT33" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU33" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV33" t="n">
-        <v>19</v>
+        <v>4.2</v>
       </c>
       <c r="AW33" t="n">
         <v>4.2</v>
@@ -6906,7 +6906,7 @@
         <v>8</v>
       </c>
       <c r="AY33" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ33" t="n">
         <v>15</v>
@@ -6918,7 +6918,7 @@
         <v>10</v>
       </c>
       <c r="BC33" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD33" t="n">
         <v>20</v>
@@ -6927,14 +6927,14 @@
         <v>4.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG33" t="n">
         <v>4.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -6968,13 +6968,13 @@
         <v>3.3</v>
       </c>
       <c r="G34" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H34" t="n">
         <v>2.34</v>
       </c>
       <c r="I34" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J34" t="n">
         <v>3.05</v>
@@ -6989,7 +6989,7 @@
         <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O34" t="n">
         <v>1.41</v>
@@ -7013,7 +7013,7 @@
         <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W34" t="n">
         <v>1.37</v>
@@ -7025,7 +7025,7 @@
         <v>10.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA34" t="n">
         <v>38</v>
@@ -7037,10 +7037,10 @@
         <v>7.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE34" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF34" t="n">
         <v>25</v>
@@ -7052,7 +7052,7 @@
         <v>23</v>
       </c>
       <c r="AI34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ34" t="n">
         <v>70</v>
@@ -7070,7 +7070,7 @@
         <v>55</v>
       </c>
       <c r="AO34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP34" t="n">
         <v>9.199999999999999</v>
@@ -7082,7 +7082,7 @@
         <v>12.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT34" t="n">
         <v>8.800000000000001</v>
@@ -7094,7 +7094,7 @@
         <v>10.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX34" t="n">
         <v>17</v>
@@ -7103,32 +7103,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="G35" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="I35" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J35" t="n">
         <v>4.1</v>
@@ -7195,7 +7195,7 @@
         <v>1.51</v>
       </c>
       <c r="R35" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S35" t="n">
         <v>2.28</v>
@@ -7204,13 +7204,13 @@
         <v>1.56</v>
       </c>
       <c r="U35" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V35" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X35" t="n">
         <v>34</v>
@@ -7267,7 +7267,7 @@
         <v>8</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ35" t="n">
         <v>11.5</v>
@@ -7276,7 +7276,7 @@
         <v>10</v>
       </c>
       <c r="AS35" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT35" t="n">
         <v>20</v>
@@ -7288,13 +7288,13 @@
         <v>8</v>
       </c>
       <c r="AW35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY35" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>4.3</v>
       </c>
       <c r="AZ35" t="n">
         <v>12</v>
@@ -7306,23 +7306,23 @@
         <v>4.8</v>
       </c>
       <c r="BC35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD35" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD35" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE35" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG35" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7413,7 @@
         <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA36" t="n">
         <v>75</v>
@@ -7443,13 +7443,13 @@
         <v>70</v>
       </c>
       <c r="AJ36" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK36" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL36" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
@@ -7461,62 +7461,62 @@
         <v>60</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AT36" t="n">
         <v>6.8</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV36" t="n">
         <v>4</v>
       </c>
       <c r="AW36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BA36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF36" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB36" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG36" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -7550,19 +7550,19 @@
         <v>2.66</v>
       </c>
       <c r="G37" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J37" t="n">
         <v>2.98</v>
       </c>
       <c r="K37" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L37" t="n">
         <v>1.53</v>
@@ -7574,7 +7574,7 @@
         <v>2.42</v>
       </c>
       <c r="O37" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P37" t="n">
         <v>1.48</v>
@@ -7592,7 +7592,7 @@
         <v>2.16</v>
       </c>
       <c r="U37" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V37" t="n">
         <v>1.45</v>
@@ -7601,7 +7601,7 @@
         <v>1.54</v>
       </c>
       <c r="X37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y37" t="n">
         <v>9.6</v>
@@ -7616,7 +7616,7 @@
         <v>8.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD37" t="n">
         <v>17.5</v>
@@ -7664,7 +7664,7 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT37" t="n">
         <v>6.4</v>
@@ -7676,7 +7676,7 @@
         <v>13</v>
       </c>
       <c r="AW37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX37" t="n">
         <v>13</v>
@@ -7688,29 +7688,29 @@
         <v>19.5</v>
       </c>
       <c r="BA37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB37" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB37" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC37" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE37" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG37" t="n">
         <v>5.2</v>
       </c>
-      <c r="BF37" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>1.53</v>
       </c>
       <c r="G38" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H38" t="n">
         <v>8.6</v>
@@ -7774,7 +7774,7 @@
         <v>1.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R38" t="n">
         <v>1.21</v>
@@ -7795,7 +7795,7 @@
         <v>2.64</v>
       </c>
       <c r="X38" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y38" t="n">
         <v>25</v>
@@ -7807,7 +7807,7 @@
         <v>550</v>
       </c>
       <c r="AB38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC38" t="n">
         <v>9.6</v>
@@ -7822,7 +7822,7 @@
         <v>8</v>
       </c>
       <c r="AG38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH38" t="n">
         <v>950</v>
@@ -7831,10 +7831,10 @@
         <v>260</v>
       </c>
       <c r="AJ38" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK38" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL38" t="n">
         <v>70</v>
@@ -7855,10 +7855,10 @@
         <v>17</v>
       </c>
       <c r="AR38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS38" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>6.8</v>
       </c>
       <c r="AT38" t="n">
         <v>4.9</v>
@@ -7867,10 +7867,10 @@
         <v>7</v>
       </c>
       <c r="AV38" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX38" t="n">
         <v>6.6</v>
@@ -7882,7 +7882,7 @@
         <v>25</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB38" t="n">
         <v>12</v>
@@ -7891,20 +7891,20 @@
         <v>16</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE38" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF38" t="n">
         <v>11.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -7935,16 +7935,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G39" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H39" t="n">
         <v>3.6</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>2.96</v>
@@ -7965,7 +7965,7 @@
         <v>1.45</v>
       </c>
       <c r="P39" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q39" t="n">
         <v>2.3</v>
@@ -7980,10 +7980,10 @@
         <v>1.94</v>
       </c>
       <c r="U39" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V39" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W39" t="n">
         <v>1.66</v>
@@ -7992,37 +7992,37 @@
         <v>11</v>
       </c>
       <c r="Y39" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AA39" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB39" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF39" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG39" t="n">
         <v>12.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI39" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ39" t="n">
         <v>40</v>
@@ -8034,13 +8034,13 @@
         <v>60</v>
       </c>
       <c r="AM39" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN39" t="n">
         <v>36</v>
       </c>
       <c r="AO39" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP39" t="n">
         <v>7.6</v>
@@ -8052,10 +8052,10 @@
         <v>19</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT39" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU39" t="n">
         <v>5.7</v>
@@ -8064,10 +8064,10 @@
         <v>12.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX39" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY39" t="n">
         <v>9.199999999999999</v>
@@ -8076,29 +8076,29 @@
         <v>15.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB39" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BC39" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.3</v>
+        <v>36</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF39" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -8141,10 +8141,10 @@
         <v>3.8</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K40" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L40" t="n">
         <v>1.59</v>
@@ -8162,7 +8162,7 @@
         <v>1.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R40" t="n">
         <v>1.13</v>
@@ -8198,10 +8198,10 @@
         <v>6.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD40" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE40" t="n">
         <v>90</v>
@@ -8222,7 +8222,7 @@
         <v>55</v>
       </c>
       <c r="AK40" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL40" t="n">
         <v>110</v>
@@ -8234,7 +8234,7 @@
         <v>70</v>
       </c>
       <c r="AO40" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP40" t="n">
         <v>6</v>
@@ -8246,7 +8246,7 @@
         <v>17</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT40" t="n">
         <v>5.5</v>
@@ -8258,7 +8258,7 @@
         <v>15</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX40" t="n">
         <v>10</v>
@@ -8267,32 +8267,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB40" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BC40" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF40" t="n">
         <v>40</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -8338,10 +8338,10 @@
         <v>5.3</v>
       </c>
       <c r="K41" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M41" t="n">
         <v>1.03</v>
@@ -8356,22 +8356,22 @@
         <v>2.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R41" t="n">
         <v>1.7</v>
       </c>
       <c r="S41" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T41" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U41" t="n">
         <v>2.16</v>
       </c>
       <c r="V41" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W41" t="n">
         <v>3.35</v>
@@ -8449,13 +8449,13 @@
         <v>11.5</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW41" t="n">
         <v>5.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY41" t="n">
         <v>9.199999999999999</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
         <v>2.18</v>
       </c>
       <c r="G42" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="H42" t="n">
         <v>3.5</v>
@@ -8529,7 +8529,7 @@
         <v>4.1</v>
       </c>
       <c r="J42" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
         <v>3.55</v>
@@ -8544,10 +8544,10 @@
         <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q42" t="n">
         <v>2.04</v>
@@ -8559,7 +8559,7 @@
         <v>3.7</v>
       </c>
       <c r="T42" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U42" t="n">
         <v>1.78</v>
@@ -8568,7 +8568,7 @@
         <v>1.33</v>
       </c>
       <c r="W42" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="X42" t="n">
         <v>14</v>
@@ -8640,7 +8640,7 @@
         <v>3.9</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AV42" t="n">
         <v>5.1</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -8714,167 +8714,167 @@
         <v>1.43</v>
       </c>
       <c r="G43" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H43" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J43" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L43" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M43" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N43" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O43" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P43" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R43" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S43" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T43" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U43" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="V43" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W43" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="X43" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y43" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z43" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD43" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF43" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AG43" t="n">
         <v>12.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI43" t="n">
         <v>200</v>
       </c>
       <c r="AJ43" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AK43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="n">
         <v>60</v>
       </c>
       <c r="AM43" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN43" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP43" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT43" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV43" t="n">
         <v>5</v>
       </c>
-      <c r="AU43" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AW43" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AX43" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AY43" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ43" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB43" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC43" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF43" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H44" t="n">
         <v>3.2</v>
@@ -8935,7 +8935,7 @@
         <v>1.3</v>
       </c>
       <c r="P44" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q44" t="n">
         <v>1.8</v>
@@ -8950,13 +8950,13 @@
         <v>1.11</v>
       </c>
       <c r="U44" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V44" t="n">
         <v>1.25</v>
       </c>
       <c r="W44" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9064,11 +9064,11 @@
         <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G45" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H45" t="n">
         <v>2.58</v>
@@ -9111,13 +9111,13 @@
         <v>2.84</v>
       </c>
       <c r="J45" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K45" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L45" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
@@ -9129,7 +9129,7 @@
         <v>1.4</v>
       </c>
       <c r="P45" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q45" t="n">
         <v>2.18</v>
@@ -9141,16 +9141,16 @@
         <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U45" t="n">
         <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W45" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X45" t="n">
         <v>13.5</v>
@@ -9165,10 +9165,10 @@
         <v>55</v>
       </c>
       <c r="AB45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC45" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD45" t="n">
         <v>14</v>
@@ -9177,7 +9177,7 @@
         <v>36</v>
       </c>
       <c r="AF45" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG45" t="n">
         <v>14</v>
@@ -9192,10 +9192,10 @@
         <v>60</v>
       </c>
       <c r="AK45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL45" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM45" t="n">
         <v>140</v>
@@ -9210,13 +9210,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ45" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR45" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT45" t="n">
         <v>8.199999999999999</v>
@@ -9240,29 +9240,29 @@
         <v>13.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB45" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC45" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF45" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BG45" t="n">
         <v>19.5</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -9308,10 +9308,10 @@
         <v>2.94</v>
       </c>
       <c r="K46" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L46" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M46" t="n">
         <v>1.08</v>
@@ -9350,7 +9350,7 @@
         <v>1000</v>
       </c>
       <c r="Y46" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z46" t="n">
         <v>36</v>
@@ -9371,10 +9371,10 @@
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG46" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH46" t="n">
         <v>26</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -9487,46 +9487,46 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G47" t="n">
-        <v>990</v>
+        <v>2.5</v>
       </c>
       <c r="H47" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I47" t="n">
-        <v>990</v>
+        <v>5.2</v>
       </c>
       <c r="J47" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L47" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M47" t="n">
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="O47" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P47" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="R47" t="n">
         <v>1.18</v>
       </c>
       <c r="S47" t="n">
-        <v>1.52</v>
+        <v>2.96</v>
       </c>
       <c r="T47" t="n">
         <v>1.11</v>
@@ -9535,10 +9535,10 @@
         <v>1.11</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9646,11 +9646,11 @@
         <v>1.01</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -9681,16 +9681,16 @@
         </is>
       </c>
       <c r="F48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G48" t="n">
         <v>1.66</v>
       </c>
-      <c r="G48" t="n">
-        <v>1.67</v>
-      </c>
       <c r="H48" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I48" t="n">
         <v>4.4</v>
-      </c>
-      <c r="I48" t="n">
-        <v>4.5</v>
       </c>
       <c r="J48" t="n">
         <v>5.8</v>
@@ -9711,34 +9711,34 @@
         <v>1.07</v>
       </c>
       <c r="P48" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R48" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="S48" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T48" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="U48" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="V48" t="n">
         <v>1.29</v>
       </c>
       <c r="W48" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X48" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Y48" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z48" t="n">
         <v>60</v>
@@ -9747,7 +9747,7 @@
         <v>110</v>
       </c>
       <c r="AB48" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AC48" t="n">
         <v>19.5</v>
@@ -9756,7 +9756,7 @@
         <v>22</v>
       </c>
       <c r="AE48" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF48" t="n">
         <v>23</v>
@@ -9765,19 +9765,19 @@
         <v>13</v>
       </c>
       <c r="AH48" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK48" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL48" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AM48" t="n">
         <v>32</v>
@@ -9789,25 +9789,25 @@
         <v>15</v>
       </c>
       <c r="AP48" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AQ48" t="n">
+        <v>44</v>
+      </c>
+      <c r="AR48" t="n">
         <v>50</v>
       </c>
-      <c r="AR48" t="n">
-        <v>55</v>
-      </c>
       <c r="AS48" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AT48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU48" t="n">
         <v>18.5</v>
       </c>
       <c r="AV48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW48" t="n">
         <v>34</v>
@@ -9825,26 +9825,26 @@
         <v>27</v>
       </c>
       <c r="BB48" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC48" t="n">
         <v>14</v>
       </c>
       <c r="BD48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BE48" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF48" t="n">
         <v>3.7</v>
       </c>
       <c r="BG48" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="G49" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H49" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="I49" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>2.06</v>
       </c>
       <c r="K49" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9899,22 +9899,22 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="O49" t="n">
         <v>1.56</v>
       </c>
       <c r="P49" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R49" t="n">
         <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T49" t="n">
         <v>1.01</v>
@@ -9923,10 +9923,10 @@
         <v>1.01</v>
       </c>
       <c r="V49" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W49" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X49" t="n">
         <v>1000</v>
@@ -9941,7 +9941,7 @@
         <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC49" t="n">
         <v>1000</v>
@@ -9983,62 +9983,62 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AT49" t="n">
         <v>1.03</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
         <v>2.76</v>
       </c>
       <c r="I50" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>3.1</v>
@@ -10090,7 +10090,7 @@
         <v>1.44</v>
       </c>
       <c r="M50" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N50" t="n">
         <v>2.84</v>
@@ -10099,7 +10099,7 @@
         <v>1.47</v>
       </c>
       <c r="P50" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q50" t="n">
         <v>2.36</v>
@@ -10111,19 +10111,19 @@
         <v>4.5</v>
       </c>
       <c r="T50" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U50" t="n">
         <v>1.89</v>
       </c>
       <c r="V50" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W50" t="n">
         <v>1.5</v>
       </c>
       <c r="X50" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y50" t="n">
         <v>9.199999999999999</v>
@@ -10141,7 +10141,7 @@
         <v>9</v>
       </c>
       <c r="AD50" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE50" t="n">
         <v>38</v>
@@ -10159,7 +10159,7 @@
         <v>60</v>
       </c>
       <c r="AJ50" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK50" t="n">
         <v>40</v>
@@ -10192,7 +10192,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU50" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV50" t="n">
         <v>11</v>
@@ -10210,29 +10210,29 @@
         <v>17.5</v>
       </c>
       <c r="BA50" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB50" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BC50" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF50" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC50" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG50" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G51" t="n">
         <v>3.65</v>
@@ -10272,7 +10272,7 @@
         <v>2.4</v>
       </c>
       <c r="I51" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J51" t="n">
         <v>3.2</v>
@@ -10281,22 +10281,22 @@
         <v>3.3</v>
       </c>
       <c r="L51" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M51" t="n">
         <v>1.11</v>
       </c>
       <c r="N51" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O51" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P51" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R51" t="n">
         <v>1.21</v>
@@ -10305,25 +10305,25 @@
         <v>4.7</v>
       </c>
       <c r="T51" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U51" t="n">
         <v>1.81</v>
       </c>
       <c r="V51" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W51" t="n">
         <v>1.38</v>
       </c>
       <c r="X51" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y51" t="n">
         <v>970</v>
       </c>
       <c r="Z51" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AA51" t="n">
         <v>46</v>
@@ -10365,68 +10365,68 @@
         <v>190</v>
       </c>
       <c r="AN51" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AO51" t="n">
         <v>36</v>
       </c>
       <c r="AP51" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ51" t="n">
         <v>6.8</v>
       </c>
       <c r="AR51" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT51" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AU51" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA51" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV51" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BB51" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG51" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC51" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>44</v>
-      </c>
-      <c r="BG51" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -10460,16 +10460,16 @@
         <v>2.38</v>
       </c>
       <c r="G52" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J52" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>3.2</v>
       </c>
       <c r="K52" t="n">
         <v>3.35</v>
@@ -10481,7 +10481,7 @@
         <v>1.09</v>
       </c>
       <c r="N52" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O52" t="n">
         <v>1.43</v>
@@ -10508,7 +10508,7 @@
         <v>1.39</v>
       </c>
       <c r="W52" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X52" t="n">
         <v>11.5</v>
@@ -10523,7 +10523,7 @@
         <v>65</v>
       </c>
       <c r="AB52" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC52" t="n">
         <v>7.8</v>
@@ -10532,7 +10532,7 @@
         <v>15.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF52" t="n">
         <v>17.5</v>
@@ -10547,7 +10547,7 @@
         <v>65</v>
       </c>
       <c r="AJ52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK52" t="n">
         <v>34</v>
@@ -10571,10 +10571,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS52" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT52" t="n">
         <v>7.4</v>
@@ -10586,7 +10586,7 @@
         <v>12</v>
       </c>
       <c r="AW52" t="n">
-        <v>36</v>
+        <v>7.8</v>
       </c>
       <c r="AX52" t="n">
         <v>13</v>
@@ -10598,10 +10598,10 @@
         <v>17</v>
       </c>
       <c r="BA52" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB52" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC52" t="n">
         <v>22</v>
@@ -10610,17 +10610,17 @@
         <v>40</v>
       </c>
       <c r="BE52" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF52" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG52" t="n">
         <v>36</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -10660,10 +10660,10 @@
         <v>2.7</v>
       </c>
       <c r="I53" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K53" t="n">
         <v>3.3</v>
@@ -10681,7 +10681,7 @@
         <v>1.51</v>
       </c>
       <c r="P53" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q53" t="n">
         <v>2.64</v>
@@ -10696,7 +10696,7 @@
         <v>2.06</v>
       </c>
       <c r="U53" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V53" t="n">
         <v>1.52</v>
@@ -10741,10 +10741,10 @@
         <v>70</v>
       </c>
       <c r="AJ53" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK53" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL53" t="n">
         <v>70</v>
@@ -10753,7 +10753,7 @@
         <v>200</v>
       </c>
       <c r="AN53" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO53" t="n">
         <v>48</v>
@@ -10765,13 +10765,13 @@
         <v>7.4</v>
       </c>
       <c r="AR53" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="AS53" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT53" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU53" t="n">
         <v>6.8</v>
@@ -10780,41 +10780,41 @@
         <v>11</v>
       </c>
       <c r="AW53" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX53" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AY53" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BA53" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC53" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BD53" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG53" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC53" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG53" t="n">
-        <v>6</v>
-      </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
         <v>1.73</v>
       </c>
       <c r="R54" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S54" t="n">
         <v>2.86</v>
@@ -10890,7 +10890,7 @@
         <v>1.64</v>
       </c>
       <c r="U54" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V54" t="n">
         <v>1.45</v>
@@ -10962,7 +10962,7 @@
         <v>17</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT54" t="n">
         <v>9.6</v>
@@ -10986,19 +10986,19 @@
         <v>12</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC54" t="n">
         <v>18.5</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF54" t="n">
         <v>12.5</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G55" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H55" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I55" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J55" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K55" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L55" t="n">
         <v>1.25</v>
@@ -11066,7 +11066,7 @@
         <v>5.6</v>
       </c>
       <c r="O55" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P55" t="n">
         <v>2.62</v>
@@ -11075,7 +11075,7 @@
         <v>1.56</v>
       </c>
       <c r="R55" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S55" t="n">
         <v>2.44</v>
@@ -11087,22 +11087,22 @@
         <v>2.2</v>
       </c>
       <c r="V55" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W55" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="X55" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y55" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Z55" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA55" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB55" t="n">
         <v>12</v>
@@ -11111,16 +11111,16 @@
         <v>13</v>
       </c>
       <c r="AD55" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE55" t="n">
         <v>85</v>
       </c>
       <c r="AF55" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG55" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH55" t="n">
         <v>21</v>
@@ -11132,31 +11132,31 @@
         <v>15</v>
       </c>
       <c r="AK55" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AL55" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM55" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN55" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO55" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP55" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ55" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR55" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS55" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="AT55" t="n">
         <v>10.5</v>
@@ -11165,22 +11165,22 @@
         <v>10.5</v>
       </c>
       <c r="AV55" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW55" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="AX55" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY55" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ55" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB55" t="n">
         <v>12.5</v>
@@ -11192,17 +11192,17 @@
         <v>19.5</v>
       </c>
       <c r="BE55" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BF55" t="n">
         <v>5.2</v>
       </c>
       <c r="BG55" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
         <v>2.34</v>
       </c>
       <c r="H56" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I56" t="n">
         <v>4.6</v>
@@ -11284,7 +11284,7 @@
         <v>1.29</v>
       </c>
       <c r="W56" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X56" t="n">
         <v>12</v>
@@ -11350,7 +11350,7 @@
         <v>19</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT56" t="n">
         <v>6.4</v>
@@ -11362,7 +11362,7 @@
         <v>14.5</v>
       </c>
       <c r="AW56" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX56" t="n">
         <v>10.5</v>
@@ -11374,7 +11374,7 @@
         <v>19</v>
       </c>
       <c r="BA56" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB56" t="n">
         <v>20</v>
@@ -11383,20 +11383,20 @@
         <v>21</v>
       </c>
       <c r="BD56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE56" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF56" t="n">
         <v>18.5</v>
       </c>
       <c r="BG56" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
         <v>2.48</v>
       </c>
       <c r="I57" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J57" t="n">
         <v>3.1</v>
@@ -11472,13 +11472,13 @@
         <v>1.85</v>
       </c>
       <c r="U57" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V57" t="n">
         <v>1.59</v>
       </c>
       <c r="W57" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X57" t="n">
         <v>13.5</v>
@@ -11487,7 +11487,7 @@
         <v>11</v>
       </c>
       <c r="Z57" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA57" t="n">
         <v>44</v>
@@ -11496,7 +11496,7 @@
         <v>12.5</v>
       </c>
       <c r="AC57" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD57" t="n">
         <v>13.5</v>
@@ -11505,13 +11505,13 @@
         <v>32</v>
       </c>
       <c r="AF57" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG57" t="n">
         <v>16</v>
       </c>
       <c r="AH57" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI57" t="n">
         <v>60</v>
@@ -11544,7 +11544,7 @@
         <v>14.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT57" t="n">
         <v>9.4</v>
@@ -11556,7 +11556,7 @@
         <v>10.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AX57" t="n">
         <v>18</v>
@@ -11574,23 +11574,23 @@
         <v>36</v>
       </c>
       <c r="BC57" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BD57" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE57" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF57" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BG57" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-05 16:03:36</t>
+          <t>2026-05-05 18:14:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="H2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I2" t="n">
         <v>3.2</v>
       </c>
-      <c r="I2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
@@ -790,13 +790,13 @@
         <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
         <v>1.71</v>
@@ -805,25 +805,25 @@
         <v>2.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
@@ -832,25 +832,25 @@
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
         <v>36</v>
@@ -859,19 +859,19 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP2" t="n">
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
         <v>30</v>
@@ -880,16 +880,16 @@
         <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
@@ -898,10 +898,10 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -910,17 +910,17 @@
         <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
         <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
@@ -1193,7 +1193,7 @@
         <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
         <v>2.42</v>
@@ -1205,10 +1205,10 @@
         <v>21</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB4" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
         <v>20</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF4" t="n">
         <v>11</v>
@@ -1232,34 +1232,34 @@
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AJ4" t="n">
         <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
         <v>8.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AP4" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
         <v>42</v>
@@ -1268,13 +1268,13 @@
         <v>9</v>
       </c>
       <c r="AU4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AX4" t="n">
         <v>9.800000000000001</v>
@@ -1286,7 +1286,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BB4" t="n">
         <v>14.5</v>
@@ -1295,20 +1295,20 @@
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BF4" t="n">
         <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.69</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.73</v>
-      </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
@@ -1369,13 +1369,13 @@
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q5" t="n">
         <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
         <v>2.4</v>
@@ -1384,22 +1384,22 @@
         <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="X5" t="n">
         <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Z5" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA5" t="n">
         <v>130</v>
@@ -1411,10 +1411,10 @@
         <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF5" t="n">
         <v>12.5</v>
@@ -1423,55 +1423,55 @@
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AJ5" t="n">
         <v>19</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AL5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AS5" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.199999999999999</v>
@@ -1483,26 +1483,26 @@
         <v>34</v>
       </c>
       <c r="BB5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
         <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -1551,7 +1551,7 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
@@ -1563,43 +1563,43 @@
         <v>1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="Q6" t="n">
         <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S6" t="n">
         <v>2.24</v>
       </c>
       <c r="T6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X6" t="n">
         <v>30</v>
       </c>
       <c r="Y6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AA6" t="n">
         <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
@@ -1611,7 +1611,7 @@
         <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
@@ -1641,10 +1641,10 @@
         <v>17.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR6" t="n">
         <v>19</v>
@@ -1653,7 +1653,7 @@
         <v>28</v>
       </c>
       <c r="AT6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU6" t="n">
         <v>9.4</v>
@@ -1674,10 +1674,10 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC6" t="n">
         <v>17</v>
@@ -1686,7 +1686,7 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BF6" t="n">
         <v>8.800000000000001</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G7" t="n">
         <v>1.57</v>
@@ -1781,7 +1781,7 @@
         <v>2.74</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
         <v>28</v>
@@ -1799,37 +1799,37 @@
         <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE7" t="n">
-        <v>130</v>
+        <v>480</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
         <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK7" t="n">
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO7" t="n">
         <v>170</v>
@@ -1841,10 +1841,10 @@
         <v>19</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -1853,10 +1853,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
@@ -1868,7 +1868,7 @@
         <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
         <v>11.5</v>
@@ -1877,20 +1877,20 @@
         <v>13.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>990</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1969,7 +1969,7 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
@@ -2074,17 +2074,17 @@
         <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG8" t="n">
         <v>1.05</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2121,10 +2121,10 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
@@ -2148,7 +2148,7 @@
         <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R9" t="n">
         <v>1.35</v>
@@ -2157,13 +2157,13 @@
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
         <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
@@ -2187,7 +2187,7 @@
         <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>38</v>
@@ -2196,7 +2196,7 @@
         <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH9" t="n">
         <v>21</v>
@@ -2214,7 +2214,7 @@
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>32</v>
@@ -2232,7 +2232,7 @@
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2244,7 +2244,7 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
         <v>14</v>
@@ -2256,19 +2256,19 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
         <v>19</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.6</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.66</v>
-      </c>
       <c r="I10" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.31</v>
@@ -2342,10 +2342,10 @@
         <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
         <v>3.1</v>
@@ -2357,122 +2357,122 @@
         <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
         <v>13</v>
       </c>
       <c r="AE10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK10" t="n">
         <v>32</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>30</v>
       </c>
       <c r="AL10" t="n">
         <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
         <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
         <v>10</v>
       </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY10" t="n">
         <v>11</v>
       </c>
-      <c r="AW10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BB10" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF10" t="n">
         <v>20</v>
       </c>
-      <c r="BD10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BG10" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="G11" t="n">
         <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="I11" t="n">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>2.52</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2551,122 +2551,122 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
         <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="G12" t="n">
         <v>2.46</v>
@@ -2721,7 +2721,7 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O12" t="n">
         <v>1.31</v>
@@ -2730,7 +2730,7 @@
         <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
         <v>1.26</v>
@@ -2745,22 +2745,22 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
         <v>1.68</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y12" t="n">
         <v>18.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>13</v>
@@ -2772,7 +2772,7 @@
         <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
         <v>19.5</v>
@@ -2784,28 +2784,28 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.06</v>
+        <v>2.86</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.800000000000001</v>
@@ -2814,7 +2814,7 @@
         <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
@@ -2826,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="AX12" t="n">
         <v>8.800000000000001</v>
@@ -2838,7 +2838,7 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="BB12" t="n">
         <v>18.5</v>
@@ -2847,20 +2847,20 @@
         <v>15</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.12</v>
+        <v>18</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.12</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.12</v>
+        <v>7.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
         <v>2.72</v>
       </c>
       <c r="H13" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="K13" t="n">
         <v>3.7</v>
@@ -2939,122 +2939,122 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
         <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AA13" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
         <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF13" t="n">
         <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AJ13" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AM13" t="n">
         <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AP13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BD13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H14" t="n">
         <v>2.06</v>
       </c>
       <c r="I14" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>1.38</v>
@@ -3109,91 +3109,91 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
         <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X14" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AC14" t="n">
         <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AF14" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.92</v>
+        <v>2.58</v>
       </c>
       <c r="AQ14" t="n">
         <v>6.8</v>
@@ -3202,7 +3202,7 @@
         <v>9.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.91</v>
+        <v>11.5</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -3214,41 +3214,41 @@
         <v>7.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.89</v>
+        <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.91</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.96</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.85</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.96</v>
+        <v>16</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.96</v>
+        <v>2.74</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.96</v>
+        <v>2.72</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.96</v>
+        <v>2.74</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.96</v>
+        <v>2.74</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.96</v>
+        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.96</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>6.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
         <v>1.25</v>
@@ -3294,7 +3294,7 @@
         <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" t="n">
         <v>1.27</v>
@@ -3330,7 +3330,7 @@
         <v>2.78</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3342,7 +3342,7 @@
         <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
         <v>1000</v>
@@ -3384,65 +3384,65 @@
         <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG15" t="n">
         <v>1.05</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3479,10 +3479,10 @@
         <v>2.14</v>
       </c>
       <c r="H16" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>3.15</v>
@@ -3521,122 +3521,122 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W16" t="n">
         <v>1.87</v>
       </c>
       <c r="X16" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.64</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G17" t="n">
         <v>2.36</v>
@@ -3676,46 +3676,46 @@
         <v>3.05</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
         <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
         <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
         <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R17" t="n">
         <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
         <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
         <v>1.73</v>
@@ -3724,49 +3724,49 @@
         <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
         <v>30</v>
       </c>
       <c r="AA17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
         <v>17</v>
       </c>
       <c r="AE17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ17" t="n">
         <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM17" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
         <v>13.5</v>
@@ -3784,7 +3784,7 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
@@ -3796,7 +3796,7 @@
         <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AX17" t="n">
         <v>13</v>
@@ -3808,7 +3808,7 @@
         <v>11.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
         <v>21</v>
@@ -3817,10 +3817,10 @@
         <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
         <v>9.800000000000001</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -3870,10 +3870,10 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J18" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>3.9</v>
@@ -3909,25 +3909,25 @@
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
         <v>1.6</v>
       </c>
       <c r="X18" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AA18" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
@@ -3936,49 +3936,49 @@
         <v>970</v>
       </c>
       <c r="AE18" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AF18" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AG18" t="n">
         <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AJ18" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="AM18" t="n">
         <v>120</v>
       </c>
       <c r="AN18" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AO18" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AP18" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,41 +3990,41 @@
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="G19" t="n">
         <v>990</v>
       </c>
       <c r="H19" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="I19" t="n">
-        <v>870</v>
+        <v>85</v>
       </c>
       <c r="J19" t="n">
-        <v>1.09</v>
+        <v>2.52</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
@@ -4103,34 +4103,34 @@
         <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W19" t="n">
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
         <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
         <v>1000</v>
@@ -4142,7 +4142,7 @@
         <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
         <v>1000</v>
@@ -4160,65 +4160,65 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="G20" t="n">
-        <v>990</v>
+        <v>10.5</v>
       </c>
       <c r="H20" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="I20" t="n">
-        <v>990</v>
+        <v>10.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1.09</v>
+        <v>2.8</v>
       </c>
       <c r="K20" t="n">
         <v>3.85</v>
@@ -4273,19 +4273,19 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
         <v>1.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
         <v>1.05</v>
@@ -4297,122 +4297,122 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X20" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H21" t="n">
         <v>6.2</v>
       </c>
       <c r="I21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J21" t="n">
         <v>4.7</v>
       </c>
       <c r="K21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4506,7 +4506,7 @@
         <v>75</v>
       </c>
       <c r="AA21" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB21" t="n">
         <v>14</v>
@@ -4518,7 +4518,7 @@
         <v>32</v>
       </c>
       <c r="AE21" t="n">
-        <v>100</v>
+        <v>480</v>
       </c>
       <c r="AF21" t="n">
         <v>13.5</v>
@@ -4530,7 +4530,7 @@
         <v>25</v>
       </c>
       <c r="AI21" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ21" t="n">
         <v>17.5</v>
@@ -4542,13 +4542,13 @@
         <v>36</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN21" t="n">
         <v>7</v>
       </c>
       <c r="AO21" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AP21" t="n">
         <v>18.5</v>
@@ -4557,7 +4557,7 @@
         <v>20</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS21" t="n">
         <v>4.2</v>
@@ -4572,7 +4572,7 @@
         <v>18.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX21" t="n">
         <v>8.199999999999999</v>
@@ -4584,7 +4584,7 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB21" t="n">
         <v>10.5</v>
@@ -4596,17 +4596,17 @@
         <v>20</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>3.95</v>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
         <v>3.3</v>
@@ -4667,10 +4667,10 @@
         <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
         <v>1.27</v>
@@ -4679,13 +4679,13 @@
         <v>3.85</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
         <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
         <v>1.83</v>
@@ -4697,10 +4697,10 @@
         <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AA22" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
         <v>8.800000000000001</v>
@@ -4712,10 +4712,10 @@
         <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF22" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
@@ -4724,7 +4724,7 @@
         <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ22" t="n">
         <v>28</v>
@@ -4733,16 +4733,16 @@
         <v>26</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AM22" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
         <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AP22" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
         <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT22" t="n">
         <v>7</v>
@@ -4766,7 +4766,7 @@
         <v>14.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX22" t="n">
         <v>10.5</v>
@@ -4778,7 +4778,7 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB22" t="n">
         <v>22</v>
@@ -4787,20 +4787,20 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G23" t="n">
         <v>2.74</v>
@@ -4840,13 +4840,13 @@
         <v>2.64</v>
       </c>
       <c r="I23" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.31</v>
@@ -4879,13 +4879,13 @@
         <v>2.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W23" t="n">
         <v>1.57</v>
       </c>
       <c r="X23" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="Y23" t="n">
         <v>970</v>
@@ -4894,7 +4894,7 @@
         <v>970</v>
       </c>
       <c r="AA23" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AB23" t="n">
         <v>970</v>
@@ -4906,37 +4906,37 @@
         <v>970</v>
       </c>
       <c r="AE23" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AG23" t="n">
         <v>970</v>
       </c>
       <c r="AH23" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI23" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AJ23" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK23" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL23" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AM23" t="n">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AO23" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AP23" t="n">
         <v>6.2</v>
@@ -4945,10 +4945,10 @@
         <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
         <v>11</v>
@@ -4957,44 +4957,44 @@
         <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY23" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.28</v>
@@ -5052,7 +5052,7 @@
         <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P24" t="n">
         <v>2.28</v>
@@ -5064,28 +5064,28 @@
         <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T24" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V24" t="n">
         <v>1.21</v>
       </c>
       <c r="W24" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="X24" t="n">
         <v>26</v>
       </c>
       <c r="Y24" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="Z24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA24" t="n">
         <v>150</v>
@@ -5100,95 +5100,95 @@
         <v>23</v>
       </c>
       <c r="AE24" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AF24" t="n">
         <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AJ24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK24" t="n">
         <v>17</v>
       </c>
-      <c r="AK24" t="n">
-        <v>16</v>
-      </c>
       <c r="AL24" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
         <v>100</v>
       </c>
       <c r="AN24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO24" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AP24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>18.5</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AR24" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW24" t="n">
         <v>13</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
         <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD24" t="n">
         <v>25</v>
       </c>
       <c r="BE24" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG24" t="n">
         <v>13</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
         <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X25" t="n">
         <v>90</v>
@@ -5279,22 +5279,22 @@
         <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AA25" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
         <v>970</v>
       </c>
       <c r="AC25" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="n">
         <v>970</v>
       </c>
       <c r="AE25" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AF25" t="n">
         <v>970</v>
@@ -5303,86 +5303,86 @@
         <v>970</v>
       </c>
       <c r="AH25" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI25" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AO25" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AP25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="AT25" t="n">
         <v>9.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.78</v>
+        <v>4.6</v>
       </c>
       <c r="BB25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF25" t="n">
         <v>3.9</v>
       </c>
-      <c r="BC25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U26" t="n">
         <v>2</v>
@@ -5467,116 +5467,116 @@
         <v>2.3</v>
       </c>
       <c r="X26" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y26" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Z26" t="n">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD26" t="n">
         <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AF26" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI26" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AJ26" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AK26" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL26" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO26" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AP26" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
         <v>15.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU26" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY26" t="n">
         <v>5.8</v>
       </c>
-      <c r="AW26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB26" t="n">
         <v>12</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
         <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U27" t="n">
         <v>2.24</v>
@@ -5658,7 +5658,7 @@
         <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X27" t="n">
         <v>21</v>
@@ -5670,7 +5670,7 @@
         <v>34</v>
       </c>
       <c r="AA27" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB27" t="n">
         <v>13.5</v>
@@ -5694,7 +5694,7 @@
         <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ27" t="n">
         <v>34</v>
@@ -5706,7 +5706,7 @@
         <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN27" t="n">
         <v>17.5</v>
@@ -5718,49 +5718,49 @@
         <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="AS27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU27" t="n">
         <v>7.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>28</v>
+        <v>3.95</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY27" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="BD27" t="n">
         <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF27" t="n">
         <v>10.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -5807,10 +5807,10 @@
         <v>1.83</v>
       </c>
       <c r="H28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J28" t="n">
         <v>3.8</v>
@@ -5855,70 +5855,70 @@
         <v>2.2</v>
       </c>
       <c r="X28" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="Y28" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="Z28" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="AA28" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AC28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AE28" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH28" t="n">
         <v>970</v>
       </c>
       <c r="AI28" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AJ28" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AK28" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL28" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AO28" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT28" t="n">
         <v>7.2</v>
@@ -5927,10 +5927,10 @@
         <v>8</v>
       </c>
       <c r="AV28" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX28" t="n">
         <v>8.800000000000001</v>
@@ -5939,10 +5939,10 @@
         <v>7.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB28" t="n">
         <v>11.5</v>
@@ -5951,20 +5951,20 @@
         <v>12</v>
       </c>
       <c r="BD28" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF28" t="n">
         <v>7.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>2.08</v>
       </c>
       <c r="H29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I29" t="n">
         <v>4.6</v>
@@ -6013,7 +6013,7 @@
         <v>3.75</v>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6025,7 +6025,7 @@
         <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q29" t="n">
         <v>2.04</v>
@@ -6037,7 +6037,7 @@
         <v>3.7</v>
       </c>
       <c r="T29" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U29" t="n">
         <v>1.9</v>
@@ -6055,67 +6055,67 @@
         <v>970</v>
       </c>
       <c r="Z29" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AA29" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC29" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD29" t="n">
         <v>970</v>
       </c>
       <c r="AE29" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AG29" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH29" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AI29" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ29" t="n">
-        <v>25</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL29" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO29" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AP29" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -6124,7 +6124,7 @@
         <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AX29" t="n">
         <v>8.6</v>
@@ -6133,10 +6133,10 @@
         <v>8</v>
       </c>
       <c r="AZ29" t="n">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BB29" t="n">
         <v>17</v>
@@ -6145,20 +6145,20 @@
         <v>17</v>
       </c>
       <c r="BD29" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF29" t="n">
         <v>13</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -6189,19 +6189,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G30" t="n">
         <v>1.5</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I30" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J30" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K30" t="n">
         <v>5.9</v>
@@ -6237,19 +6237,19 @@
         <v>2.08</v>
       </c>
       <c r="V30" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W30" t="n">
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Y30" t="n">
         <v>950</v>
       </c>
       <c r="Z30" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AA30" t="n">
         <v>240</v>
@@ -6258,55 +6258,55 @@
         <v>970</v>
       </c>
       <c r="AC30" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AD30" t="n">
         <v>950</v>
       </c>
       <c r="AE30" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
         <v>950</v>
       </c>
       <c r="AI30" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ30" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>970</v>
       </c>
       <c r="AL30" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
       </c>
       <c r="AN30" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="AO30" t="n">
         <v>110</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AS30" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AT30" t="n">
         <v>9.800000000000001</v>
@@ -6315,10 +6315,10 @@
         <v>10.5</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AX30" t="n">
         <v>9</v>
@@ -6327,32 +6327,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC30" t="n">
         <v>12</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF30" t="n">
         <v>4.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H31" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I31" t="n">
         <v>2.3</v>
@@ -6398,7 +6398,7 @@
         <v>3.65</v>
       </c>
       <c r="K31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
         <v>1.3</v>
@@ -6437,58 +6437,58 @@
         <v>1.38</v>
       </c>
       <c r="X31" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA31" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AB31" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AC31" t="n">
         <v>10.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI31" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AJ31" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK31" t="n">
         <v>42</v>
       </c>
       <c r="AL31" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AM31" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN31" t="n">
         <v>34</v>
       </c>
       <c r="AO31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP31" t="n">
         <v>15.5</v>
@@ -6500,7 +6500,7 @@
         <v>13.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AT31" t="n">
         <v>13</v>
@@ -6524,19 +6524,19 @@
         <v>13.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF31" t="n">
         <v>21</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6580,19 @@
         <v>5.9</v>
       </c>
       <c r="G32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I32" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="J32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K32" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6622,7 +6622,7 @@
         <v>1.79</v>
       </c>
       <c r="U32" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
@@ -6631,58 +6631,58 @@
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="Y32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD32" t="n">
         <v>10</v>
       </c>
-      <c r="Z32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AE32" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AF32" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AG32" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AH32" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AI32" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AK32" t="n">
-        <v>95</v>
+        <v>700</v>
       </c>
       <c r="AL32" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AM32" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AO32" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AP32" t="n">
         <v>15</v>
@@ -6709,7 +6709,7 @@
         <v>12.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AY32" t="n">
         <v>18</v>
@@ -6718,29 +6718,29 @@
         <v>15.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB32" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG32" t="n">
         <v>6.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G33" t="n">
         <v>1.54</v>
@@ -6780,7 +6780,7 @@
         <v>6.4</v>
       </c>
       <c r="I33" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J33" t="n">
         <v>4.8</v>
@@ -6825,13 +6825,13 @@
         <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Y33" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Z33" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA33" t="n">
         <v>220</v>
@@ -6840,34 +6840,34 @@
         <v>13.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AD33" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AE33" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF33" t="n">
         <v>13</v>
       </c>
       <c r="AG33" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ33" t="n">
         <v>17</v>
       </c>
       <c r="AK33" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AL33" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="n">
         <v>110</v>
@@ -6885,10 +6885,10 @@
         <v>21</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT33" t="n">
         <v>8.199999999999999</v>
@@ -6897,10 +6897,10 @@
         <v>10</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AX33" t="n">
         <v>8</v>
@@ -6912,7 +6912,7 @@
         <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BB33" t="n">
         <v>10</v>
@@ -6924,17 +6924,17 @@
         <v>20</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF33" t="n">
         <v>5.1</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -6968,22 +6968,22 @@
         <v>3.3</v>
       </c>
       <c r="G34" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H34" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I34" t="n">
         <v>2.56</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
         <v>3.4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M34" t="n">
         <v>1.1</v>
@@ -6998,16 +6998,16 @@
         <v>1.69</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R34" t="n">
         <v>1.26</v>
       </c>
       <c r="S34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U34" t="n">
         <v>1.94</v>
@@ -7016,16 +7016,16 @@
         <v>1.64</v>
       </c>
       <c r="W34" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X34" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z34" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA34" t="n">
         <v>38</v>
@@ -7052,7 +7052,7 @@
         <v>23</v>
       </c>
       <c r="AI34" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AJ34" t="n">
         <v>70</v>
@@ -7064,7 +7064,7 @@
         <v>70</v>
       </c>
       <c r="AM34" t="n">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="AN34" t="n">
         <v>55</v>
@@ -7082,7 +7082,7 @@
         <v>12.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AT34" t="n">
         <v>8.800000000000001</v>
@@ -7094,7 +7094,7 @@
         <v>10.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX34" t="n">
         <v>17</v>
@@ -7103,32 +7103,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BE34" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="H35" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="I35" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="J35" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L35" t="n">
         <v>1.22</v>
@@ -7195,22 +7195,22 @@
         <v>1.51</v>
       </c>
       <c r="R35" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S35" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T35" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U35" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V35" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="W35" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X35" t="n">
         <v>34</v>
@@ -7258,7 +7258,7 @@
         <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AN35" t="n">
         <v>38</v>
@@ -7267,7 +7267,7 @@
         <v>8</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AQ35" t="n">
         <v>11.5</v>
@@ -7291,7 +7291,7 @@
         <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="AY35" t="n">
         <v>15.5</v>
@@ -7303,26 +7303,26 @@
         <v>18.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF35" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG35" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -7353,19 +7353,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G36" t="n">
         <v>2.42</v>
       </c>
       <c r="H36" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I36" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J36" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
         <v>3.8</v>
@@ -7401,34 +7401,34 @@
         <v>1.98</v>
       </c>
       <c r="V36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W36" t="n">
         <v>1.71</v>
       </c>
       <c r="X36" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y36" t="n">
         <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AA36" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AB36" t="n">
         <v>970</v>
       </c>
       <c r="AC36" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD36" t="n">
         <v>970</v>
       </c>
       <c r="AE36" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF36" t="n">
         <v>970</v>
@@ -7440,34 +7440,34 @@
         <v>950</v>
       </c>
       <c r="AI36" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ36" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK36" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AL36" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN36" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AO36" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP36" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AS36" t="n">
         <v>3.3</v>
@@ -7476,47 +7476,47 @@
         <v>6.8</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AV36" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="AZ36" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BA36" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BC36" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG36" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G37" t="n">
         <v>2.82</v>
@@ -7559,10 +7559,10 @@
         <v>3.25</v>
       </c>
       <c r="J37" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L37" t="n">
         <v>1.53</v>
@@ -7601,49 +7601,49 @@
         <v>1.54</v>
       </c>
       <c r="X37" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z37" t="n">
         <v>24</v>
       </c>
       <c r="AA37" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB37" t="n">
         <v>8.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE37" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AF37" t="n">
         <v>18</v>
       </c>
       <c r="AG37" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI37" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AJ37" t="n">
         <v>55</v>
       </c>
       <c r="AK37" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AL37" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM37" t="n">
         <v>250</v>
@@ -7664,7 +7664,7 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT37" t="n">
         <v>6.4</v>
@@ -7676,7 +7676,7 @@
         <v>13</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AX37" t="n">
         <v>13</v>
@@ -7688,29 +7688,29 @@
         <v>19.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BC37" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         <v>4.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U38" t="n">
         <v>1.57</v>
@@ -7801,7 +7801,7 @@
         <v>25</v>
       </c>
       <c r="Z38" t="n">
-        <v>100</v>
+        <v>480</v>
       </c>
       <c r="AA38" t="n">
         <v>550</v>
@@ -7813,7 +7813,7 @@
         <v>9.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="AE38" t="n">
         <v>280</v>
@@ -7825,7 +7825,7 @@
         <v>13.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="AI38" t="n">
         <v>260</v>
@@ -7834,16 +7834,16 @@
         <v>17.5</v>
       </c>
       <c r="AK38" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AL38" t="n">
-        <v>70</v>
+        <v>380</v>
       </c>
       <c r="AM38" t="n">
         <v>390</v>
       </c>
       <c r="AN38" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO38" t="n">
         <v>600</v>
@@ -7855,7 +7855,7 @@
         <v>17</v>
       </c>
       <c r="AR38" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS38" t="n">
         <v>6.6</v>
@@ -7867,10 +7867,10 @@
         <v>7</v>
       </c>
       <c r="AV38" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX38" t="n">
         <v>6.6</v>
@@ -7882,7 +7882,7 @@
         <v>25</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB38" t="n">
         <v>12</v>
@@ -7891,7 +7891,7 @@
         <v>16</v>
       </c>
       <c r="BD38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE38" t="n">
         <v>6.6</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
         <v>3.8</v>
       </c>
       <c r="J39" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K39" t="n">
         <v>3.35</v>
@@ -7968,7 +7968,7 @@
         <v>1.61</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R39" t="n">
         <v>1.23</v>
@@ -7989,16 +7989,16 @@
         <v>1.66</v>
       </c>
       <c r="X39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y39" t="n">
         <v>11.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA39" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB39" t="n">
         <v>8.800000000000001</v>
@@ -8007,13 +8007,13 @@
         <v>7.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AE39" t="n">
-        <v>55</v>
+        <v>370</v>
       </c>
       <c r="AF39" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AG39" t="n">
         <v>12.5</v>
@@ -8022,25 +8022,25 @@
         <v>950</v>
       </c>
       <c r="AI39" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ39" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AK39" t="n">
         <v>36</v>
       </c>
       <c r="AL39" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN39" t="n">
         <v>60</v>
       </c>
-      <c r="AM39" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>36</v>
-      </c>
       <c r="AO39" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP39" t="n">
         <v>7.6</v>
@@ -8052,7 +8052,7 @@
         <v>19</v>
       </c>
       <c r="AS39" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT39" t="n">
         <v>7.4</v>
@@ -8064,10 +8064,10 @@
         <v>12.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX39" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AY39" t="n">
         <v>9.199999999999999</v>
@@ -8076,29 +8076,29 @@
         <v>15.5</v>
       </c>
       <c r="BA39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC39" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>6.6</v>
       </c>
       <c r="BD39" t="n">
         <v>36</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF39" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
         <v>3.8</v>
       </c>
       <c r="J40" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
         <v>3.3</v>
@@ -8150,16 +8150,16 @@
         <v>1.59</v>
       </c>
       <c r="M40" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N40" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O40" t="n">
         <v>1.73</v>
       </c>
       <c r="P40" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q40" t="n">
         <v>3.15</v>
@@ -8171,7 +8171,7 @@
         <v>6.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="U40" t="n">
         <v>1.58</v>
@@ -8189,13 +8189,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z40" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA40" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB40" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC40" t="n">
         <v>8</v>
@@ -8204,37 +8204,37 @@
         <v>18.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AF40" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH40" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AJ40" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AK40" t="n">
-        <v>48</v>
+        <v>290</v>
       </c>
       <c r="AL40" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AM40" t="n">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="AN40" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AO40" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP40" t="n">
         <v>6</v>
@@ -8246,7 +8246,7 @@
         <v>17</v>
       </c>
       <c r="AS40" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT40" t="n">
         <v>5.5</v>
@@ -8258,7 +8258,7 @@
         <v>15</v>
       </c>
       <c r="AW40" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AX40" t="n">
         <v>10</v>
@@ -8267,32 +8267,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BA40" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB40" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC40" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BD40" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE40" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF40" t="n">
         <v>40</v>
       </c>
       <c r="BG40" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -8338,10 +8338,10 @@
         <v>5.3</v>
       </c>
       <c r="K41" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L41" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M41" t="n">
         <v>1.03</v>
@@ -8398,7 +8398,7 @@
         <v>36</v>
       </c>
       <c r="AE41" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF41" t="n">
         <v>12</v>
@@ -8410,7 +8410,7 @@
         <v>26</v>
       </c>
       <c r="AI41" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AJ41" t="n">
         <v>14.5</v>
@@ -8449,7 +8449,7 @@
         <v>11.5</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AW41" t="n">
         <v>5.5</v>
@@ -8482,11 +8482,11 @@
         <v>4</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -8520,16 +8520,16 @@
         <v>2.18</v>
       </c>
       <c r="G42" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="H42" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I42" t="n">
         <v>4.1</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K42" t="n">
         <v>3.55</v>
@@ -8541,13 +8541,13 @@
         <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
         <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q42" t="n">
         <v>2.04</v>
@@ -8556,19 +8556,19 @@
         <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
         <v>1.89</v>
       </c>
       <c r="U42" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="V42" t="n">
         <v>1.33</v>
       </c>
       <c r="W42" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="X42" t="n">
         <v>14</v>
@@ -8601,22 +8601,22 @@
         <v>11.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI42" t="n">
         <v>80</v>
       </c>
       <c r="AJ42" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK42" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL42" t="n">
         <v>55</v>
       </c>
       <c r="AM42" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN42" t="n">
         <v>29</v>
@@ -8625,62 +8625,62 @@
         <v>65</v>
       </c>
       <c r="AP42" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AR42" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV42" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX42" t="n">
         <v>5.1</v>
       </c>
-      <c r="AW42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AY42" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC42" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD42" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF42" t="n">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="BG42" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -8720,16 +8720,16 @@
         <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K43" t="n">
         <v>4.9</v>
       </c>
       <c r="L43" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M43" t="n">
         <v>1.07</v>
@@ -8771,7 +8771,7 @@
         <v>28</v>
       </c>
       <c r="Z43" t="n">
-        <v>100</v>
+        <v>480</v>
       </c>
       <c r="AA43" t="n">
         <v>490</v>
@@ -8795,10 +8795,10 @@
         <v>12.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI43" t="n">
-        <v>200</v>
+        <v>540</v>
       </c>
       <c r="AJ43" t="n">
         <v>14.5</v>
@@ -8825,10 +8825,10 @@
         <v>18</v>
       </c>
       <c r="AR43" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT43" t="n">
         <v>5.6</v>
@@ -8837,10 +8837,10 @@
         <v>8</v>
       </c>
       <c r="AV43" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX43" t="n">
         <v>6.6</v>
@@ -8849,10 +8849,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB43" t="n">
         <v>11</v>
@@ -8861,20 +8861,20 @@
         <v>15.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF43" t="n">
         <v>7.2</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -8959,49 +8959,49 @@
         <v>1.69</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y44" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AC44" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD44" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AE44" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF44" t="n">
         <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI44" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL44" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM44" t="n">
         <v>1000</v>
@@ -9013,62 +9013,62 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -9099,25 +9099,25 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="G45" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H45" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="I45" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="J45" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
         <v>3.3</v>
       </c>
       <c r="L45" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
@@ -9129,34 +9129,34 @@
         <v>1.4</v>
       </c>
       <c r="P45" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q45" t="n">
         <v>2.18</v>
       </c>
       <c r="R45" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T45" t="n">
         <v>1.83</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V45" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W45" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y45" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z45" t="n">
         <v>21</v>
@@ -9165,7 +9165,7 @@
         <v>55</v>
       </c>
       <c r="AB45" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC45" t="n">
         <v>7.4</v>
@@ -9177,92 +9177,92 @@
         <v>36</v>
       </c>
       <c r="AF45" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG45" t="n">
         <v>14</v>
       </c>
       <c r="AH45" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI45" t="n">
         <v>55</v>
       </c>
       <c r="AJ45" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AK45" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL45" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM45" t="n">
         <v>140</v>
       </c>
       <c r="AN45" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO45" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP45" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT45" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ45" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS45" t="n">
+      <c r="AU45" t="n">
         <v>6</v>
       </c>
-      <c r="AT45" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AV45" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW45" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AX45" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC45" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BD45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE45" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF45" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG45" t="n">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -9293,82 +9293,82 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="G46" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="H46" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J46" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K46" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L46" t="n">
         <v>1.37</v>
       </c>
       <c r="M46" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N46" t="n">
+        <v>3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q46" t="n">
         <v>2.16</v>
       </c>
-      <c r="O46" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2</v>
-      </c>
       <c r="R46" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S46" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T46" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U46" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V46" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W46" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y46" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD46" t="n">
         <v>970</v>
       </c>
-      <c r="Z46" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>22</v>
-      </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF46" t="n">
         <v>970</v>
@@ -9377,86 +9377,86 @@
         <v>970</v>
       </c>
       <c r="AH46" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ46" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK46" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ46" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="AT46" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU46" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV46" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.16</v>
+        <v>5.9</v>
       </c>
       <c r="AX46" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY46" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2.06</v>
+        <v>5.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="BB46" t="n">
-        <v>2.12</v>
+        <v>5.9</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.16</v>
+        <v>6.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="BF46" t="n">
-        <v>2.16</v>
+        <v>5.7</v>
       </c>
       <c r="BG46" t="n">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G47" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H47" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I47" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K47" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L47" t="n">
         <v>1.38</v>
@@ -9511,7 +9511,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O47" t="n">
         <v>1.44</v>
@@ -9535,122 +9535,122 @@
         <v>1.11</v>
       </c>
       <c r="V47" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA47" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -9687,10 +9687,10 @@
         <v>1.66</v>
       </c>
       <c r="H48" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
         <v>5.8</v>
@@ -9699,7 +9699,7 @@
         <v>5.9</v>
       </c>
       <c r="L48" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="M48" t="n">
         <v>1.01</v>
@@ -9711,31 +9711,31 @@
         <v>1.07</v>
       </c>
       <c r="P48" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R48" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="S48" t="n">
         <v>1.57</v>
       </c>
       <c r="T48" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="U48" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W48" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X48" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y48" t="n">
         <v>48</v>
@@ -9744,7 +9744,7 @@
         <v>60</v>
       </c>
       <c r="AA48" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB48" t="n">
         <v>29</v>
@@ -9759,19 +9759,19 @@
         <v>38</v>
       </c>
       <c r="AF48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG48" t="n">
         <v>13</v>
       </c>
       <c r="AH48" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI48" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ48" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK48" t="n">
         <v>14.5</v>
@@ -9783,10 +9783,10 @@
         <v>32</v>
       </c>
       <c r="AN48" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AO48" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP48" t="n">
         <v>65</v>
@@ -9807,44 +9807,44 @@
         <v>18.5</v>
       </c>
       <c r="AV48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW48" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX48" t="n">
         <v>21</v>
       </c>
       <c r="AY48" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ48" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC48" t="n">
         <v>14</v>
       </c>
       <c r="BD48" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BE48" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BF48" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BG48" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
         <v>2.24</v>
       </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J49" t="n">
         <v>2.06</v>
@@ -9893,16 +9893,16 @@
         <v>3.3</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M49" t="n">
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="O49" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="P49" t="n">
         <v>1.36</v>
@@ -9914,13 +9914,13 @@
         <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V49" t="n">
         <v>1.44</v>
@@ -9929,7 +9929,7 @@
         <v>1.28</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y49" t="n">
         <v>1000</v>
@@ -9938,7 +9938,7 @@
         <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB49" t="n">
         <v>970</v>
@@ -9965,7 +9965,7 @@
         <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK49" t="n">
         <v>1000</v>
@@ -9983,62 +9983,62 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -10075,16 +10075,16 @@
         <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I50" t="n">
         <v>2.9</v>
       </c>
       <c r="J50" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K50" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L50" t="n">
         <v>1.44</v>
@@ -10093,7 +10093,7 @@
         <v>1.11</v>
       </c>
       <c r="N50" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O50" t="n">
         <v>1.47</v>
@@ -10132,7 +10132,7 @@
         <v>22</v>
       </c>
       <c r="AA50" t="n">
-        <v>48</v>
+        <v>350</v>
       </c>
       <c r="AB50" t="n">
         <v>9.4</v>
@@ -10144,7 +10144,7 @@
         <v>13.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AF50" t="n">
         <v>23</v>
@@ -10156,25 +10156,25 @@
         <v>21</v>
       </c>
       <c r="AI50" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="AJ50" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK50" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AL50" t="n">
-        <v>60</v>
+        <v>490</v>
       </c>
       <c r="AM50" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN50" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AP50" t="n">
         <v>8.800000000000001</v>
@@ -10210,29 +10210,29 @@
         <v>17.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BB50" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC50" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BD50" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE50" t="n">
         <v>8.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BG50" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -10266,16 +10266,16 @@
         <v>3.4</v>
       </c>
       <c r="G51" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H51" t="n">
         <v>2.4</v>
       </c>
       <c r="I51" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K51" t="n">
         <v>3.3</v>
@@ -10293,7 +10293,7 @@
         <v>1.49</v>
       </c>
       <c r="P51" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q51" t="n">
         <v>2.36</v>
@@ -10302,131 +10302,131 @@
         <v>1.21</v>
       </c>
       <c r="S51" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T51" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U51" t="n">
         <v>1.81</v>
       </c>
       <c r="V51" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W51" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X51" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z51" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AA51" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AB51" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AC51" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD51" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE51" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="AF51" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="AG51" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AH51" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI51" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ51" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK51" t="n">
-        <v>55</v>
+        <v>320</v>
       </c>
       <c r="AL51" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM51" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AN51" t="n">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="AO51" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AP51" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ51" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AR51" t="n">
         <v>9.6</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT51" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AU51" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV51" t="n">
         <v>9.6</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="AX51" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AY51" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ51" t="n">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB51" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC51" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BD51" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF51" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG51" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -10463,16 +10463,16 @@
         <v>2.56</v>
       </c>
       <c r="H52" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I52" t="n">
         <v>3.55</v>
       </c>
       <c r="J52" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K52" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10535,7 +10535,7 @@
         <v>48</v>
       </c>
       <c r="AF52" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG52" t="n">
         <v>12.5</v>
@@ -10550,7 +10550,7 @@
         <v>38</v>
       </c>
       <c r="AK52" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL52" t="n">
         <v>55</v>
@@ -10574,19 +10574,19 @@
         <v>19</v>
       </c>
       <c r="AS52" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT52" t="n">
         <v>7.4</v>
       </c>
       <c r="AU52" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV52" t="n">
         <v>12</v>
       </c>
       <c r="AW52" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX52" t="n">
         <v>13</v>
@@ -10598,7 +10598,7 @@
         <v>17</v>
       </c>
       <c r="BA52" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB52" t="n">
         <v>7.6</v>
@@ -10610,17 +10610,17 @@
         <v>40</v>
       </c>
       <c r="BE52" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF52" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG52" t="n">
         <v>36</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -10663,40 +10663,40 @@
         <v>2.9</v>
       </c>
       <c r="J53" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K53" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L53" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M53" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="O53" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="P53" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q53" t="n">
         <v>2.64</v>
       </c>
       <c r="R53" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S53" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T53" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U53" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V53" t="n">
         <v>1.52</v>
@@ -10705,13 +10705,13 @@
         <v>1.48</v>
       </c>
       <c r="X53" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y53" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z53" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA53" t="n">
         <v>55</v>
@@ -10720,7 +10720,7 @@
         <v>8.6</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD53" t="n">
         <v>970</v>
@@ -10729,92 +10729,92 @@
         <v>44</v>
       </c>
       <c r="AF53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG53" t="n">
         <v>15.5</v>
       </c>
       <c r="AH53" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI53" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ53" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK53" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL53" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM53" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN53" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO53" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP53" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AQ53" t="n">
         <v>7.4</v>
       </c>
       <c r="AR53" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AS53" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT53" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU53" t="n">
         <v>6.8</v>
       </c>
       <c r="AV53" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW53" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX53" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX53" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AY53" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BA53" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB53" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BC53" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD53" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE53" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BF53" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG53" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
         <v>17</v>
       </c>
       <c r="AS54" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT54" t="n">
         <v>9.6</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -11039,31 +11039,31 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G55" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H55" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I55" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J55" t="n">
         <v>4.8</v>
       </c>
       <c r="K55" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L55" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M55" t="n">
         <v>1.03</v>
       </c>
       <c r="N55" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
         <v>1.19</v>
@@ -11084,13 +11084,13 @@
         <v>1.74</v>
       </c>
       <c r="U55" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V55" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W55" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="X55" t="n">
         <v>25</v>
@@ -11099,7 +11099,7 @@
         <v>32</v>
       </c>
       <c r="Z55" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA55" t="n">
         <v>210</v>
@@ -11111,19 +11111,19 @@
         <v>13</v>
       </c>
       <c r="AD55" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE55" t="n">
         <v>85</v>
       </c>
       <c r="AF55" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG55" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI55" t="n">
         <v>75</v>
@@ -11132,13 +11132,13 @@
         <v>15</v>
       </c>
       <c r="AK55" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL55" t="n">
         <v>27</v>
       </c>
       <c r="AM55" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN55" t="n">
         <v>5.7</v>
@@ -11150,7 +11150,7 @@
         <v>21</v>
       </c>
       <c r="AQ55" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR55" t="n">
         <v>32</v>
@@ -11165,10 +11165,10 @@
         <v>10.5</v>
       </c>
       <c r="AV55" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW55" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX55" t="n">
         <v>9.800000000000001</v>
@@ -11177,10 +11177,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ55" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA55" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB55" t="n">
         <v>12.5</v>
@@ -11189,7 +11189,7 @@
         <v>12.5</v>
       </c>
       <c r="BD55" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BE55" t="n">
         <v>36</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -11242,10 +11242,10 @@
         <v>3.9</v>
       </c>
       <c r="I56" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J56" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K56" t="n">
         <v>3.45</v>
@@ -11263,10 +11263,10 @@
         <v>1.47</v>
       </c>
       <c r="P56" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R56" t="n">
         <v>1.22</v>
@@ -11284,7 +11284,7 @@
         <v>1.29</v>
       </c>
       <c r="W56" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X56" t="n">
         <v>12</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="AI56" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ56" t="n">
         <v>36</v>
@@ -11350,7 +11350,7 @@
         <v>19</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT56" t="n">
         <v>6.4</v>
@@ -11383,7 +11383,7 @@
         <v>21</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE56" t="n">
         <v>4.3</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
         <v>1.09</v>
       </c>
       <c r="N57" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O57" t="n">
         <v>1.39</v>
@@ -11460,10 +11460,10 @@
         <v>1.73</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R57" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -11508,7 +11508,7 @@
         <v>24</v>
       </c>
       <c r="AG57" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH57" t="n">
         <v>21</v>
@@ -11544,7 +11544,7 @@
         <v>14.5</v>
       </c>
       <c r="AS57" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT57" t="n">
         <v>9.4</v>
@@ -11556,7 +11556,7 @@
         <v>10.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX57" t="n">
         <v>18</v>
@@ -11574,23 +11574,23 @@
         <v>36</v>
       </c>
       <c r="BC57" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD57" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF57" t="n">
         <v>5.9</v>
       </c>
-      <c r="BE57" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BG57" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
         <v>1.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R58" t="n">
         <v>1.18</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-05 18:14:47</t>
+          <t>2026-05-05 20:26:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H2" t="n">
         <v>3.15</v>
@@ -769,13 +769,13 @@
         <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -802,16 +802,16 @@
         <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
         <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
         <v>13.5</v>
@@ -826,22 +826,22 @@
         <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -850,7 +850,7 @@
         <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
         <v>36</v>
@@ -859,7 +859,7 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
@@ -868,13 +868,13 @@
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -895,32 +895,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
         <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1151,19 +1151,19 @@
         <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1175,25 +1175,25 @@
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
         <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
         <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
         <v>2.42</v>
@@ -1211,7 +1211,7 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK4" t="n">
         <v>21</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>75</v>
@@ -1259,7 +1259,7 @@
         <v>17.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AS4" t="n">
         <v>42</v>
@@ -1271,10 +1271,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AX4" t="n">
         <v>9.800000000000001</v>
@@ -1295,7 +1295,7 @@
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE4" t="n">
         <v>60</v>
@@ -1304,11 +1304,11 @@
         <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
@@ -1369,19 +1369,19 @@
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
         <v>2.4</v>
@@ -1390,7 +1390,7 @@
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X5" t="n">
         <v>27</v>
@@ -1402,7 +1402,7 @@
         <v>95</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AB5" t="n">
         <v>12.5</v>
@@ -1429,13 +1429,13 @@
         <v>250</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1447,16 +1447,16 @@
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
         <v>34</v>
       </c>
       <c r="AS5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AT5" t="n">
         <v>11</v>
@@ -1465,10 +1465,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1480,7 +1480,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BB5" t="n">
         <v>15</v>
@@ -1492,17 +1492,17 @@
         <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF5" t="n">
         <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
@@ -1551,7 +1551,7 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
@@ -1563,7 +1563,7 @@
         <v>1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q6" t="n">
         <v>1.5</v>
@@ -1572,7 +1572,7 @@
         <v>1.75</v>
       </c>
       <c r="S6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T6" t="n">
         <v>1.5</v>
@@ -1593,7 +1593,7 @@
         <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
         <v>55</v>
@@ -1611,7 +1611,7 @@
         <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
@@ -1644,13 +1644,13 @@
         <v>24</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AS6" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AT6" t="n">
         <v>15</v>
@@ -1662,7 +1662,7 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
         <v>16.5</v>
@@ -1674,10 +1674,10 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BB6" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BC6" t="n">
         <v>17</v>
@@ -1686,7 +1686,7 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BF6" t="n">
         <v>8.800000000000001</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R7" t="n">
         <v>1.4</v>
@@ -1784,7 +1784,7 @@
         <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z7" t="n">
         <v>70</v>
@@ -1835,7 +1835,7 @@
         <v>170</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>19</v>
@@ -1844,7 +1844,7 @@
         <v>7.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -1856,7 +1856,7 @@
         <v>14</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
@@ -1868,7 +1868,7 @@
         <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB7" t="n">
         <v>11.5</v>
@@ -1880,17 +1880,17 @@
         <v>18</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="G8" t="n">
-        <v>990</v>
+        <v>9.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>1.94</v>
       </c>
       <c r="J8" t="n">
-        <v>1.45</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -1969,10 +1969,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>2.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -1990,7 +1990,7 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU8" t="n">
         <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF8" t="n">
         <v>1.55</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
@@ -2139,13 +2139,13 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
         <v>1.9</v>
@@ -2214,7 +2214,7 @@
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
         <v>32</v>
@@ -2232,7 +2232,7 @@
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2256,19 +2256,19 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.9</v>
+        <v>30</v>
       </c>
       <c r="BC9" t="n">
         <v>5.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
         <v>19</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2309,31 +2309,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>1.28</v>
@@ -2357,22 +2357,22 @@
         <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
         <v>19</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB10" t="n">
         <v>13.5</v>
@@ -2381,10 +2381,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF10" t="n">
         <v>22</v>
@@ -2399,22 +2399,22 @@
         <v>40</v>
       </c>
       <c r="AJ10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL10" t="n">
         <v>46</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>42</v>
       </c>
       <c r="AM10" t="n">
         <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP10" t="n">
         <v>13</v>
@@ -2426,7 +2426,7 @@
         <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2438,19 +2438,19 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY10" t="n">
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BB10" t="n">
         <v>16</v>
@@ -2459,20 +2459,20 @@
         <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
         <v>17.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.21</v>
+        <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>2.68</v>
       </c>
       <c r="H11" t="n">
-        <v>1.17</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA11" t="n">
         <v>65</v>
       </c>
-      <c r="AA11" t="n">
-        <v>460</v>
-      </c>
       <c r="AB11" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>370</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI11" t="n">
         <v>60</v>
       </c>
-      <c r="AG11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>500</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>430</v>
+        <v>38</v>
       </c>
       <c r="AK11" t="n">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>490</v>
+        <v>70</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AN11" t="n">
-        <v>990</v>
+        <v>29</v>
       </c>
       <c r="AO11" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS11" t="n">
         <v>16.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BF11" t="n">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.7</v>
+        <v>23</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G12" t="n">
         <v>2.46</v>
@@ -2721,7 +2721,7 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
         <v>1.31</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
         <v>2.72</v>
       </c>
       <c r="H13" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J13" t="n">
         <v>2.8</v>
@@ -2924,25 +2924,25 @@
         <v>1.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V13" t="n">
         <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2951,7 +2951,7 @@
         <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
@@ -2966,7 +2966,7 @@
         <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
         <v>970</v>
@@ -2978,7 +2978,7 @@
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
         <v>900</v>
@@ -2987,16 +2987,16 @@
         <v>80</v>
       </c>
       <c r="AL13" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
         <v>9.199999999999999</v>
@@ -3005,10 +3005,10 @@
         <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AT13" t="n">
         <v>5.1</v>
@@ -3020,7 +3020,7 @@
         <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
         <v>7.6</v>
@@ -3029,32 +3029,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB13" t="n">
         <v>6</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BC13" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BD13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BF13" t="n">
         <v>7</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
         <v>7.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G14" t="n">
         <v>4.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J14" t="n">
         <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>1.38</v>
@@ -3115,25 +3115,25 @@
         <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q14" t="n">
         <v>1.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
         <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W14" t="n">
         <v>1.31</v>
@@ -3148,7 +3148,7 @@
         <v>18.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="n">
         <v>32</v>
@@ -3160,7 +3160,7 @@
         <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AF14" t="n">
         <v>80</v>
@@ -3193,10 +3193,10 @@
         <v>85</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR14" t="n">
         <v>9.6</v>
@@ -3208,7 +3208,7 @@
         <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV14" t="n">
         <v>7.4</v>
@@ -3229,16 +3229,16 @@
         <v>16</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BF14" t="n">
         <v>7.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
@@ -3312,7 +3312,7 @@
         <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
@@ -3387,62 +3387,62 @@
         <v>270</v>
       </c>
       <c r="AP15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
         <v>1.02</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
         <v>1.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3524,13 +3524,13 @@
         <v>1.24</v>
       </c>
       <c r="W16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X16" t="n">
         <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
         <v>500</v>
@@ -3545,7 +3545,7 @@
         <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
         <v>500</v>
@@ -3554,10 +3554,10 @@
         <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH16" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
@@ -3581,7 +3581,7 @@
         <v>500</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.64</v>
+        <v>5.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.68</v>
@@ -3605,7 +3605,7 @@
         <v>1.79</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.68</v>
+        <v>5.8</v>
       </c>
       <c r="AY16" t="n">
         <v>1.66</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
         <v>11.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
         <v>21</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -3870,13 +3870,13 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
         <v>1.39</v>
@@ -3885,10 +3885,10 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
         <v>1.82</v>
@@ -3900,7 +3900,7 @@
         <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
         <v>1.79</v>
@@ -3909,7 +3909,7 @@
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
         <v>1.6</v>
@@ -3918,7 +3918,7 @@
         <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
         <v>44</v>
@@ -3951,7 +3951,7 @@
         <v>290</v>
       </c>
       <c r="AJ18" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK18" t="n">
         <v>90</v>
@@ -3978,7 +3978,7 @@
         <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,7 +3990,7 @@
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX18" t="n">
         <v>7.6</v>
@@ -4002,13 +4002,13 @@
         <v>4.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
         <v>4.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD18" t="n">
         <v>5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -4637,34 +4637,34 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
         <v>1.75</v>
@@ -4676,28 +4676,28 @@
         <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
         <v>1.89</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -4706,16 +4706,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AF22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
@@ -4724,7 +4724,7 @@
         <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>170</v>
+        <v>370</v>
       </c>
       <c r="AJ22" t="n">
         <v>28</v>
@@ -4754,7 +4754,7 @@
         <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT22" t="n">
         <v>7</v>
@@ -4766,10 +4766,10 @@
         <v>14.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY22" t="n">
         <v>9.199999999999999</v>
@@ -4778,7 +4778,7 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB22" t="n">
         <v>22</v>
@@ -4787,10 +4787,10 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -4837,13 +4837,13 @@
         <v>2.74</v>
       </c>
       <c r="H23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I23" t="n">
         <v>2.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
         <v>3.9</v>
@@ -4879,7 +4879,7 @@
         <v>2.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W23" t="n">
         <v>1.57</v>
@@ -4963,7 +4963,7 @@
         <v>6.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY23" t="n">
         <v>10.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -5031,13 +5031,13 @@
         <v>1.72</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I24" t="n">
         <v>5.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
         <v>4.6</v>
@@ -5058,7 +5058,7 @@
         <v>2.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R24" t="n">
         <v>1.5</v>
@@ -5070,7 +5070,7 @@
         <v>1.73</v>
       </c>
       <c r="U24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
         <v>1.21</v>
@@ -5091,22 +5091,22 @@
         <v>150</v>
       </c>
       <c r="AB24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC24" t="n">
         <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="AF24" t="n">
         <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH24" t="n">
         <v>19</v>
@@ -5142,7 +5142,7 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT24" t="n">
         <v>9</v>
@@ -5151,10 +5151,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA24" t="n">
         <v>13</v>
@@ -5178,17 +5178,17 @@
         <v>25</v>
       </c>
       <c r="BE24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF24" t="n">
         <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -5225,13 +5225,13 @@
         <v>2.58</v>
       </c>
       <c r="H25" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I25" t="n">
         <v>3.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
@@ -5261,7 +5261,7 @@
         <v>2.92</v>
       </c>
       <c r="T25" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U25" t="n">
         <v>2.28</v>
@@ -5279,7 +5279,7 @@
         <v>970</v>
       </c>
       <c r="Z25" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
@@ -5288,7 +5288,7 @@
         <v>970</v>
       </c>
       <c r="AC25" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AD25" t="n">
         <v>970</v>
@@ -5306,16 +5306,16 @@
         <v>60</v>
       </c>
       <c r="AI25" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ25" t="n">
         <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL25" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
         <v>580</v>
@@ -5324,7 +5324,7 @@
         <v>55</v>
       </c>
       <c r="AO25" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AP25" t="n">
         <v>9</v>
@@ -5336,7 +5336,7 @@
         <v>6.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AT25" t="n">
         <v>9.4</v>
@@ -5348,7 +5348,7 @@
         <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -5360,7 +5360,7 @@
         <v>8.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
         <v>7.2</v>
@@ -5372,17 +5372,17 @@
         <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG25" t="n">
         <v>3.9</v>
       </c>
-      <c r="BG25" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -5419,13 +5419,13 @@
         <v>1.76</v>
       </c>
       <c r="H26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I26" t="n">
         <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
         <v>4.4</v>
@@ -5443,7 +5443,7 @@
         <v>1.27</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
         <v>1.82</v>
@@ -5470,7 +5470,7 @@
         <v>90</v>
       </c>
       <c r="Y26" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="Z26" t="n">
         <v>140</v>
@@ -5485,10 +5485,10 @@
         <v>14</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AE26" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AF26" t="n">
         <v>19.5</v>
@@ -5500,7 +5500,7 @@
         <v>60</v>
       </c>
       <c r="AI26" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ26" t="n">
         <v>48</v>
@@ -5518,7 +5518,7 @@
         <v>29</v>
       </c>
       <c r="AO26" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AP26" t="n">
         <v>9</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G27" t="n">
         <v>2.28</v>
@@ -5625,7 +5625,7 @@
         <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
@@ -5736,7 +5736,7 @@
         <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX27" t="n">
         <v>13</v>
@@ -5757,7 +5757,7 @@
         <v>4</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE27" t="n">
         <v>4.1</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -5813,13 +5813,13 @@
         <v>6.4</v>
       </c>
       <c r="J28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K28" t="n">
         <v>4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
@@ -5831,19 +5831,19 @@
         <v>1.26</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="T28" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U28" t="n">
         <v>2.08</v>
@@ -5915,7 +5915,7 @@
         <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS28" t="n">
         <v>8.6</v>
@@ -5960,11 +5960,11 @@
         <v>7.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>3.75</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6037,7 +6037,7 @@
         <v>3.7</v>
       </c>
       <c r="T29" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U29" t="n">
         <v>1.9</v>
@@ -6115,7 +6115,7 @@
         <v>8.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -6145,7 +6145,7 @@
         <v>17</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE29" t="n">
         <v>8.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -6192,13 +6192,13 @@
         <v>1.42</v>
       </c>
       <c r="G30" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H30" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I30" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="J30" t="n">
         <v>5.1</v>
@@ -6219,13 +6219,13 @@
         <v>1.17</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q30" t="n">
         <v>1.51</v>
       </c>
       <c r="R30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S30" t="n">
         <v>2.3</v>
@@ -6234,16 +6234,16 @@
         <v>1.72</v>
       </c>
       <c r="U30" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W30" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X30" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="Y30" t="n">
         <v>950</v>
@@ -6267,7 +6267,7 @@
         <v>240</v>
       </c>
       <c r="AF30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG30" t="n">
         <v>11</v>
@@ -6303,10 +6303,10 @@
         <v>6.8</v>
       </c>
       <c r="AR30" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS30" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT30" t="n">
         <v>9.800000000000001</v>
@@ -6318,7 +6318,7 @@
         <v>6.8</v>
       </c>
       <c r="AW30" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX30" t="n">
         <v>9</v>
@@ -6330,10 +6330,10 @@
         <v>6.2</v>
       </c>
       <c r="BA30" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC30" t="n">
         <v>12</v>
@@ -6342,7 +6342,7 @@
         <v>6.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF30" t="n">
         <v>4.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G31" t="n">
         <v>3.6</v>
@@ -6398,7 +6398,7 @@
         <v>3.65</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L31" t="n">
         <v>1.3</v>
@@ -6407,7 +6407,7 @@
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O31" t="n">
         <v>1.24</v>
@@ -6419,16 +6419,16 @@
         <v>1.73</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T31" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V31" t="n">
         <v>1.76</v>
@@ -6452,7 +6452,7 @@
         <v>16.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD31" t="n">
         <v>11.5</v>
@@ -6488,7 +6488,7 @@
         <v>34</v>
       </c>
       <c r="AO31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP31" t="n">
         <v>15.5</v>
@@ -6503,7 +6503,7 @@
         <v>14.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU31" t="n">
         <v>7.6</v>
@@ -6527,16 +6527,16 @@
         <v>16</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC31" t="n">
         <v>16</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF31" t="n">
         <v>21</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="I32" t="n">
         <v>1.61</v>
@@ -6718,7 +6718,7 @@
         <v>15.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB32" t="n">
         <v>12</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
         <v>1.75</v>
       </c>
       <c r="U33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
@@ -6828,7 +6828,7 @@
         <v>75</v>
       </c>
       <c r="Y33" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Z33" t="n">
         <v>160</v>
@@ -6843,7 +6843,7 @@
         <v>12</v>
       </c>
       <c r="AD33" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AE33" t="n">
         <v>240</v>
@@ -6897,7 +6897,7 @@
         <v>10</v>
       </c>
       <c r="AV33" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW33" t="n">
         <v>6</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -6977,10 +6977,10 @@
         <v>2.56</v>
       </c>
       <c r="J34" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
         <v>1.47</v>
@@ -7022,10 +7022,10 @@
         <v>11.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA34" t="n">
         <v>38</v>
@@ -7049,7 +7049,7 @@
         <v>16.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI34" t="n">
         <v>120</v>
@@ -7064,7 +7064,7 @@
         <v>70</v>
       </c>
       <c r="AM34" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN34" t="n">
         <v>55</v>
@@ -7085,7 +7085,7 @@
         <v>16</v>
       </c>
       <c r="AT34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU34" t="n">
         <v>6.2</v>
@@ -7106,29 +7106,29 @@
         <v>14.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BC34" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD34" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF34" t="n">
         <v>8.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G35" t="n">
         <v>5.2</v>
       </c>
       <c r="H35" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I35" t="n">
         <v>1.81</v>
@@ -7189,7 +7189,7 @@
         <v>1.17</v>
       </c>
       <c r="P35" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q35" t="n">
         <v>1.51</v>
@@ -7216,7 +7216,7 @@
         <v>34</v>
       </c>
       <c r="Y35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z35" t="n">
         <v>16.5</v>
@@ -7231,7 +7231,7 @@
         <v>12.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE35" t="n">
         <v>19.5</v>
@@ -7258,13 +7258,13 @@
         <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN35" t="n">
         <v>38</v>
       </c>
       <c r="AO35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP35" t="n">
         <v>13</v>
@@ -7273,7 +7273,7 @@
         <v>11.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AS35" t="n">
         <v>14.5</v>
@@ -7282,16 +7282,16 @@
         <v>20</v>
       </c>
       <c r="AU35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AW35" t="n">
         <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>18</v>
+        <v>5.2</v>
       </c>
       <c r="AY35" t="n">
         <v>15.5</v>
@@ -7303,16 +7303,16 @@
         <v>18.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE35" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="BF35" t="n">
         <v>5.3</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>3.05</v>
       </c>
       <c r="I37" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
@@ -7607,13 +7607,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA37" t="n">
         <v>900</v>
       </c>
       <c r="AB37" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC37" t="n">
         <v>7.8</v>
@@ -7634,7 +7634,7 @@
         <v>27</v>
       </c>
       <c r="AI37" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AJ37" t="n">
         <v>55</v>
@@ -7646,16 +7646,16 @@
         <v>170</v>
       </c>
       <c r="AM37" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN37" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO37" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP37" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ37" t="n">
         <v>7.2</v>
@@ -7664,7 +7664,7 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT37" t="n">
         <v>6.4</v>
@@ -7676,7 +7676,7 @@
         <v>13</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="AX37" t="n">
         <v>13</v>
@@ -7688,29 +7688,29 @@
         <v>19.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB37" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BC37" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BD37" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE37" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF37" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G38" t="n">
         <v>1.6</v>
@@ -7792,7 +7792,7 @@
         <v>1.11</v>
       </c>
       <c r="W38" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X38" t="n">
         <v>10</v>
@@ -7822,7 +7822,7 @@
         <v>8</v>
       </c>
       <c r="AG38" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH38" t="n">
         <v>150</v>
@@ -7855,10 +7855,10 @@
         <v>17</v>
       </c>
       <c r="AR38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT38" t="n">
         <v>4.9</v>
@@ -7870,7 +7870,7 @@
         <v>16</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX38" t="n">
         <v>6.6</v>
@@ -7882,7 +7882,7 @@
         <v>25</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB38" t="n">
         <v>12</v>
@@ -7894,17 +7894,17 @@
         <v>6.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF38" t="n">
         <v>11.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
         <v>2.5</v>
       </c>
       <c r="H39" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I39" t="n">
         <v>3.8</v>
@@ -8028,7 +8028,7 @@
         <v>85</v>
       </c>
       <c r="AK39" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AL39" t="n">
         <v>290</v>
@@ -8052,7 +8052,7 @@
         <v>19</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT39" t="n">
         <v>7.4</v>
@@ -8064,7 +8064,7 @@
         <v>12.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX39" t="n">
         <v>6</v>
@@ -8094,11 +8094,11 @@
         <v>7.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -8135,22 +8135,22 @@
         <v>2.6</v>
       </c>
       <c r="H40" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I40" t="n">
         <v>3.8</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K40" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L40" t="n">
         <v>1.59</v>
       </c>
       <c r="M40" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N40" t="n">
         <v>2.16</v>
@@ -8171,7 +8171,7 @@
         <v>6.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U40" t="n">
         <v>1.58</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
         <v>2.16</v>
       </c>
       <c r="V41" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W41" t="n">
         <v>3.35</v>
@@ -8392,7 +8392,7 @@
         <v>13.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD41" t="n">
         <v>36</v>
@@ -8425,22 +8425,22 @@
         <v>110</v>
       </c>
       <c r="AN41" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO41" t="n">
         <v>120</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ41" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT41" t="n">
         <v>10</v>
@@ -8449,13 +8449,13 @@
         <v>11.5</v>
       </c>
       <c r="AV41" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX41" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY41" t="n">
         <v>9.199999999999999</v>
@@ -8464,7 +8464,7 @@
         <v>19.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB41" t="n">
         <v>11</v>
@@ -8476,17 +8476,17 @@
         <v>21</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF41" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG41" t="n">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -8520,16 +8520,16 @@
         <v>2.18</v>
       </c>
       <c r="G42" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H42" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J42" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K42" t="n">
         <v>3.55</v>
@@ -8541,7 +8541,7 @@
         <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>1.4</v>
@@ -8550,28 +8550,28 @@
         <v>1.69</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R42" t="n">
         <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U42" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="V42" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W42" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X42" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y42" t="n">
         <v>12.5</v>
@@ -8580,7 +8580,7 @@
         <v>27</v>
       </c>
       <c r="AA42" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AB42" t="n">
         <v>8.800000000000001</v>
@@ -8607,34 +8607,34 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK42" t="n">
         <v>28</v>
       </c>
       <c r="AL42" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM42" t="n">
         <v>580</v>
       </c>
       <c r="AN42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO42" t="n">
         <v>65</v>
       </c>
       <c r="AP42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AR42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS42" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT42" t="n">
         <v>7.4</v>
@@ -8643,44 +8643,44 @@
         <v>6.6</v>
       </c>
       <c r="AV42" t="n">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX42" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ42" t="n">
         <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB42" t="n">
         <v>6.8</v>
       </c>
       <c r="BC42" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF42" t="n">
         <v>20</v>
       </c>
       <c r="BG42" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
         <v>4.3</v>
       </c>
       <c r="K43" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
         <v>1.41</v>
@@ -8777,10 +8777,10 @@
         <v>490</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD43" t="n">
         <v>44</v>
@@ -8789,7 +8789,7 @@
         <v>230</v>
       </c>
       <c r="AF43" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG43" t="n">
         <v>12.5</v>
@@ -8801,10 +8801,10 @@
         <v>540</v>
       </c>
       <c r="AJ43" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL43" t="n">
         <v>60</v>
@@ -8813,22 +8813,22 @@
         <v>260</v>
       </c>
       <c r="AN43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO43" t="n">
         <v>400</v>
       </c>
       <c r="AP43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ43" t="n">
         <v>18</v>
       </c>
       <c r="AR43" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT43" t="n">
         <v>5.6</v>
@@ -8840,7 +8840,7 @@
         <v>14.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX43" t="n">
         <v>6.6</v>
@@ -8852,7 +8852,7 @@
         <v>14.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB43" t="n">
         <v>11</v>
@@ -8861,20 +8861,20 @@
         <v>15.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF43" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.6</v>
+        <v>15</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -8908,10 +8908,10 @@
         <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="H44" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I44" t="n">
         <v>4.9</v>
@@ -8920,7 +8920,7 @@
         <v>2.96</v>
       </c>
       <c r="K44" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L44" t="n">
         <v>1.32</v>
@@ -8932,7 +8932,7 @@
         <v>2.92</v>
       </c>
       <c r="O44" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P44" t="n">
         <v>1.76</v>
@@ -8956,7 +8956,7 @@
         <v>1.25</v>
       </c>
       <c r="W44" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X44" t="n">
         <v>90</v>
@@ -8998,7 +8998,7 @@
         <v>900</v>
       </c>
       <c r="AK44" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AL44" t="n">
         <v>180</v>
@@ -9013,52 +9013,52 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT44" t="n">
         <v>1.18</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AU44" t="n">
         <v>1.18</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AV44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AY44" t="n">
         <v>1.18</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AZ44" t="n">
         <v>1.19</v>
       </c>
-      <c r="AT44" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AX44" t="n">
+      <c r="BA44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BB44" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.19</v>
       </c>
       <c r="BC44" t="n">
         <v>1.19</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BF44" t="n">
         <v>1.55</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -9099,16 +9099,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G45" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H45" t="n">
         <v>2.72</v>
       </c>
       <c r="I45" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J45" t="n">
         <v>3</v>
@@ -9117,7 +9117,7 @@
         <v>3.3</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
@@ -9141,16 +9141,16 @@
         <v>4.1</v>
       </c>
       <c r="T45" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U45" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V45" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W45" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X45" t="n">
         <v>13</v>
@@ -9228,7 +9228,7 @@
         <v>11</v>
       </c>
       <c r="AW45" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX45" t="n">
         <v>16</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
         <v>1.26</v>
       </c>
       <c r="S46" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
         <v>1.87</v>
@@ -9350,16 +9350,16 @@
         <v>23</v>
       </c>
       <c r="Y46" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Z46" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AA46" t="n">
         <v>900</v>
       </c>
       <c r="AB46" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="AC46" t="n">
         <v>14</v>
@@ -9368,7 +9368,7 @@
         <v>970</v>
       </c>
       <c r="AE46" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AF46" t="n">
         <v>970</v>
@@ -9377,86 +9377,86 @@
         <v>970</v>
       </c>
       <c r="AH46" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI46" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AJ46" t="n">
         <v>900</v>
       </c>
       <c r="AK46" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL46" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM46" t="n">
         <v>580</v>
       </c>
       <c r="AN46" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AO46" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP46" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ46" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>5.9</v>
+        <v>21</v>
       </c>
       <c r="AS46" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV46" t="n">
         <v>6</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="AW46" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ46" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU46" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BA46" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB46" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BC46" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="BD46" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG46" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G47" t="n">
         <v>2.46</v>
@@ -9496,13 +9496,13 @@
         <v>3.25</v>
       </c>
       <c r="I47" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J47" t="n">
         <v>3.05</v>
       </c>
       <c r="K47" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L47" t="n">
         <v>1.38</v>
@@ -9541,10 +9541,10 @@
         <v>1.68</v>
       </c>
       <c r="X47" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y47" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z47" t="n">
         <v>500</v>
@@ -9553,13 +9553,13 @@
         <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC47" t="n">
         <v>500</v>
       </c>
       <c r="AD47" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE47" t="n">
         <v>500</v>
@@ -9568,10 +9568,10 @@
         <v>500</v>
       </c>
       <c r="AG47" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH47" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI47" t="n">
         <v>500</v>
@@ -9613,7 +9613,7 @@
         <v>1.15</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AW47" t="n">
         <v>1.18</v>
@@ -9640,7 +9640,7 @@
         <v>1.18</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BF47" t="n">
         <v>1.55</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
         <v>4.4</v>
       </c>
       <c r="I48" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J48" t="n">
         <v>5.8</v>
@@ -9738,25 +9738,25 @@
         <v>70</v>
       </c>
       <c r="Y48" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z48" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA48" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB48" t="n">
         <v>29</v>
       </c>
       <c r="AC48" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AD48" t="n">
         <v>22</v>
       </c>
       <c r="AE48" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF48" t="n">
         <v>22</v>
@@ -9783,16 +9783,16 @@
         <v>32</v>
       </c>
       <c r="AN48" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AO48" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP48" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AQ48" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AR48" t="n">
         <v>50</v>
@@ -9804,7 +9804,7 @@
         <v>28</v>
       </c>
       <c r="AU48" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AV48" t="n">
         <v>21</v>
@@ -9816,7 +9816,7 @@
         <v>21</v>
       </c>
       <c r="AY48" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ48" t="n">
         <v>15.5</v>
@@ -9825,7 +9825,7 @@
         <v>28</v>
       </c>
       <c r="BB48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC48" t="n">
         <v>14</v>
@@ -9834,17 +9834,17 @@
         <v>16.5</v>
       </c>
       <c r="BE48" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF48" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BG48" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -9905,7 +9905,7 @@
         <v>1.3</v>
       </c>
       <c r="P49" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q49" t="n">
         <v>2.72</v>
@@ -9914,7 +9914,7 @@
         <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="T49" t="n">
         <v>1.11</v>
@@ -9929,116 +9929,116 @@
         <v>1.28</v>
       </c>
       <c r="X49" t="n">
-        <v>90</v>
+        <v>9.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB49" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF49" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG49" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH49" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI49" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ49" t="n">
         <v>900</v>
       </c>
       <c r="AK49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.12</v>
+        <v>5.9</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.13</v>
+        <v>5.6</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.13</v>
+        <v>11</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.13</v>
+        <v>5.2</v>
       </c>
       <c r="AT49" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.13</v>
+        <v>5.3</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.13</v>
+        <v>9.6</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.13</v>
+        <v>5.2</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.13</v>
+        <v>16.5</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.13</v>
+        <v>17.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.13</v>
+        <v>5.4</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.13</v>
+        <v>5.7</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.55</v>
+        <v>5.3</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10174,7 @@
         <v>500</v>
       </c>
       <c r="AO50" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP50" t="n">
         <v>8.800000000000001</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -10266,13 +10266,13 @@
         <v>3.4</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H51" t="n">
         <v>2.4</v>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J51" t="n">
         <v>3.25</v>
@@ -10317,7 +10317,7 @@
         <v>1.39</v>
       </c>
       <c r="X51" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="Y51" t="n">
         <v>19</v>
@@ -10335,7 +10335,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD51" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AE51" t="n">
         <v>140</v>
@@ -10371,16 +10371,16 @@
         <v>110</v>
       </c>
       <c r="AP51" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AQ51" t="n">
         <v>6</v>
       </c>
       <c r="AR51" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AT51" t="n">
         <v>5.1</v>
@@ -10395,38 +10395,38 @@
         <v>16</v>
       </c>
       <c r="AX51" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AY51" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AZ51" t="n">
         <v>18.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB51" t="n">
         <v>7.6</v>
       </c>
       <c r="BC51" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD51" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE51" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF51" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG51" t="n">
         <v>6.8</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -10457,52 +10457,52 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G52" t="n">
         <v>2.56</v>
       </c>
       <c r="H52" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I52" t="n">
         <v>3.55</v>
       </c>
       <c r="J52" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K52" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N52" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="O52" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P52" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="R52" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S52" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="T52" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="U52" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="V52" t="n">
         <v>1.39</v>
@@ -10514,25 +10514,25 @@
         <v>11.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z52" t="n">
         <v>23</v>
       </c>
       <c r="AA52" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AB52" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC52" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD52" t="n">
         <v>15.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF52" t="n">
         <v>17</v>
@@ -10541,16 +10541,16 @@
         <v>12.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI52" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ52" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK52" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL52" t="n">
         <v>55</v>
@@ -10559,25 +10559,25 @@
         <v>150</v>
       </c>
       <c r="AN52" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO52" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP52" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ52" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR52" t="n">
         <v>19</v>
       </c>
       <c r="AS52" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT52" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU52" t="n">
         <v>6.6</v>
@@ -10586,7 +10586,7 @@
         <v>12</v>
       </c>
       <c r="AW52" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AX52" t="n">
         <v>13</v>
@@ -10595,32 +10595,32 @@
         <v>10</v>
       </c>
       <c r="AZ52" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA52" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB52" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC52" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BD52" t="n">
         <v>40</v>
       </c>
       <c r="BE52" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF52" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BG52" t="n">
         <v>36</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
         <v>3.05</v>
       </c>
       <c r="H53" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I53" t="n">
         <v>2.9</v>
@@ -10669,22 +10669,22 @@
         <v>3.35</v>
       </c>
       <c r="L53" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M53" t="n">
         <v>1.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O53" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P53" t="n">
         <v>1.55</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="R53" t="n">
         <v>1.2</v>
@@ -10693,7 +10693,7 @@
         <v>5.4</v>
       </c>
       <c r="T53" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U53" t="n">
         <v>1.78</v>
@@ -10705,25 +10705,25 @@
         <v>1.48</v>
       </c>
       <c r="X53" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y53" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z53" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AA53" t="n">
         <v>55</v>
       </c>
       <c r="AB53" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC53" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE53" t="n">
         <v>44</v>
@@ -10756,19 +10756,19 @@
         <v>60</v>
       </c>
       <c r="AO53" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP53" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ53" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR53" t="n">
         <v>14.5</v>
       </c>
       <c r="AS53" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AT53" t="n">
         <v>7.4</v>
@@ -10780,10 +10780,10 @@
         <v>11.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="AX53" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="AY53" t="n">
         <v>12.5</v>
@@ -10792,29 +10792,29 @@
         <v>21</v>
       </c>
       <c r="BA53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BB53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BC53" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BE53" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF53" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG53" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -10845,22 +10845,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="G54" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="H54" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J54" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K54" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L54" t="n">
         <v>1.3</v>
@@ -10875,7 +10875,7 @@
         <v>1.25</v>
       </c>
       <c r="P54" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q54" t="n">
         <v>1.73</v>
@@ -10884,31 +10884,31 @@
         <v>1.46</v>
       </c>
       <c r="S54" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T54" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U54" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V54" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W54" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X54" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y54" t="n">
         <v>16.5</v>
       </c>
       <c r="Z54" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA54" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB54" t="n">
         <v>14.5</v>
@@ -10917,10 +10917,10 @@
         <v>10</v>
       </c>
       <c r="AD54" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF54" t="n">
         <v>20</v>
@@ -10929,10 +10929,10 @@
         <v>13.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI54" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ54" t="n">
         <v>38</v>
@@ -10944,13 +10944,13 @@
         <v>40</v>
       </c>
       <c r="AM54" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN54" t="n">
         <v>19</v>
       </c>
       <c r="AO54" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AP54" t="n">
         <v>14</v>
@@ -10962,10 +10962,10 @@
         <v>17</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT54" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU54" t="n">
         <v>6.8</v>
@@ -10974,7 +10974,7 @@
         <v>10.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>24</v>
+        <v>5.4</v>
       </c>
       <c r="AX54" t="n">
         <v>15</v>
@@ -10986,19 +10986,19 @@
         <v>12</v>
       </c>
       <c r="BA54" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB54" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC54" t="n">
         <v>18.5</v>
       </c>
       <c r="BD54" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE54" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF54" t="n">
         <v>12.5</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -11039,13 +11039,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G55" t="n">
         <v>1.54</v>
       </c>
       <c r="H55" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I55" t="n">
         <v>7</v>
@@ -11054,10 +11054,10 @@
         <v>4.8</v>
       </c>
       <c r="K55" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L55" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="M55" t="n">
         <v>1.03</v>
@@ -11078,13 +11078,13 @@
         <v>1.65</v>
       </c>
       <c r="S55" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T55" t="n">
         <v>1.74</v>
       </c>
       <c r="U55" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V55" t="n">
         <v>1.16</v>
@@ -11096,7 +11096,7 @@
         <v>25</v>
       </c>
       <c r="Y55" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Z55" t="n">
         <v>65</v>
@@ -11117,7 +11117,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG55" t="n">
         <v>11.5</v>
@@ -11150,10 +11150,10 @@
         <v>21</v>
       </c>
       <c r="AQ55" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR55" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS55" t="n">
         <v>46</v>
@@ -11165,13 +11165,13 @@
         <v>10.5</v>
       </c>
       <c r="AV55" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW55" t="n">
         <v>34</v>
       </c>
       <c r="AX55" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY55" t="n">
         <v>9.4</v>
@@ -11180,7 +11180,7 @@
         <v>18</v>
       </c>
       <c r="BA55" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB55" t="n">
         <v>12.5</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
         <v>19</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT56" t="n">
         <v>6.4</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -11436,13 +11436,13 @@
         <v>2.48</v>
       </c>
       <c r="I57" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="J57" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K57" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L57" t="n">
         <v>1.41</v>
@@ -11454,37 +11454,37 @@
         <v>3.15</v>
       </c>
       <c r="O57" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P57" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R57" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T57" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U57" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V57" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W57" t="n">
         <v>1.42</v>
       </c>
       <c r="X57" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y57" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z57" t="n">
         <v>18.5</v>
@@ -11499,22 +11499,22 @@
         <v>7.8</v>
       </c>
       <c r="AD57" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE57" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF57" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH57" t="n">
         <v>21</v>
       </c>
       <c r="AI57" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ57" t="n">
         <v>60</v>
@@ -11529,19 +11529,19 @@
         <v>140</v>
       </c>
       <c r="AN57" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO57" t="n">
         <v>32</v>
       </c>
       <c r="AP57" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ57" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR57" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS57" t="n">
         <v>6.4</v>
@@ -11550,16 +11550,16 @@
         <v>9.4</v>
       </c>
       <c r="AU57" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV57" t="n">
         <v>10.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX57" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY57" t="n">
         <v>11.5</v>
@@ -11574,23 +11574,23 @@
         <v>36</v>
       </c>
       <c r="BC57" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG57" t="n">
         <v>6</v>
       </c>
-      <c r="BD57" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-05 20:26:03</t>
+          <t>2026-05-05 22:36:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH58"/>
+  <dimension ref="A1:BH59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
         <v>2.52</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
         <v>1.66</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
         <v>22</v>
@@ -823,13 +823,13 @@
         <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC2" t="n">
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>34</v>
@@ -859,22 +859,22 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -889,10 +889,10 @@
         <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>14</v>
@@ -910,17 +910,17 @@
         <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF2" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
         <v>25</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
         <v>1.9</v>
@@ -1059,28 +1059,28 @@
         <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="AU3" t="n">
         <v>5.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AX3" t="n">
         <v>2.8</v>
@@ -1089,32 +1089,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="BE3" t="n">
         <v>2.96</v>
       </c>
       <c r="BF3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="n">
         <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
@@ -1178,13 +1178,13 @@
         <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
         <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
         <v>1.79</v>
@@ -1193,7 +1193,7 @@
         <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
         <v>2.42</v>
@@ -1202,16 +1202,16 @@
         <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
@@ -1220,28 +1220,28 @@
         <v>20</v>
       </c>
       <c r="AE4" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AF4" t="n">
         <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AJ4" t="n">
         <v>17.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1262,7 +1262,7 @@
         <v>34</v>
       </c>
       <c r="AS4" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
         <v>9</v>
@@ -1271,7 +1271,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>46</v>
@@ -1286,7 +1286,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB4" t="n">
         <v>14.5</v>
@@ -1304,11 +1304,11 @@
         <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
@@ -1357,7 +1357,7 @@
         <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
@@ -1369,16 +1369,16 @@
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
         <v>1.65</v>
@@ -1390,97 +1390,97 @@
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X5" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y5" t="n">
         <v>27</v>
       </c>
-      <c r="Y5" t="n">
-        <v>40</v>
-      </c>
       <c r="Z5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
         <v>700</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
         <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>130</v>
+        <v>320</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
         <v>18.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AP5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AR5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BB5" t="n">
         <v>15</v>
@@ -1492,17 +1492,17 @@
         <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G6" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="H6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I6" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.25</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -1551,112 +1551,112 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S6" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U6" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="X6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y6" t="n">
         <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AF6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI6" t="n">
         <v>32</v>
       </c>
       <c r="AJ6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
         <v>24</v>
       </c>
       <c r="AQ6" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AR6" t="n">
         <v>23</v>
       </c>
       <c r="AS6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV6" t="n">
         <v>13</v>
@@ -1665,38 +1665,38 @@
         <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
@@ -1748,7 +1748,7 @@
         <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
@@ -1757,22 +1757,22 @@
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
         <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.94</v>
       </c>
       <c r="U7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1787,19 +1787,19 @@
         <v>25</v>
       </c>
       <c r="Z7" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA7" t="n">
         <v>270</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE7" t="n">
         <v>480</v>
@@ -1817,10 +1817,10 @@
         <v>390</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
         <v>38</v>
@@ -1829,7 +1829,7 @@
         <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO7" t="n">
         <v>170</v>
@@ -1838,59 +1838,59 @@
         <v>14.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT7" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
         <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>13.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="G8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC8" t="n">
         <v>9.4</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>42</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.02</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.02</v>
+        <v>6.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.02</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.02</v>
+        <v>14</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.02</v>
+        <v>15.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.02</v>
+        <v>8.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.02</v>
+        <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.02</v>
+        <v>21</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.02</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.02</v>
+        <v>34</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.02</v>
+        <v>6.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.02</v>
+        <v>6.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.02</v>
+        <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.02</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -2118,167 +2118,167 @@
         <v>2.72</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I9" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.33</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.3</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
         <v>13.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL9" t="n">
         <v>50</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>32</v>
       </c>
       <c r="AO9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
         <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="BB9" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="I10" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.32</v>
@@ -2342,13 +2342,13 @@
         <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
         <v>1.73</v>
@@ -2357,10 +2357,10 @@
         <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
         <v>19</v>
@@ -2441,7 +2441,7 @@
         <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY10" t="n">
         <v>11</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -2506,22 +2506,22 @@
         <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -2530,7 +2530,7 @@
         <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
         <v>1.73</v>
@@ -2545,16 +2545,16 @@
         <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
@@ -2569,13 +2569,13 @@
         <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
         <v>44</v>
@@ -2587,7 +2587,7 @@
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>60</v>
@@ -2599,13 +2599,13 @@
         <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO11" t="n">
         <v>46</v>
@@ -2614,25 +2614,25 @@
         <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU11" t="n">
         <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX11" t="n">
         <v>13.5</v>
@@ -2644,29 +2644,29 @@
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.32</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.31</v>
-      </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
         <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="X12" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>440</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AJ12" t="n">
         <v>85</v>
       </c>
       <c r="AK12" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.86</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -2891,61 +2891,61 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
         <v>3.7</v>
       </c>
       <c r="L13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.36</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.35</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
         <v>970</v>
@@ -2954,13 +2954,13 @@
         <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
         <v>970</v>
@@ -2978,7 +2978,7 @@
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ13" t="n">
         <v>900</v>
@@ -2990,13 +2990,13 @@
         <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
         <v>9.199999999999999</v>
@@ -3008,7 +3008,7 @@
         <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
         <v>5.1</v>
@@ -3029,32 +3029,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB13" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6</v>
       </c>
       <c r="BC13" t="n">
         <v>7.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>3.65</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H14" t="n">
         <v>2.02</v>
       </c>
       <c r="I14" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>1.38</v>
@@ -3109,22 +3109,22 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="R14" t="n">
         <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
         <v>1.81</v>
@@ -3133,34 +3133,34 @@
         <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X14" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="Y14" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AA14" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB14" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AF14" t="n">
         <v>80</v>
@@ -3169,7 +3169,7 @@
         <v>500</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -3187,40 +3187,40 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.64</v>
+        <v>8.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS14" t="n">
         <v>11.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
         <v>10.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>9</v>
@@ -3229,26 +3229,26 @@
         <v>16</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.78</v>
+        <v>8.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.78</v>
+        <v>8</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.82</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="I15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.27</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V15" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>19</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
         <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>270</v>
+        <v>5.7</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.02</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.9</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H16" t="n">
         <v>4.2</v>
@@ -3491,152 +3491,152 @@
         <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="V16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AF16" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.68</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.76</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.73</v>
+        <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.79</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.66</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.75</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.79</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.76</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.75</v>
+        <v>20</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.79</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.79</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.78</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
         <v>2.36</v>
@@ -3697,13 +3697,13 @@
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
         <v>2.62</v>
@@ -3715,7 +3715,7 @@
         <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.73</v>
@@ -3730,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AA17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
         <v>13.5</v>
@@ -3739,10 +3739,10 @@
         <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
         <v>17</v>
@@ -3784,25 +3784,25 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="AX17" t="n">
         <v>13</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
         <v>11.5</v>
@@ -3814,13 +3814,13 @@
         <v>21</v>
       </c>
       <c r="BC17" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BF17" t="n">
         <v>9.800000000000001</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3864,16 @@
         <v>2.42</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J18" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
         <v>3.95</v>
@@ -3894,7 +3894,7 @@
         <v>1.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R18" t="n">
         <v>1.31</v>
@@ -3903,13 +3903,13 @@
         <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
         <v>1.6</v>
@@ -3921,34 +3921,34 @@
         <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI18" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
         <v>130</v>
@@ -3960,13 +3960,13 @@
         <v>290</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO18" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP18" t="n">
         <v>9.4</v>
@@ -3978,7 +3978,7 @@
         <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,7 +3990,7 @@
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX18" t="n">
         <v>7.6</v>
@@ -3999,32 +3999,32 @@
         <v>7</v>
       </c>
       <c r="AZ18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE18" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BF18" t="n">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="BG18" t="n">
         <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -4055,61 +4055,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="G19" t="n">
-        <v>990</v>
+        <v>2.26</v>
       </c>
       <c r="H19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O19" t="n">
         <v>1.36</v>
       </c>
-      <c r="I19" t="n">
-        <v>85</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.25</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.16</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Y19" t="n">
         <v>950</v>
@@ -4118,13 +4118,13 @@
         <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC19" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AD19" t="n">
         <v>950</v>
@@ -4133,92 +4133,92 @@
         <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
         <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.05</v>
+        <v>5.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.05</v>
+        <v>3.7</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.05</v>
+        <v>4.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.05</v>
+        <v>5.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.05</v>
+        <v>5.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="G20" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="I20" t="n">
-        <v>10.5</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W20" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X20" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y20" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD20" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AF20" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AJ20" t="n">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AK20" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AL20" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM20" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO20" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AP20" t="n">
         <v>5.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.73</v>
+        <v>6</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU20" t="n">
         <v>4.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.64</v>
+        <v>4.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.72</v>
+        <v>5.9</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.64</v>
+        <v>4.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.74</v>
+        <v>6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.73</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.72</v>
+        <v>5.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.74</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.74</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.74</v>
+        <v>6.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.74</v>
+        <v>5.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O21" t="n">
         <v>1.19</v>
@@ -4485,10 +4485,10 @@
         <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V21" t="n">
         <v>1.14</v>
@@ -4560,7 +4560,7 @@
         <v>4.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
         <v>370</v>
       </c>
       <c r="AF22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
@@ -4754,7 +4754,7 @@
         <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
         <v>7</v>
@@ -4766,19 +4766,19 @@
         <v>14.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB22" t="n">
         <v>22</v>
@@ -4787,20 +4787,20 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="BE22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -4834,16 +4834,16 @@
         <v>2.66</v>
       </c>
       <c r="G23" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H23" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I23" t="n">
         <v>2.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
         <v>3.9</v>
@@ -4879,7 +4879,7 @@
         <v>2.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W23" t="n">
         <v>1.57</v>
@@ -4939,16 +4939,16 @@
         <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23" t="n">
         <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AT23" t="n">
         <v>11</v>
@@ -4972,16 +4972,16 @@
         <v>5.8</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BE23" t="n">
         <v>8.199999999999999</v>
@@ -4990,11 +4990,11 @@
         <v>6.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
         <v>1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
         <v>4.6</v>
@@ -5058,7 +5058,7 @@
         <v>2.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R24" t="n">
         <v>1.5</v>
@@ -5082,7 +5082,7 @@
         <v>26</v>
       </c>
       <c r="Y24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z24" t="n">
         <v>46</v>
@@ -5136,16 +5136,16 @@
         <v>17.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
         <v>12</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU24" t="n">
         <v>8.800000000000001</v>
@@ -5154,7 +5154,7 @@
         <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
@@ -5166,7 +5166,7 @@
         <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
         <v>15.5</v>
@@ -5184,11 +5184,11 @@
         <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
         <v>6.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT25" t="n">
         <v>9.4</v>
@@ -5360,7 +5360,7 @@
         <v>8.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BB25" t="n">
         <v>7.2</v>
@@ -5375,14 +5375,14 @@
         <v>8.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BG25" t="n">
         <v>3.9</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -5521,10 +5521,10 @@
         <v>700</v>
       </c>
       <c r="AP26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR26" t="n">
         <v>8.6</v>
@@ -5533,7 +5533,7 @@
         <v>4</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU26" t="n">
         <v>8.199999999999999</v>
@@ -5542,7 +5542,7 @@
         <v>7.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.4</v>
+        <v>23</v>
       </c>
       <c r="AX26" t="n">
         <v>5.6</v>
@@ -5551,7 +5551,7 @@
         <v>5.8</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
         <v>9.199999999999999</v>
@@ -5560,7 +5560,7 @@
         <v>12</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
         <v>16</v>
@@ -5569,14 +5569,14 @@
         <v>4</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>2.08</v>
       </c>
       <c r="G27" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J27" t="n">
         <v>3.6</v>
@@ -5736,7 +5736,7 @@
         <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AX27" t="n">
         <v>13</v>
@@ -5757,7 +5757,7 @@
         <v>4</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
         <v>4.1</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
         <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R28" t="n">
         <v>1.41</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>3.75</v>
       </c>
       <c r="L29" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6112,7 +6112,7 @@
         <v>7.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT29" t="n">
         <v>6.8</v>
@@ -6124,7 +6124,7 @@
         <v>13.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX29" t="n">
         <v>8.6</v>
@@ -6133,10 +6133,10 @@
         <v>8</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB29" t="n">
         <v>17</v>
@@ -6145,20 +6145,20 @@
         <v>17</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF29" t="n">
         <v>13</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -6192,13 +6192,13 @@
         <v>1.42</v>
       </c>
       <c r="G30" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I30" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J30" t="n">
         <v>5.1</v>
@@ -6213,7 +6213,7 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
         <v>1.17</v>
@@ -6237,7 +6237,7 @@
         <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W30" t="n">
         <v>3.05</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
         <v>1.76</v>
       </c>
       <c r="W31" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X31" t="n">
         <v>19.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BD34" t="n">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="BE34" t="n">
         <v>9.199999999999999</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G35" t="n">
         <v>5.2</v>
@@ -7174,7 +7174,7 @@
         <v>4.2</v>
       </c>
       <c r="K35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L35" t="n">
         <v>1.22</v>
@@ -7192,10 +7192,10 @@
         <v>2.66</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R35" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S35" t="n">
         <v>2.22</v>
@@ -7249,7 +7249,7 @@
         <v>32</v>
       </c>
       <c r="AJ35" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AK35" t="n">
         <v>60</v>
@@ -7264,10 +7264,10 @@
         <v>38</v>
       </c>
       <c r="AO35" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AP35" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AQ35" t="n">
         <v>11.5</v>
@@ -7291,7 +7291,7 @@
         <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY35" t="n">
         <v>15.5</v>
@@ -7303,16 +7303,16 @@
         <v>18.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC35" t="n">
-        <v>20</v>
+        <v>5.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>23</v>
+        <v>5.9</v>
       </c>
       <c r="BF35" t="n">
         <v>5.3</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -7353,61 +7353,61 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H36" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I36" t="n">
         <v>3.85</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K36" t="n">
         <v>3.8</v>
       </c>
       <c r="L36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M36" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O36" t="n">
         <v>1.36</v>
       </c>
       <c r="P36" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
         <v>3.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U36" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V36" t="n">
         <v>1.35</v>
       </c>
       <c r="W36" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X36" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y36" t="n">
         <v>970</v>
@@ -7437,7 +7437,7 @@
         <v>970</v>
       </c>
       <c r="AH36" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI36" t="n">
         <v>500</v>
@@ -7461,62 +7461,62 @@
         <v>500</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AT36" t="n">
         <v>6.8</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AW36" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AX36" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="AY36" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="BA36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BF36" t="n">
         <v>3.65</v>
       </c>
-      <c r="BB36" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG36" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>3.05</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G38" t="n">
         <v>1.6</v>
       </c>
       <c r="H38" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I38" t="n">
         <v>10</v>
@@ -7792,7 +7792,7 @@
         <v>1.11</v>
       </c>
       <c r="W38" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X38" t="n">
         <v>10</v>
@@ -7855,7 +7855,7 @@
         <v>17</v>
       </c>
       <c r="AR38" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS38" t="n">
         <v>6.8</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G39" t="n">
         <v>2.5</v>
@@ -7950,7 +7950,7 @@
         <v>2.98</v>
       </c>
       <c r="K39" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L39" t="n">
         <v>1.46</v>
@@ -8007,7 +8007,7 @@
         <v>7.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AE39" t="n">
         <v>370</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -8135,22 +8135,22 @@
         <v>2.6</v>
       </c>
       <c r="H40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I40" t="n">
         <v>3.8</v>
       </c>
       <c r="J40" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L40" t="n">
         <v>1.59</v>
       </c>
       <c r="M40" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N40" t="n">
         <v>2.16</v>
@@ -8171,7 +8171,7 @@
         <v>6.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U40" t="n">
         <v>1.58</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -8431,13 +8431,13 @@
         <v>120</v>
       </c>
       <c r="AP41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ41" t="n">
         <v>34</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS41" t="n">
         <v>5.9</v>
@@ -8482,11 +8482,11 @@
         <v>4.2</v>
       </c>
       <c r="BG41" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G42" t="n">
         <v>2.34</v>
@@ -8529,7 +8529,7 @@
         <v>4.2</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K42" t="n">
         <v>3.55</v>
@@ -8589,7 +8589,7 @@
         <v>7.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE42" t="n">
         <v>55</v>
@@ -8625,16 +8625,16 @@
         <v>65</v>
       </c>
       <c r="AP42" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ42" t="n">
         <v>10</v>
       </c>
       <c r="AR42" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS42" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT42" t="n">
         <v>7.4</v>
@@ -8646,41 +8646,41 @@
         <v>14.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX42" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ42" t="n">
         <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB42" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC42" t="n">
         <v>7.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF42" t="n">
         <v>20</v>
       </c>
       <c r="BG42" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
         <v>5</v>
       </c>
       <c r="L43" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M43" t="n">
         <v>1.07</v>
@@ -8750,7 +8750,7 @@
         <v>1.31</v>
       </c>
       <c r="S43" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T43" t="n">
         <v>2.26</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
         <v>2.36</v>
       </c>
       <c r="H44" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I44" t="n">
         <v>4.9</v>
@@ -8920,7 +8920,7 @@
         <v>2.96</v>
       </c>
       <c r="K44" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L44" t="n">
         <v>1.32</v>
@@ -8959,40 +8959,40 @@
         <v>1.73</v>
       </c>
       <c r="X44" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y44" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="Z44" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA44" t="n">
         <v>900</v>
       </c>
       <c r="AB44" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AC44" t="n">
         <v>95</v>
       </c>
       <c r="AD44" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AE44" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG44" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AH44" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AI44" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AJ44" t="n">
         <v>900</v>
@@ -9001,64 +9001,64 @@
         <v>150</v>
       </c>
       <c r="AL44" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AM44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ44" t="n">
         <v>1.2</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AR44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT44" t="n">
         <v>1.19</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AU44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AV44" t="n">
         <v>1.2</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AW44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BB44" t="n">
         <v>1.21</v>
       </c>
-      <c r="AT44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BB44" t="n">
+      <c r="BC44" t="n">
         <v>1.2</v>
       </c>
-      <c r="BC44" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BD44" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BF44" t="n">
         <v>1.55</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -9105,19 +9105,19 @@
         <v>3.1</v>
       </c>
       <c r="H45" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I45" t="n">
         <v>2.94</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K45" t="n">
         <v>3.3</v>
       </c>
       <c r="L45" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
         <v>3.7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M46" t="n">
         <v>1.09</v>
@@ -9407,7 +9407,7 @@
         <v>10.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AS46" t="n">
         <v>7</v>
@@ -9422,28 +9422,28 @@
         <v>6</v>
       </c>
       <c r="AW46" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AX46" t="n">
         <v>11</v>
       </c>
       <c r="AY46" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ46" t="n">
         <v>6.4</v>
       </c>
       <c r="BA46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC46" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB46" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>20</v>
-      </c>
       <c r="BD46" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BE46" t="n">
         <v>3.85</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -9496,10 +9496,10 @@
         <v>3.25</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="K47" t="n">
         <v>4.6</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -9693,10 +9693,10 @@
         <v>4.6</v>
       </c>
       <c r="J48" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K48" t="n">
         <v>5.8</v>
-      </c>
-      <c r="K48" t="n">
-        <v>5.9</v>
       </c>
       <c r="L48" t="n">
         <v>1.16</v>
@@ -9711,22 +9711,22 @@
         <v>1.07</v>
       </c>
       <c r="P48" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q48" t="n">
         <v>1.22</v>
       </c>
       <c r="R48" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="S48" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T48" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="U48" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="V48" t="n">
         <v>1.28</v>
@@ -9738,28 +9738,28 @@
         <v>70</v>
       </c>
       <c r="Y48" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z48" t="n">
         <v>65</v>
       </c>
       <c r="AA48" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AB48" t="n">
         <v>29</v>
       </c>
       <c r="AC48" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE48" t="n">
         <v>40</v>
       </c>
       <c r="AF48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG48" t="n">
         <v>13</v>
@@ -9768,10 +9768,10 @@
         <v>16</v>
       </c>
       <c r="AI48" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK48" t="n">
         <v>14.5</v>
@@ -9783,7 +9783,7 @@
         <v>32</v>
       </c>
       <c r="AN48" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AO48" t="n">
         <v>15</v>
@@ -9792,19 +9792,19 @@
         <v>60</v>
       </c>
       <c r="AQ48" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AR48" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS48" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AT48" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU48" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AV48" t="n">
         <v>21</v>
@@ -9822,7 +9822,7 @@
         <v>15.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB48" t="n">
         <v>25</v>
@@ -9834,17 +9834,17 @@
         <v>16.5</v>
       </c>
       <c r="BE48" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BF48" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BG48" t="n">
         <v>14.5</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -9932,7 +9932,7 @@
         <v>9.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z49" t="n">
         <v>18.5</v>
@@ -9941,7 +9941,7 @@
         <v>500</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC49" t="n">
         <v>8.4</v>
@@ -9953,7 +9953,7 @@
         <v>120</v>
       </c>
       <c r="AF49" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AG49" t="n">
         <v>17</v>
@@ -9962,7 +9962,7 @@
         <v>30</v>
       </c>
       <c r="AI49" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AJ49" t="n">
         <v>900</v>
@@ -9992,7 +9992,7 @@
         <v>11</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT49" t="n">
         <v>7.8</v>
@@ -10004,10 +10004,10 @@
         <v>9.6</v>
       </c>
       <c r="AW49" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX49" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>16.5</v>
       </c>
       <c r="AY49" t="n">
         <v>11.5</v>
@@ -10016,29 +10016,29 @@
         <v>17.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB49" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC49" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG49" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G50" t="n">
         <v>3</v>
@@ -10078,7 +10078,7 @@
         <v>2.78</v>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="J50" t="n">
         <v>3.2</v>
@@ -10090,49 +10090,49 @@
         <v>1.44</v>
       </c>
       <c r="M50" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N50" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O50" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P50" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q50" t="n">
         <v>2.36</v>
       </c>
       <c r="R50" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S50" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T50" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U50" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V50" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W50" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X50" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z50" t="n">
         <v>22</v>
       </c>
       <c r="AA50" t="n">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="AB50" t="n">
         <v>9.4</v>
@@ -10153,10 +10153,10 @@
         <v>13.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI50" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AJ50" t="n">
         <v>900</v>
@@ -10174,7 +10174,7 @@
         <v>500</v>
       </c>
       <c r="AO50" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AP50" t="n">
         <v>8.800000000000001</v>
@@ -10213,26 +10213,26 @@
         <v>23</v>
       </c>
       <c r="BB50" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC50" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="BD50" t="n">
         <v>28</v>
       </c>
       <c r="BE50" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF50" t="n">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="BG50" t="n">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
         <v>900</v>
       </c>
       <c r="AB51" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AC51" t="n">
         <v>8.800000000000001</v>
@@ -10338,7 +10338,7 @@
         <v>12.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AF51" t="n">
         <v>95</v>
@@ -10356,22 +10356,22 @@
         <v>900</v>
       </c>
       <c r="AK51" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AL51" t="n">
         <v>500</v>
       </c>
       <c r="AM51" t="n">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="AN51" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AO51" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP51" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ51" t="n">
         <v>6</v>
@@ -10404,36 +10404,36 @@
         <v>18.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC51" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC51" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD51" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE51" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BF51" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG51" t="n">
         <v>6.8</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10443,184 +10443,184 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="G52" t="n">
-        <v>2.56</v>
+        <v>1000</v>
       </c>
       <c r="H52" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="I52" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J52" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="K52" t="n">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>2.84</v>
+        <v>1.24</v>
       </c>
       <c r="O52" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="P52" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.42</v>
+        <v>1.25</v>
       </c>
       <c r="R52" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S52" t="n">
-        <v>4.8</v>
+        <v>1.25</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U52" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="X52" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y52" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z52" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA52" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC52" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD52" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE52" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF52" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG52" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH52" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI52" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ52" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK52" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL52" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM52" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN52" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO52" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ52" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR52" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS52" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AT52" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU52" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV52" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW52" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AX52" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY52" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ52" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA52" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BB52" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC52" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BD52" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE52" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF52" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BG52" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -10642,186 +10642,186 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="G53" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="H53" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K53" t="n">
         <v>3.35</v>
       </c>
       <c r="L53" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M53" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N53" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="O53" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="P53" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="R53" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S53" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="T53" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="V53" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W53" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="X53" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AA53" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AB53" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC53" t="n">
         <v>7.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE53" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF53" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG53" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH53" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI53" t="n">
         <v>75</v>
       </c>
       <c r="AJ53" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO53" t="n">
         <v>60</v>
       </c>
-      <c r="AK53" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>55</v>
-      </c>
       <c r="AP53" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AQ53" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT53" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR53" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS53" t="n">
+      <c r="AU53" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD53" t="n">
         <v>40</v>
       </c>
-      <c r="AT53" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>11</v>
-      </c>
       <c r="BE53" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BF53" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="BG53" t="n">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10831,191 +10831,191 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>El Paso Locomotive FC</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="G54" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="H54" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="I54" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K54" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="L54" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="M54" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N54" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="O54" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="P54" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.73</v>
+        <v>2.72</v>
       </c>
       <c r="R54" t="n">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="S54" t="n">
-        <v>2.84</v>
+        <v>5.5</v>
       </c>
       <c r="T54" t="n">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="U54" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="V54" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W54" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="X54" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y54" t="n">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z54" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC54" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AD54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE54" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AF54" t="n">
         <v>20</v>
       </c>
       <c r="AG54" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AI54" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS54" t="n">
         <v>42</v>
       </c>
-      <c r="AJ54" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AT54" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AU54" t="n">
         <v>6.8</v>
       </c>
       <c r="AV54" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC54" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW54" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD54" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF54" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BG54" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CONCACAF Champions League</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -11025,191 +11025,191 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>El Paso Locomotive FC</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.51</v>
+        <v>2.52</v>
       </c>
       <c r="G55" t="n">
-        <v>1.54</v>
+        <v>2.62</v>
       </c>
       <c r="H55" t="n">
-        <v>6.6</v>
+        <v>2.86</v>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="J55" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="K55" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="L55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O55" t="n">
         <v>1.25</v>
       </c>
-      <c r="M55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N55" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1.19</v>
-      </c>
       <c r="P55" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="R55" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="S55" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="T55" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="U55" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="V55" t="n">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="W55" t="n">
-        <v>2.84</v>
+        <v>1.62</v>
       </c>
       <c r="X55" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y55" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ55" t="n">
         <v>38</v>
       </c>
-      <c r="Z55" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB55" t="n">
+      <c r="AK55" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ55" t="n">
         <v>12</v>
       </c>
-      <c r="AC55" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>18</v>
-      </c>
       <c r="BA55" t="n">
-        <v>55</v>
+        <v>5.3</v>
       </c>
       <c r="BB55" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF55" t="n">
         <v>12.5</v>
       </c>
-      <c r="BC55" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG55" t="n">
-        <v>55</v>
+        <v>18.5</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>CONCACAF Champions League</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11219,184 +11219,184 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>23:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="G56" t="n">
-        <v>2.34</v>
+        <v>1.57</v>
       </c>
       <c r="H56" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="I56" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="J56" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="K56" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="L56" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="M56" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="N56" t="n">
-        <v>2.86</v>
+        <v>5.6</v>
       </c>
       <c r="O56" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="P56" t="n">
-        <v>1.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.26</v>
+        <v>1.56</v>
       </c>
       <c r="R56" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="S56" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="T56" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="U56" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="V56" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="W56" t="n">
-        <v>1.77</v>
+        <v>2.76</v>
       </c>
       <c r="X56" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>470</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB56" t="n">
         <v>12</v>
       </c>
-      <c r="Y56" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AC56" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AD56" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE56" t="n">
         <v>80</v>
       </c>
       <c r="AF56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ56" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AK56" t="n">
         <v>14</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AL56" t="n">
         <v>27</v>
       </c>
-      <c r="AI56" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ56" t="n">
+      <c r="AM56" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE56" t="n">
         <v>36</v>
       </c>
-      <c r="AK56" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF56" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="BG56" t="n">
-        <v>4.2</v>
+        <v>34</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
@@ -11418,373 +11418,567 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3.05</v>
+        <v>2.14</v>
       </c>
       <c r="G57" t="n">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="H57" t="n">
-        <v>2.48</v>
+        <v>3.9</v>
       </c>
       <c r="I57" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="J57" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K57" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L57" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M57" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N57" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="O57" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="P57" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R57" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S57" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T57" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="U57" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="V57" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="W57" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="X57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y57" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="AA57" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AB57" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AC57" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AD57" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE57" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AF57" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AG57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH57" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AI57" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AJ57" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AK57" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL57" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM57" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AN57" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AO57" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="AP57" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ57" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR57" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AS57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT57" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>9.4</v>
       </c>
       <c r="AU57" t="n">
         <v>6.4</v>
       </c>
       <c r="AV57" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX57" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW57" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>16</v>
-      </c>
       <c r="AY57" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ57" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA57" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BB57" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="BC57" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BD57" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE57" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="BF57" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="BG57" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-05 22:36:53</t>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Chile)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X58" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH58" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:47:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>23:15:00</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>CD Olimpia</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>CD Marathon</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="F59" t="n">
         <v>1.04</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G59" t="n">
         <v>990</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H59" t="n">
         <v>1.04</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I59" t="n">
         <v>990</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J59" t="n">
         <v>1.04</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K59" t="n">
         <v>950</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L59" t="n">
         <v>1.01</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M59" t="n">
         <v>1.01</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N59" t="n">
         <v>1.3</v>
       </c>
-      <c r="O58" t="n">
+      <c r="O59" t="n">
         <v>1.23</v>
       </c>
-      <c r="P58" t="n">
+      <c r="P59" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Q59" t="n">
         <v>1.22</v>
       </c>
-      <c r="R58" t="n">
+      <c r="R59" t="n">
         <v>1.18</v>
       </c>
-      <c r="S58" t="n">
+      <c r="S59" t="n">
         <v>1.24</v>
       </c>
-      <c r="T58" t="n">
+      <c r="T59" t="n">
         <v>1.11</v>
       </c>
-      <c r="U58" t="n">
+      <c r="U59" t="n">
         <v>1.11</v>
       </c>
-      <c r="V58" t="n">
+      <c r="V59" t="n">
         <v>1.01</v>
       </c>
-      <c r="W58" t="n">
+      <c r="W59" t="n">
         <v>1.01</v>
       </c>
-      <c r="X58" t="n">
+      <c r="X59" t="n">
         <v>1000</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Y59" t="n">
         <v>1000</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="Z59" t="n">
         <v>1000</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AA59" t="n">
         <v>1000</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AB59" t="n">
         <v>1000</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AC59" t="n">
         <v>1000</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AD59" t="n">
         <v>1000</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AE59" t="n">
         <v>1000</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AF59" t="n">
         <v>1000</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AG59" t="n">
         <v>1000</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AH59" t="n">
         <v>1000</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AI59" t="n">
         <v>1000</v>
       </c>
-      <c r="AJ58" t="n">
+      <c r="AJ59" t="n">
         <v>1000</v>
       </c>
-      <c r="AK58" t="n">
+      <c r="AK59" t="n">
         <v>1000</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AL59" t="n">
         <v>1000</v>
       </c>
-      <c r="AM58" t="n">
+      <c r="AM59" t="n">
         <v>1000</v>
       </c>
-      <c r="AN58" t="n">
+      <c r="AN59" t="n">
         <v>1000</v>
       </c>
-      <c r="AO58" t="n">
+      <c r="AO59" t="n">
         <v>1000</v>
       </c>
-      <c r="AP58" t="n">
+      <c r="AP59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AQ59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AR59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AS58" t="n">
+      <c r="AS59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AT58" t="n">
+      <c r="AT59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AU58" t="n">
+      <c r="AU59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AV58" t="n">
+      <c r="AV59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AW58" t="n">
+      <c r="AW59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AX58" t="n">
+      <c r="AX59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AY58" t="n">
+      <c r="AY59" t="n">
         <v>1.03</v>
       </c>
-      <c r="AZ58" t="n">
+      <c r="AZ59" t="n">
         <v>1.03</v>
       </c>
-      <c r="BA58" t="n">
+      <c r="BA59" t="n">
         <v>1.03</v>
       </c>
-      <c r="BB58" t="n">
+      <c r="BB59" t="n">
         <v>1.03</v>
       </c>
-      <c r="BC58" t="n">
+      <c r="BC59" t="n">
         <v>1.03</v>
       </c>
-      <c r="BD58" t="n">
+      <c r="BD59" t="n">
         <v>1.03</v>
       </c>
-      <c r="BE58" t="n">
+      <c r="BE59" t="n">
         <v>1.03</v>
       </c>
-      <c r="BF58" t="n">
+      <c r="BF59" t="n">
         <v>1.01</v>
       </c>
-      <c r="BG58" t="n">
+      <c r="BG59" t="n">
         <v>1.01</v>
       </c>
-      <c r="BH58" t="inlineStr">
-        <is>
-          <t>2026-05-05 22:36:53</t>
+      <c r="BH59" t="inlineStr">
+        <is>
+          <t>2026-05-06 00:47:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,73 +757,73 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G2" t="n">
         <v>2.52</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.56</v>
-      </c>
       <c r="H2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.3</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P2" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
         <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
         <v>7.4</v>
@@ -832,61 +832,61 @@
         <v>13.5</v>
       </c>
       <c r="AE2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>36</v>
       </c>
-      <c r="AF2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>38</v>
-      </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
         <v>19.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -895,32 +895,32 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BB2" t="n">
         <v>30</v>
       </c>
       <c r="BC2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BE2" t="n">
         <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BG2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
         <v>5.6</v>
@@ -1160,37 +1160,37 @@
         <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1202,7 +1202,7 @@
         <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
         <v>55</v>
@@ -1211,16 +1211,16 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AF4" t="n">
         <v>11</v>
@@ -1232,25 +1232,25 @@
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP4" t="n">
         <v>17.5</v>
@@ -1259,16 +1259,16 @@
         <v>18.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
         <v>18</v>
@@ -1277,13 +1277,13 @@
         <v>50</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
         <v>50</v>
@@ -1292,23 +1292,23 @@
         <v>14.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
         <v>26</v>
       </c>
       <c r="BE4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG4" t="n">
         <v>60</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
@@ -1363,146 +1363,146 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="X5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
         <v>23</v>
       </c>
-      <c r="Y5" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="n">
         <v>11</v>
       </c>
-      <c r="AC5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>12</v>
-      </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AR5" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS5" t="n">
         <v>48</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY5" t="n">
         <v>9</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>17.5</v>
       </c>
-      <c r="AW5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA5" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BB5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD5" t="n">
         <v>25</v>
       </c>
       <c r="BE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG5" t="n">
         <v>55</v>
       </c>
-      <c r="BF5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>38</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1533,139 +1533,139 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G6" t="n">
         <v>2.18</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.22</v>
-      </c>
       <c r="H6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="n">
         <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
         <v>4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U6" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.4</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="Y6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Z6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
         <v>27</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>13.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
         <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP6" t="n">
         <v>40</v>
       </c>
-      <c r="AN6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>36</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AR6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AS6" t="n">
         <v>46</v>
       </c>
       <c r="AT6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
         <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY6" t="n">
         <v>11.5</v>
@@ -1674,29 +1674,29 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE6" t="n">
         <v>24</v>
       </c>
-      <c r="BB6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>32</v>
-      </c>
       <c r="BF6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1727,25 +1727,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J7" t="n">
         <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -1760,13 +1760,13 @@
         <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
         <v>1.94</v>
@@ -1778,34 +1778,34 @@
         <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z7" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AA7" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE7" t="n">
         <v>480</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
@@ -1814,34 +1814,34 @@
         <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>390</v>
+        <v>260</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
         <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AS7" t="n">
         <v>11</v>
@@ -1850,16 +1850,16 @@
         <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
         <v>8.800000000000001</v>
@@ -1868,10 +1868,10 @@
         <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC7" t="n">
         <v>13.5</v>
@@ -1880,7 +1880,7 @@
         <v>19</v>
       </c>
       <c r="BE7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF7" t="n">
         <v>7</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1921,91 +1921,91 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="I8" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
         <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="U8" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD8" t="n">
         <v>10.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
         <v>36</v>
@@ -2017,31 +2017,31 @@
         <v>260</v>
       </c>
       <c r="AL8" t="n">
-        <v>260</v>
+        <v>440</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AO8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -2050,41 +2050,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.4</v>
+        <v>18</v>
       </c>
       <c r="AY8" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BF8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>8</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2115,130 +2115,130 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="T9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.74</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.1</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>28</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AT9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
@@ -2247,38 +2247,38 @@
         <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="I10" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>1.38</v>
@@ -2345,134 +2345,134 @@
         <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE10" t="n">
         <v>26</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI10" t="n">
         <v>36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP10" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AT10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY10" t="n">
         <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BC10" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
         <v>46</v>
       </c>
       <c r="BF10" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BG10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.35</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.45</v>
@@ -2527,88 +2527,88 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
         <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
       </c>
       <c r="Y11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH11" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI11" t="n">
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO11" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
@@ -2623,7 +2623,7 @@
         <v>28</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>6.8</v>
@@ -2632,41 +2632,41 @@
         <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
         <v>24</v>
       </c>
       <c r="BB11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE11" t="n">
         <v>29</v>
       </c>
-      <c r="BC11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BF11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BG11" t="n">
         <v>32</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
         <v>2.2</v>
@@ -2715,58 +2715,58 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AA12" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
         <v>16</v>
@@ -2775,92 +2775,92 @@
         <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="AJ12" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AK12" t="n">
         <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB12" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
         <v>18.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BF12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2906,37 +2906,37 @@
         <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
         <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
         <v>1.5</v>
@@ -2945,10 +2945,10 @@
         <v>1.58</v>
       </c>
       <c r="X13" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z13" t="n">
         <v>500</v>
@@ -2957,31 +2957,31 @@
         <v>440</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC13" t="n">
         <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF13" t="n">
         <v>500</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>970</v>
       </c>
       <c r="AG13" t="n">
         <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
         <v>290</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK13" t="n">
         <v>80</v>
@@ -3005,22 +3005,22 @@
         <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
         <v>7.8</v>
@@ -3032,13 +3032,13 @@
         <v>10.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD13" t="n">
         <v>30</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3085,52 +3085,52 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J14" t="n">
         <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.32</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.37</v>
-      </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
         <v>1.83</v>
@@ -3139,13 +3139,13 @@
         <v>1.32</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA14" t="n">
         <v>85</v>
@@ -3154,7 +3154,7 @@
         <v>26</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
         <v>11.5</v>
@@ -3166,10 +3166,10 @@
         <v>80</v>
       </c>
       <c r="AG14" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -3187,68 +3187,68 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
         <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
         <v>11.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
         <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
         <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
         <v>30</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BC14" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v>5.4</v>
       </c>
       <c r="K15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.32</v>
@@ -3303,7 +3303,7 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.22</v>
@@ -3318,7 +3318,7 @@
         <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
@@ -3399,7 +3399,7 @@
         <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
         <v>11</v>
@@ -3408,7 +3408,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AX15" t="n">
         <v>8</v>
@@ -3420,7 +3420,7 @@
         <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB15" t="n">
         <v>8.4</v>
@@ -3435,14 +3435,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG15" t="n">
         <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
         <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.95</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
         <v>12</v>
@@ -3563,22 +3563,22 @@
         <v>370</v>
       </c>
       <c r="AJ16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK16" t="n">
         <v>25</v>
       </c>
-      <c r="AK16" t="n">
-        <v>26</v>
-      </c>
       <c r="AL16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AP16" t="n">
         <v>9.199999999999999</v>
@@ -3590,7 +3590,7 @@
         <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
@@ -3602,7 +3602,7 @@
         <v>16</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX16" t="n">
         <v>9.4</v>
@@ -3614,7 +3614,7 @@
         <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB16" t="n">
         <v>19.5</v>
@@ -3626,17 +3626,17 @@
         <v>12.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF16" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
         <v>3.1</v>
@@ -3682,7 +3682,7 @@
         <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.33</v>
@@ -3718,7 +3718,7 @@
         <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X17" t="n">
         <v>22</v>
@@ -3820,7 +3820,7 @@
         <v>13</v>
       </c>
       <c r="BE17" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF17" t="n">
         <v>9.800000000000001</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H18" t="n">
         <v>3.05</v>
       </c>
       <c r="I18" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.45</v>
@@ -3888,31 +3888,31 @@
         <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
         <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
@@ -3924,13 +3924,13 @@
         <v>44</v>
       </c>
       <c r="AA18" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD18" t="n">
         <v>970</v>
@@ -3939,19 +3939,19 @@
         <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
         <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ18" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK18" t="n">
         <v>90</v>
@@ -3969,62 +3969,62 @@
         <v>600</v>
       </c>
       <c r="AP18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>5.8</v>
       </c>
       <c r="AR18" t="n">
         <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AU18" t="n">
         <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY18" t="n">
         <v>7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC18" t="n">
         <v>12</v>
       </c>
       <c r="BD18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE18" t="n">
         <v>10.5</v>
       </c>
-      <c r="BE18" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BF18" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4079,7 +4079,7 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>1.38</v>
@@ -4088,13 +4088,13 @@
         <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
         <v>1.89</v>
@@ -4103,10 +4103,10 @@
         <v>1.92</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X19" t="n">
         <v>29</v>
@@ -4169,56 +4169,56 @@
         <v>6.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW19" t="n">
         <v>9</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AX19" t="n">
         <v>5.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="BB19" t="n">
         <v>6</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="BG19" t="n">
-        <v>9</v>
+        <v>2.04</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -4249,91 +4249,91 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
         <v>2.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="U20" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
         <v>19.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
         <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI20" t="n">
         <v>120</v>
@@ -4342,77 +4342,77 @@
         <v>100</v>
       </c>
       <c r="AK20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>250</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO20" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF20" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG20" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -4443,31 +4443,31 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="G21" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.2</v>
@@ -4476,31 +4476,31 @@
         <v>2.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S21" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T21" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="X21" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Y21" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="Z21" t="n">
         <v>420</v>
@@ -4509,19 +4509,19 @@
         <v>700</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AE21" t="n">
         <v>480</v>
       </c>
       <c r="AF21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
@@ -4533,10 +4533,10 @@
         <v>390</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL21" t="n">
         <v>80</v>
@@ -4545,7 +4545,7 @@
         <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AO21" t="n">
         <v>700</v>
@@ -4554,40 +4554,40 @@
         <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV21" t="n">
         <v>11.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
         <v>13</v>
@@ -4596,17 +4596,17 @@
         <v>14.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="G22" t="n">
         <v>2.06</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
@@ -4655,82 +4655,82 @@
         <v>3.65</v>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
         <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
         <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
         <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
         <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI22" t="n">
         <v>370</v>
       </c>
       <c r="AJ22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK22" t="n">
         <v>24</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>23</v>
       </c>
       <c r="AL22" t="n">
         <v>180</v>
@@ -4739,68 +4739,68 @@
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>600</v>
+        <v>170</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS22" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AT22" t="n">
         <v>7.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>15.5</v>
       </c>
-      <c r="AW22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA22" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="H23" t="n">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="I23" t="n">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
         <v>1.37</v>
@@ -4867,7 +4867,7 @@
         <v>1.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -4876,46 +4876,46 @@
         <v>1.63</v>
       </c>
       <c r="U23" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="X23" t="n">
         <v>38</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="Z23" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AA23" t="n">
         <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC23" t="n">
         <v>9</v>
       </c>
       <c r="AD23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG23" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>970</v>
-      </c>
       <c r="AH23" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>500</v>
@@ -4924,7 +4924,7 @@
         <v>900</v>
       </c>
       <c r="AK23" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL23" t="n">
         <v>500</v>
@@ -4933,68 +4933,68 @@
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO23" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AQ23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>11</v>
-      </c>
       <c r="AU23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>15.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="BD23" t="n">
         <v>12</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -5031,46 +5031,46 @@
         <v>1.79</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P24" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="T24" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="U24" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V24" t="n">
         <v>1.24</v>
@@ -5079,116 +5079,116 @@
         <v>2.26</v>
       </c>
       <c r="X24" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Y24" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="Z24" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AA24" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="AF24" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH24" t="n">
         <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK24" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL24" t="n">
         <v>48</v>
       </c>
       <c r="AM24" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN24" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AO24" t="n">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="AP24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS24" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA24" t="n">
         <v>29</v>
       </c>
-      <c r="AX24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>28</v>
-      </c>
       <c r="BB24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE24" t="n">
-        <v>16.5</v>
+        <v>38</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G25" t="n">
         <v>2.58</v>
@@ -5243,13 +5243,13 @@
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
         <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q25" t="n">
         <v>1.73</v>
@@ -5258,16 +5258,16 @@
         <v>1.49</v>
       </c>
       <c r="S25" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T25" t="n">
         <v>1.64</v>
       </c>
       <c r="U25" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V25" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.63</v>
@@ -5327,22 +5327,22 @@
         <v>600</v>
       </c>
       <c r="AP25" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
         <v>11.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT25" t="n">
         <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AV25" t="n">
         <v>7</v>
@@ -5360,10 +5360,10 @@
         <v>8.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BC25" t="n">
         <v>13</v>
@@ -5372,7 +5372,7 @@
         <v>8.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BF25" t="n">
         <v>6.6</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J26" t="n">
         <v>4.1</v>
@@ -5446,10 +5446,10 @@
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
         <v>2.94</v>
@@ -5479,10 +5479,10 @@
         <v>900</v>
       </c>
       <c r="AB26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD26" t="n">
         <v>500</v>
@@ -5515,7 +5515,7 @@
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO26" t="n">
         <v>700</v>
@@ -5530,7 +5530,7 @@
         <v>18.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AT26" t="n">
         <v>8.6</v>
@@ -5542,7 +5542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AX26" t="n">
         <v>9.4</v>
@@ -5554,7 +5554,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BB26" t="n">
         <v>9.199999999999999</v>
@@ -5566,17 +5566,17 @@
         <v>16</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF26" t="n">
         <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>2.12</v>
       </c>
       <c r="G27" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H27" t="n">
         <v>3.4</v>
@@ -5622,7 +5622,7 @@
         <v>3.6</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L27" t="n">
         <v>1.37</v>
@@ -5631,16 +5631,16 @@
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
         <v>1.27</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R27" t="n">
         <v>1.43</v>
@@ -5655,10 +5655,10 @@
         <v>2.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X27" t="n">
         <v>21</v>
@@ -5721,10 +5721,10 @@
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT27" t="n">
         <v>9.6</v>
@@ -5736,7 +5736,7 @@
         <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX27" t="n">
         <v>13</v>
@@ -5748,19 +5748,19 @@
         <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BD27" t="n">
         <v>24</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF27" t="n">
         <v>10.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>1.69</v>
       </c>
       <c r="G28" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H28" t="n">
         <v>4.9</v>
@@ -5831,10 +5831,10 @@
         <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R28" t="n">
         <v>1.45</v>
@@ -5846,7 +5846,7 @@
         <v>1.81</v>
       </c>
       <c r="U28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V28" t="n">
         <v>1.21</v>
@@ -5915,7 +5915,7 @@
         <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS28" t="n">
         <v>9</v>
@@ -5930,7 +5930,7 @@
         <v>16.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="AX28" t="n">
         <v>5.8</v>
@@ -5942,7 +5942,7 @@
         <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="BB28" t="n">
         <v>9</v>
@@ -5951,7 +5951,7 @@
         <v>12</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BE28" t="n">
         <v>8.800000000000001</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -5998,55 +5998,55 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H29" t="n">
         <v>4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.28</v>
       </c>
-      <c r="S29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.29</v>
-      </c>
       <c r="W29" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="X29" t="n">
         <v>25</v>
@@ -6061,7 +6061,7 @@
         <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AC29" t="n">
         <v>14</v>
@@ -6085,7 +6085,7 @@
         <v>500</v>
       </c>
       <c r="AJ29" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK29" t="n">
         <v>65</v>
@@ -6109,56 +6109,56 @@
         <v>8.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU29" t="n">
         <v>6.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY29" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ29" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BA29" t="n">
         <v>10.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE29" t="n">
         <v>11</v>
       </c>
       <c r="BF29" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BG29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -6189,61 +6189,61 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="G30" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="H30" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="I30" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J30" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="K30" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
         <v>1.76</v>
       </c>
       <c r="U30" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W30" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="X30" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Y30" t="n">
         <v>950</v>
@@ -6252,16 +6252,16 @@
         <v>170</v>
       </c>
       <c r="AA30" t="n">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC30" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AE30" t="n">
         <v>240</v>
@@ -6279,7 +6279,7 @@
         <v>200</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="AK30" t="n">
         <v>970</v>
@@ -6291,68 +6291,68 @@
         <v>100</v>
       </c>
       <c r="AN30" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO30" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AP30" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU30" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX30" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>9</v>
       </c>
       <c r="AY30" t="n">
         <v>9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA30" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG30" t="n">
         <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -6383,31 +6383,31 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="G31" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H31" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
         <v>1.24</v>
@@ -6416,58 +6416,58 @@
         <v>2.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S31" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U31" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="W31" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X31" t="n">
         <v>28</v>
       </c>
       <c r="Y31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA31" t="n">
         <v>48</v>
       </c>
       <c r="AB31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH31" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>16.5</v>
       </c>
       <c r="AI31" t="n">
         <v>70</v>
@@ -6485,25 +6485,25 @@
         <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO31" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AP31" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ31" t="n">
         <v>10</v>
       </c>
       <c r="AR31" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU31" t="n">
         <v>7.6</v>
@@ -6521,16 +6521,16 @@
         <v>12</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BA31" t="n">
         <v>16.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>9.4</v>
+        <v>23</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD31" t="n">
         <v>18.5</v>
@@ -6539,14 +6539,14 @@
         <v>29</v>
       </c>
       <c r="BF31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG31" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="G32" t="n">
         <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="I32" t="n">
         <v>1.64</v>
@@ -6592,22 +6592,22 @@
         <v>4.7</v>
       </c>
       <c r="K32" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
         <v>1.04</v>
       </c>
       <c r="N32" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O32" t="n">
         <v>1.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q32" t="n">
         <v>1.58</v>
@@ -6616,13 +6616,13 @@
         <v>1.6</v>
       </c>
       <c r="S32" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T32" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="U32" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
@@ -6631,106 +6631,106 @@
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z32" t="n">
         <v>12</v>
       </c>
       <c r="AA32" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AB32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF32" t="n">
         <v>50</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>500</v>
       </c>
       <c r="AG32" t="n">
         <v>22</v>
       </c>
       <c r="AH32" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI32" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="AJ32" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AK32" t="n">
-        <v>400</v>
+        <v>65</v>
       </c>
       <c r="AL32" t="n">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="AM32" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN32" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AP32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV32" t="n">
         <v>9</v>
       </c>
-      <c r="AQ32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AW32" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AY32" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA32" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BB32" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BC32" t="n">
         <v>28</v>
       </c>
       <c r="BD32" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BE32" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF32" t="n">
         <v>11.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -6777,46 +6777,46 @@
         <v>1.47</v>
       </c>
       <c r="H33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I33" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K33" t="n">
         <v>5.9</v>
       </c>
       <c r="L33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="S33" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="T33" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="U33" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
@@ -6825,10 +6825,10 @@
         <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Y33" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="Z33" t="n">
         <v>160</v>
@@ -6837,10 +6837,10 @@
         <v>230</v>
       </c>
       <c r="AB33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD33" t="n">
         <v>950</v>
@@ -6849,10 +6849,10 @@
         <v>240</v>
       </c>
       <c r="AF33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG33" t="n">
         <v>11</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>10.5</v>
       </c>
       <c r="AH33" t="n">
         <v>950</v>
@@ -6861,28 +6861,28 @@
         <v>200</v>
       </c>
       <c r="AJ33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK33" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AL33" t="n">
         <v>500</v>
       </c>
       <c r="AM33" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN33" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AO33" t="n">
         <v>100</v>
       </c>
       <c r="AP33" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR33" t="n">
         <v>10.5</v>
@@ -6891,7 +6891,7 @@
         <v>11.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU33" t="n">
         <v>10.5</v>
@@ -6900,7 +6900,7 @@
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX33" t="n">
         <v>9.4</v>
@@ -6909,32 +6909,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB33" t="n">
         <v>11.5</v>
       </c>
       <c r="BC33" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE33" t="n">
         <v>10.5</v>
       </c>
-      <c r="BD33" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>11</v>
-      </c>
       <c r="BF33" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG33" t="n">
         <v>15</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -6965,25 +6965,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G34" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H34" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I34" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
         <v>3.45</v>
       </c>
       <c r="L34" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
         <v>1.09</v>
@@ -6995,25 +6995,25 @@
         <v>1.42</v>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R34" t="n">
         <v>1.26</v>
       </c>
       <c r="S34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T34" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W34" t="n">
         <v>1.37</v>
@@ -7043,13 +7043,13 @@
         <v>30</v>
       </c>
       <c r="AF34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG34" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI34" t="n">
         <v>120</v>
@@ -7058,7 +7058,7 @@
         <v>500</v>
       </c>
       <c r="AK34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL34" t="n">
         <v>70</v>
@@ -7067,7 +7067,7 @@
         <v>580</v>
       </c>
       <c r="AN34" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AO34" t="n">
         <v>27</v>
@@ -7085,10 +7085,10 @@
         <v>16.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV34" t="n">
         <v>10</v>
@@ -7109,26 +7109,26 @@
         <v>23</v>
       </c>
       <c r="BB34" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BC34" t="n">
         <v>34</v>
       </c>
       <c r="BD34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE34" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BF34" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG34" t="n">
         <v>21</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G35" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H35" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I35" t="n">
         <v>1.78</v>
@@ -7195,22 +7195,22 @@
         <v>1.52</v>
       </c>
       <c r="R35" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S35" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T35" t="n">
         <v>1.58</v>
       </c>
       <c r="U35" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V35" t="n">
         <v>2.28</v>
       </c>
       <c r="W35" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
         <v>34</v>
@@ -7240,7 +7240,7 @@
         <v>46</v>
       </c>
       <c r="AG35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH35" t="n">
         <v>18.5</v>
@@ -7258,31 +7258,31 @@
         <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN35" t="n">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AO35" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="AQ35" t="n">
         <v>11.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS35" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="AT35" t="n">
         <v>20</v>
       </c>
       <c r="AU35" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV35" t="n">
         <v>9.4</v>
@@ -7291,13 +7291,13 @@
         <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="AY35" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA35" t="n">
         <v>18.5</v>
@@ -7306,23 +7306,23 @@
         <v>6.2</v>
       </c>
       <c r="BC35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE35" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>6.2</v>
       </c>
       <c r="BF35" t="n">
         <v>5.3</v>
       </c>
       <c r="BG35" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -7353,58 +7353,58 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="G36" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="H36" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I36" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="J36" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L36" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M36" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N36" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="P36" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="T36" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W36" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="X36" t="n">
         <v>970</v>
@@ -7419,25 +7419,25 @@
         <v>900</v>
       </c>
       <c r="AB36" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AC36" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD36" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE36" t="n">
         <v>500</v>
       </c>
       <c r="AF36" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG36" t="n">
         <v>500</v>
       </c>
       <c r="AH36" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI36" t="n">
         <v>500</v>
@@ -7461,62 +7461,62 @@
         <v>600</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR36" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF36" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV36" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>6</v>
-      </c>
       <c r="BG36" t="n">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="G37" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>3.05</v>
       </c>
       <c r="K37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L37" t="n">
         <v>1.62</v>
@@ -7571,73 +7571,73 @@
         <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O37" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="P37" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R37" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U37" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V37" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W37" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X37" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y37" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z37" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA37" t="n">
         <v>900</v>
       </c>
       <c r="AB37" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC37" t="n">
         <v>7.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE37" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG37" t="n">
         <v>13.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AI37" t="n">
         <v>500</v>
       </c>
       <c r="AJ37" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK37" t="n">
         <v>110</v>
@@ -7649,19 +7649,19 @@
         <v>500</v>
       </c>
       <c r="AN37" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO37" t="n">
         <v>600</v>
       </c>
       <c r="AP37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ37" t="n">
         <v>7.6</v>
       </c>
       <c r="AR37" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AS37" t="n">
         <v>19</v>
@@ -7673,44 +7673,44 @@
         <v>6.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW37" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AX37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA37" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BB37" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="BC37" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF37" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG37" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -7741,61 +7741,61 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G38" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H38" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I38" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K38" t="n">
         <v>4.2</v>
       </c>
       <c r="L38" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="O38" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P38" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R38" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T38" t="n">
         <v>2.3</v>
       </c>
       <c r="U38" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V38" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W38" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X38" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y38" t="n">
         <v>22</v>
@@ -7810,13 +7810,13 @@
         <v>6.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD38" t="n">
         <v>110</v>
       </c>
       <c r="AE38" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AF38" t="n">
         <v>8.199999999999999</v>
@@ -7825,7 +7825,7 @@
         <v>12.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="n">
         <v>190</v>
@@ -7840,37 +7840,37 @@
         <v>380</v>
       </c>
       <c r="AM38" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO38" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AP38" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ38" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AS38" t="n">
         <v>8.4</v>
       </c>
       <c r="AT38" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU38" t="n">
         <v>7.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX38" t="n">
         <v>6.6</v>
@@ -7882,29 +7882,29 @@
         <v>18.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB38" t="n">
         <v>13</v>
       </c>
       <c r="BC38" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BE38" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF38" t="n">
         <v>10.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -7935,16 +7935,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G39" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H39" t="n">
         <v>3.65</v>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J39" t="n">
         <v>3.05</v>
@@ -7959,7 +7959,7 @@
         <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O39" t="n">
         <v>1.46</v>
@@ -7983,10 +7983,10 @@
         <v>1.87</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X39" t="n">
         <v>10</v>
@@ -8007,7 +8007,7 @@
         <v>7.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AE39" t="n">
         <v>370</v>
@@ -8052,7 +8052,7 @@
         <v>19</v>
       </c>
       <c r="AS39" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="AT39" t="n">
         <v>7.4</v>
@@ -8061,44 +8061,44 @@
         <v>6.2</v>
       </c>
       <c r="AV39" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW39" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AX39" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ39" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB39" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA39" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>8</v>
-      </c>
       <c r="BC39" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="BE39" t="n">
         <v>9.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG39" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -8138,43 +8138,43 @@
         <v>3.45</v>
       </c>
       <c r="I40" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K40" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L40" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M40" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N40" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="O40" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="P40" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R40" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S40" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="T40" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="U40" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V40" t="n">
         <v>1.37</v>
@@ -8183,7 +8183,7 @@
         <v>1.64</v>
       </c>
       <c r="X40" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y40" t="n">
         <v>9.6</v>
@@ -8213,7 +8213,7 @@
         <v>13.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI40" t="n">
         <v>540</v>
@@ -8222,7 +8222,7 @@
         <v>220</v>
       </c>
       <c r="AK40" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AL40" t="n">
         <v>230</v>
@@ -8231,13 +8231,13 @@
         <v>500</v>
       </c>
       <c r="AN40" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AO40" t="n">
         <v>600</v>
       </c>
       <c r="AP40" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ40" t="n">
         <v>7.2</v>
@@ -8246,19 +8246,19 @@
         <v>17</v>
       </c>
       <c r="AS40" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV40" t="n">
         <v>15</v>
       </c>
       <c r="AW40" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="AX40" t="n">
         <v>10</v>
@@ -8270,29 +8270,29 @@
         <v>16</v>
       </c>
       <c r="BA40" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BC40" t="n">
         <v>32</v>
       </c>
       <c r="BD40" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF40" t="n">
         <v>36</v>
       </c>
       <c r="BG40" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -8323,25 +8323,25 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="G41" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J41" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K41" t="n">
         <v>6.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M41" t="n">
         <v>1.03</v>
@@ -8350,55 +8350,55 @@
         <v>6.4</v>
       </c>
       <c r="O41" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P41" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="Q41" t="n">
         <v>1.51</v>
       </c>
       <c r="R41" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="S41" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="T41" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U41" t="n">
         <v>2.08</v>
       </c>
       <c r="V41" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W41" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="X41" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y41" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="Z41" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AA41" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AB41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC41" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC41" t="n">
-        <v>14</v>
-      </c>
       <c r="AD41" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE41" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AF41" t="n">
         <v>10</v>
@@ -8407,64 +8407,64 @@
         <v>10.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI41" t="n">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="AJ41" t="n">
         <v>12</v>
       </c>
       <c r="AK41" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL41" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM41" t="n">
         <v>110</v>
       </c>
       <c r="AN41" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AO41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP41" t="n">
-        <v>6.8</v>
+        <v>26</v>
       </c>
       <c r="AQ41" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="AR41" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="AT41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU41" t="n">
         <v>11.5</v>
       </c>
       <c r="AV41" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AW41" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="AX41" t="n">
         <v>9</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA41" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BB41" t="n">
         <v>10.5</v>
@@ -8473,20 +8473,20 @@
         <v>12</v>
       </c>
       <c r="BD41" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BE41" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG41" t="n">
         <v>15</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -8526,13 +8526,13 @@
         <v>3.7</v>
       </c>
       <c r="I42" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L42" t="n">
         <v>1.47</v>
@@ -8544,31 +8544,31 @@
         <v>3.25</v>
       </c>
       <c r="O42" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R42" t="n">
         <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T42" t="n">
         <v>1.9</v>
       </c>
       <c r="U42" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V42" t="n">
         <v>1.33</v>
       </c>
       <c r="W42" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X42" t="n">
         <v>13</v>
@@ -8601,16 +8601,16 @@
         <v>11.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI42" t="n">
         <v>80</v>
       </c>
       <c r="AJ42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK42" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL42" t="n">
         <v>120</v>
@@ -8622,19 +8622,19 @@
         <v>26</v>
       </c>
       <c r="AO42" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP42" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AQ42" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR42" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT42" t="n">
         <v>7.2</v>
@@ -8643,44 +8643,44 @@
         <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AW42" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AX42" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY42" t="n">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="AZ42" t="n">
         <v>17</v>
       </c>
       <c r="BA42" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD42" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB42" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>8</v>
-      </c>
       <c r="BE42" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF42" t="n">
         <v>18</v>
       </c>
       <c r="BG42" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -8711,88 +8711,88 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="G43" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="H43" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="I43" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K43" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L43" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M43" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N43" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O43" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P43" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="T43" t="n">
         <v>2.38</v>
       </c>
       <c r="U43" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V43" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W43" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="X43" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y43" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z43" t="n">
         <v>480</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD43" t="n">
         <v>100</v>
       </c>
       <c r="AE43" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AF43" t="n">
         <v>8.4</v>
       </c>
       <c r="AG43" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH43" t="n">
         <v>75</v>
@@ -8801,80 +8801,80 @@
         <v>540</v>
       </c>
       <c r="AJ43" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AK43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="n">
         <v>290</v>
       </c>
       <c r="AM43" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AN43" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO43" t="n">
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="AP43" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AQ43" t="n">
         <v>18</v>
       </c>
       <c r="AR43" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AT43" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU43" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX43" t="n">
         <v>6.4</v>
       </c>
       <c r="AY43" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ43" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB43" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC43" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BE43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BF43" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG43" t="n">
         <v>15</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="H44" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J44" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K44" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L44" t="n">
         <v>1.41</v>
@@ -8929,146 +8929,146 @@
         <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O44" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P44" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R44" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S44" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T44" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U44" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V44" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W44" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="X44" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA44" t="n">
         <v>500</v>
       </c>
-      <c r="Y44" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>900</v>
-      </c>
       <c r="AB44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF44" t="n">
         <v>13</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AG44" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD44" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC44" t="n">
         <v>18.5</v>
       </c>
-      <c r="AG44" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>180</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>15</v>
-      </c>
       <c r="BD44" t="n">
-        <v>2.78</v>
+        <v>7.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>2.92</v>
+        <v>9</v>
       </c>
       <c r="BF44" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG44" t="n">
-        <v>2.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G45" t="n">
         <v>3.05</v>
@@ -9108,13 +9108,13 @@
         <v>2.76</v>
       </c>
       <c r="I45" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J45" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K45" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L45" t="n">
         <v>1.48</v>
@@ -9123,13 +9123,13 @@
         <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O45" t="n">
         <v>1.4</v>
       </c>
       <c r="P45" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q45" t="n">
         <v>2.24</v>
@@ -9141,7 +9141,7 @@
         <v>4.2</v>
       </c>
       <c r="T45" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U45" t="n">
         <v>1.98</v>
@@ -9153,7 +9153,7 @@
         <v>1.48</v>
       </c>
       <c r="X45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y45" t="n">
         <v>11</v>
@@ -9180,7 +9180,7 @@
         <v>20</v>
       </c>
       <c r="AG45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH45" t="n">
         <v>18.5</v>
@@ -9207,7 +9207,7 @@
         <v>36</v>
       </c>
       <c r="AP45" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ45" t="n">
         <v>9</v>
@@ -9216,7 +9216,7 @@
         <v>15.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT45" t="n">
         <v>8.6</v>
@@ -9228,7 +9228,7 @@
         <v>11</v>
       </c>
       <c r="AW45" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX45" t="n">
         <v>16</v>
@@ -9237,32 +9237,32 @@
         <v>11</v>
       </c>
       <c r="AZ45" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB45" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC45" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BD45" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE45" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF45" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG45" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G46" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H46" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I46" t="n">
         <v>3.7</v>
       </c>
       <c r="J46" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K46" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L46" t="n">
         <v>1.48</v>
@@ -9320,13 +9320,13 @@
         <v>3.15</v>
       </c>
       <c r="O46" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P46" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R46" t="n">
         <v>1.26</v>
@@ -9335,7 +9335,7 @@
         <v>4.2</v>
       </c>
       <c r="T46" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U46" t="n">
         <v>1.92</v>
@@ -9344,7 +9344,7 @@
         <v>1.37</v>
       </c>
       <c r="W46" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X46" t="n">
         <v>23</v>
@@ -9395,22 +9395,22 @@
         <v>580</v>
       </c>
       <c r="AN46" t="n">
-        <v>26</v>
+        <v>600</v>
       </c>
       <c r="AO46" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP46" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ46" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR46" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT46" t="n">
         <v>7.4</v>
@@ -9422,41 +9422,41 @@
         <v>12.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX46" t="n">
         <v>11</v>
       </c>
       <c r="AY46" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA46" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB46" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC46" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD46" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF46" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -9490,19 +9490,19 @@
         <v>2.12</v>
       </c>
       <c r="G47" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H47" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I47" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K47" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L47" t="n">
         <v>1.48</v>
@@ -9511,40 +9511,40 @@
         <v>1.09</v>
       </c>
       <c r="N47" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O47" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P47" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R47" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S47" t="n">
         <v>4.1</v>
       </c>
       <c r="T47" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U47" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V47" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W47" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X47" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Z47" t="n">
         <v>500</v>
@@ -9553,13 +9553,13 @@
         <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC47" t="n">
         <v>8</v>
       </c>
       <c r="AD47" t="n">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="AE47" t="n">
         <v>500</v>
@@ -9571,7 +9571,7 @@
         <v>36</v>
       </c>
       <c r="AH47" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AI47" t="n">
         <v>500</v>
@@ -9580,7 +9580,7 @@
         <v>500</v>
       </c>
       <c r="AK47" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AL47" t="n">
         <v>500</v>
@@ -9589,13 +9589,13 @@
         <v>580</v>
       </c>
       <c r="AN47" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO47" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP47" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ47" t="n">
         <v>9.6</v>
@@ -9604,10 +9604,10 @@
         <v>21</v>
       </c>
       <c r="AS47" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT47" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU47" t="n">
         <v>6.6</v>
@@ -9616,19 +9616,19 @@
         <v>13</v>
       </c>
       <c r="AW47" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX47" t="n">
         <v>10</v>
       </c>
       <c r="AY47" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ47" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA47" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB47" t="n">
         <v>21</v>
@@ -9637,20 +9637,20 @@
         <v>20</v>
       </c>
       <c r="BD47" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF47" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG47" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -9681,16 +9681,16 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G48" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I48" t="n">
         <v>4.6</v>
-      </c>
-      <c r="I48" t="n">
-        <v>4.7</v>
       </c>
       <c r="J48" t="n">
         <v>5.7</v>
@@ -9705,10 +9705,10 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="O48" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P48" t="n">
         <v>5</v>
@@ -9717,13 +9717,13 @@
         <v>1.24</v>
       </c>
       <c r="R48" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="S48" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T48" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="U48" t="n">
         <v>4</v>
@@ -9732,13 +9732,13 @@
         <v>1.27</v>
       </c>
       <c r="W48" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X48" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Y48" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z48" t="n">
         <v>60</v>
@@ -9753,22 +9753,22 @@
         <v>17.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE48" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF48" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ48" t="n">
         <v>24</v>
@@ -9783,13 +9783,13 @@
         <v>32</v>
       </c>
       <c r="AN48" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AO48" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AQ48" t="n">
         <v>48</v>
@@ -9807,13 +9807,13 @@
         <v>17</v>
       </c>
       <c r="AV48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW48" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX48" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY48" t="n">
         <v>12</v>
@@ -9822,19 +9822,19 @@
         <v>16</v>
       </c>
       <c r="BA48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC48" t="n">
         <v>13.5</v>
       </c>
       <c r="BD48" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BE48" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF48" t="n">
         <v>3.7</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -9875,97 +9875,97 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="G49" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H49" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="I49" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J49" t="n">
         <v>2.76</v>
       </c>
-      <c r="J49" t="n">
-        <v>2.84</v>
-      </c>
       <c r="K49" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="L49" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="M49" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="N49" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="O49" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="P49" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="R49" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="U49" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V49" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="W49" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X49" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="Y49" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA49" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE49" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AF49" t="n">
         <v>22</v>
       </c>
       <c r="AG49" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH49" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AI49" t="n">
         <v>500</v>
       </c>
       <c r="AJ49" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK49" t="n">
         <v>500</v>
@@ -9977,68 +9977,68 @@
         <v>500</v>
       </c>
       <c r="AN49" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO49" t="n">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="AP49" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ49" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR49" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT49" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AU49" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV49" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX49" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY49" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AZ49" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BA49" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB49" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC49" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD49" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BE49" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BF49" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BG49" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -10072,13 +10072,13 @@
         <v>2.88</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H50" t="n">
         <v>2.76</v>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J50" t="n">
         <v>3.2</v>
@@ -10087,7 +10087,7 @@
         <v>3.4</v>
       </c>
       <c r="L50" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M50" t="n">
         <v>1.11</v>
@@ -10099,7 +10099,7 @@
         <v>1.47</v>
       </c>
       <c r="P50" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q50" t="n">
         <v>2.44</v>
@@ -10108,7 +10108,7 @@
         <v>1.24</v>
       </c>
       <c r="S50" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T50" t="n">
         <v>1.96</v>
@@ -10222,7 +10222,7 @@
         <v>7.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF50" t="n">
         <v>34</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -10269,16 +10269,16 @@
         <v>3.5</v>
       </c>
       <c r="H51" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J51" t="n">
         <v>3.25</v>
       </c>
       <c r="K51" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L51" t="n">
         <v>1.55</v>
@@ -10305,7 +10305,7 @@
         <v>5.3</v>
       </c>
       <c r="T51" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U51" t="n">
         <v>1.81</v>
@@ -10371,7 +10371,7 @@
         <v>500</v>
       </c>
       <c r="AP51" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AQ51" t="n">
         <v>6</v>
@@ -10383,7 +10383,7 @@
         <v>16</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU51" t="n">
         <v>6.6</v>
@@ -10404,29 +10404,29 @@
         <v>18.5</v>
       </c>
       <c r="BA51" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC51" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>8</v>
       </c>
       <c r="BD51" t="n">
         <v>10</v>
       </c>
       <c r="BE51" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF51" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG51" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -10460,13 +10460,13 @@
         <v>1.04</v>
       </c>
       <c r="G52" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H52" t="n">
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J52" t="n">
         <v>1.02</v>
@@ -10481,13 +10481,13 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O52" t="n">
         <v>1.25</v>
       </c>
       <c r="P52" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q52" t="n">
         <v>1.25</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
         <v>3.45</v>
       </c>
       <c r="J53" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K53" t="n">
         <v>3.35</v>
@@ -10675,10 +10675,10 @@
         <v>1.11</v>
       </c>
       <c r="N53" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O53" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P53" t="n">
         <v>1.64</v>
@@ -10693,7 +10693,7 @@
         <v>4.9</v>
       </c>
       <c r="T53" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U53" t="n">
         <v>1.88</v>
@@ -10714,7 +10714,7 @@
         <v>23</v>
       </c>
       <c r="AA53" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB53" t="n">
         <v>8.4</v>
@@ -10723,7 +10723,7 @@
         <v>7.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE53" t="n">
         <v>50</v>
@@ -10741,10 +10741,10 @@
         <v>70</v>
       </c>
       <c r="AJ53" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK53" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL53" t="n">
         <v>55</v>
@@ -10753,10 +10753,10 @@
         <v>150</v>
       </c>
       <c r="AN53" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO53" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP53" t="n">
         <v>9</v>
@@ -10768,13 +10768,13 @@
         <v>19</v>
       </c>
       <c r="AS53" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT53" t="n">
         <v>7.2</v>
       </c>
       <c r="AU53" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV53" t="n">
         <v>12</v>
@@ -10789,32 +10789,32 @@
         <v>10</v>
       </c>
       <c r="AZ53" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA53" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC53" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BD53" t="n">
         <v>40</v>
       </c>
       <c r="BE53" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF53" t="n">
         <v>26</v>
       </c>
       <c r="BG53" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -10845,22 +10845,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G54" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H54" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I54" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J54" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K54" t="n">
         <v>3.25</v>
-      </c>
-      <c r="K54" t="n">
-        <v>3.3</v>
       </c>
       <c r="L54" t="n">
         <v>1.6</v>
@@ -10869,7 +10869,7 @@
         <v>1.13</v>
       </c>
       <c r="N54" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O54" t="n">
         <v>1.57</v>
@@ -10878,34 +10878,34 @@
         <v>1.54</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R54" t="n">
         <v>1.19</v>
       </c>
       <c r="S54" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U54" t="n">
         <v>1.76</v>
       </c>
       <c r="V54" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W54" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X54" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y54" t="n">
         <v>8.6</v>
       </c>
       <c r="Z54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA54" t="n">
         <v>55</v>
@@ -10944,7 +10944,7 @@
         <v>75</v>
       </c>
       <c r="AM54" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN54" t="n">
         <v>55</v>
@@ -10953,7 +10953,7 @@
         <v>55</v>
       </c>
       <c r="AP54" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ54" t="n">
         <v>7.6</v>
@@ -10977,38 +10977,38 @@
         <v>34</v>
       </c>
       <c r="AX54" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY54" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ54" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BB54" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC54" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD54" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BE54" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF54" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BF54" t="n">
-        <v>12</v>
       </c>
       <c r="BG54" t="n">
         <v>38</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
         <v>2.44</v>
       </c>
       <c r="G55" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H55" t="n">
         <v>2.86</v>
@@ -11090,7 +11090,7 @@
         <v>1.5</v>
       </c>
       <c r="W55" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X55" t="n">
         <v>21</v>
@@ -11168,7 +11168,7 @@
         <v>10.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX55" t="n">
         <v>15</v>
@@ -11180,16 +11180,16 @@
         <v>12</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB55" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC55" t="n">
         <v>18.5</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE55" t="n">
         <v>5.7</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
         <v>6.4</v>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J56" t="n">
         <v>4.7</v>
@@ -11254,7 +11254,7 @@
         <v>1.29</v>
       </c>
       <c r="M56" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N56" t="n">
         <v>5.7</v>
@@ -11269,16 +11269,16 @@
         <v>1.59</v>
       </c>
       <c r="R56" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S56" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T56" t="n">
         <v>1.72</v>
       </c>
       <c r="U56" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V56" t="n">
         <v>1.17</v>
@@ -11287,13 +11287,13 @@
         <v>2.78</v>
       </c>
       <c r="X56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y56" t="n">
         <v>30</v>
       </c>
       <c r="Z56" t="n">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="AA56" t="n">
         <v>210</v>
@@ -11308,7 +11308,7 @@
         <v>25</v>
       </c>
       <c r="AE56" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF56" t="n">
         <v>11</v>
@@ -11317,13 +11317,13 @@
         <v>10.5</v>
       </c>
       <c r="AH56" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI56" t="n">
         <v>70</v>
       </c>
       <c r="AJ56" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK56" t="n">
         <v>14.5</v>
@@ -11332,10 +11332,10 @@
         <v>27</v>
       </c>
       <c r="AM56" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN56" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AO56" t="n">
         <v>70</v>
@@ -11344,7 +11344,7 @@
         <v>21</v>
       </c>
       <c r="AQ56" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR56" t="n">
         <v>29</v>
@@ -11359,7 +11359,7 @@
         <v>10</v>
       </c>
       <c r="AV56" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AW56" t="n">
         <v>34</v>
@@ -11371,13 +11371,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ56" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA56" t="n">
         <v>32</v>
       </c>
       <c r="BB56" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC56" t="n">
         <v>13</v>
@@ -11389,14 +11389,14 @@
         <v>36</v>
       </c>
       <c r="BF56" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG56" t="n">
         <v>34</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
         <v>1.11</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O57" t="n">
         <v>1.47</v>
@@ -11466,7 +11466,7 @@
         <v>1.23</v>
       </c>
       <c r="S57" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T57" t="n">
         <v>2.02</v>
@@ -11568,7 +11568,7 @@
         <v>18.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB57" t="n">
         <v>27</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
         <v>3.3</v>
       </c>
       <c r="H58" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I58" t="n">
         <v>2.64</v>
@@ -11639,13 +11639,13 @@
         <v>3.35</v>
       </c>
       <c r="L58" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M58" t="n">
         <v>1.09</v>
       </c>
       <c r="N58" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O58" t="n">
         <v>1.42</v>
@@ -11663,7 +11663,7 @@
         <v>4.3</v>
       </c>
       <c r="T58" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U58" t="n">
         <v>1.96</v>
@@ -11684,7 +11684,7 @@
         <v>16</v>
       </c>
       <c r="AA58" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB58" t="n">
         <v>12.5</v>
@@ -11708,7 +11708,7 @@
         <v>21</v>
       </c>
       <c r="AI58" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ58" t="n">
         <v>60</v>
@@ -11738,7 +11738,7 @@
         <v>13.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT58" t="n">
         <v>9.4</v>
@@ -11750,10 +11750,10 @@
         <v>10.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX58" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY58" t="n">
         <v>11.5</v>
@@ -11774,17 +11774,17 @@
         <v>46</v>
       </c>
       <c r="BE58" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF58" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG58" t="n">
         <v>22</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -11857,7 +11857,7 @@
         <v>1.24</v>
       </c>
       <c r="T59" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U59" t="n">
         <v>1.11</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="G2" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.35</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -817,28 +817,28 @@
         <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>18</v>
@@ -847,10 +847,10 @@
         <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
@@ -859,49 +859,49 @@
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AP2" t="n">
         <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
         <v>46</v>
       </c>
       <c r="BB2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC2" t="n">
         <v>25</v>
@@ -910,17 +910,17 @@
         <v>38</v>
       </c>
       <c r="BE2" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
         <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I4" t="n">
         <v>5.6</v>
       </c>
       <c r="J4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.4</v>
       </c>
-      <c r="K4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG4" t="n">
         <v>9.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
         <v>17</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="AP4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AR4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
         <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4" t="n">
         <v>60</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G5" t="n">
         <v>1.61</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
@@ -1369,10 +1369,10 @@
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
         <v>1.58</v>
@@ -1381,10 +1381,10 @@
         <v>2.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V5" t="n">
         <v>1.18</v>
@@ -1393,7 +1393,7 @@
         <v>2.64</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y5" t="n">
         <v>26</v>
@@ -1405,7 +1405,7 @@
         <v>170</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
@@ -1420,7 +1420,7 @@
         <v>11</v>
       </c>
       <c r="AG5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
         <v>19.5</v>
@@ -1438,7 +1438,7 @@
         <v>28</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
         <v>6.8</v>
@@ -1453,19 +1453,19 @@
         <v>23</v>
       </c>
       <c r="AR5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS5" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU5" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
         <v>55</v>
@@ -1474,22 +1474,22 @@
         <v>9.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
         <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE5" t="n">
         <v>75</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H6" t="n">
         <v>3.1</v>
@@ -1545,130 +1545,130 @@
         <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>12</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P6" t="n">
         <v>4.6</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N6" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U6" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.6</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X6" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="Y6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="Z6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
         <v>27</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
         <v>13.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK6" t="n">
         <v>18.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AM6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>34</v>
       </c>
-      <c r="AN6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>28</v>
-      </c>
       <c r="AR6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
         <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
         <v>12.5</v>
@@ -1680,23 +1680,23 @@
         <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="H7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I7" t="n">
         <v>6.8</v>
       </c>
-      <c r="I7" t="n">
-        <v>7.4</v>
-      </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
         <v>4.6</v>
@@ -1748,7 +1748,7 @@
         <v>1.39</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
         <v>4.2</v>
@@ -1760,7 +1760,7 @@
         <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
         <v>1.42</v>
@@ -1769,82 +1769,82 @@
         <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W7" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z7" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>480</v>
+        <v>95</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK7" t="n">
         <v>16.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO7" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AP7" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR7" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AT7" t="n">
         <v>7.8</v>
@@ -1853,44 +1853,44 @@
         <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG7" t="n">
         <v>13.5</v>
       </c>
-      <c r="BD7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>11</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1921,88 +1921,88 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="I8" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R8" t="n">
         <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AB8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
         <v>10.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
@@ -2017,31 +2017,31 @@
         <v>260</v>
       </c>
       <c r="AL8" t="n">
-        <v>440</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>320</v>
+        <v>130</v>
       </c>
       <c r="AO8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS8" t="n">
         <v>15.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -2053,38 +2053,38 @@
         <v>15.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AY8" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.74</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.57</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG9" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>7</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="H10" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
@@ -2339,13 +2339,13 @@
         <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
         <v>3.05</v>
@@ -2354,125 +2354,125 @@
         <v>1.66</v>
       </c>
       <c r="U10" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AB10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
         <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF10" t="n">
         <v>26</v>
       </c>
-      <c r="AF10" t="n">
-        <v>23</v>
-      </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
         <v>15.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AN10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU10" t="n">
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX10" t="n">
         <v>22</v>
       </c>
-      <c r="AX10" t="n">
-        <v>19</v>
-      </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC10" t="n">
         <v>30</v>
       </c>
-      <c r="BB10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>27</v>
-      </c>
       <c r="BD10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE10" t="n">
         <v>46</v>
       </c>
       <c r="BF10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BG10" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2509,13 +2509,13 @@
         <v>2.38</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
@@ -2527,88 +2527,88 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
         <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
         <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
         <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ11" t="n">
         <v>32</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
@@ -2617,19 +2617,19 @@
         <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU11" t="n">
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>34</v>
@@ -2638,35 +2638,35 @@
         <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BB11" t="n">
         <v>27</v>
       </c>
       <c r="BC11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD11" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BF11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2697,121 +2697,121 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
         <v>2.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA12" t="n">
         <v>440</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="AJ12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR12" t="n">
         <v>21</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>17.5</v>
       </c>
       <c r="AS12" t="n">
         <v>27</v>
@@ -2820,47 +2820,47 @@
         <v>10.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV12" t="n">
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY12" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BE12" t="n">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="H13" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.4</v>
@@ -2915,64 +2915,64 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
         <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
         <v>18.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AA13" t="n">
         <v>440</v>
       </c>
       <c r="AB13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
         <v>25</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="AF13" t="n">
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AH13" t="n">
         <v>60</v>
@@ -2981,7 +2981,7 @@
         <v>290</v>
       </c>
       <c r="AJ13" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>80</v>
@@ -2993,68 +2993,68 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO13" t="n">
         <v>55</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>600</v>
       </c>
       <c r="AP13" t="n">
         <v>7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AX13" t="n">
         <v>7.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC13" t="n">
         <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3085,100 +3085,100 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="I14" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.55</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC14" t="n">
         <v>9</v>
       </c>
-      <c r="Z14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8</v>
-      </c>
       <c r="AD14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AG14" t="n">
-        <v>85</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ14" t="n">
         <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL14" t="n">
         <v>500</v>
@@ -3190,65 +3190,65 @@
         <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS14" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY14" t="n">
         <v>15</v>
       </c>
-      <c r="AX14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BC14" t="n">
         <v>19.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3288,10 +3288,10 @@
         <v>1.35</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="J15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K15" t="n">
         <v>6.6</v>
@@ -3303,28 +3303,28 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U15" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="V15" t="n">
         <v>3.5</v>
@@ -3336,7 +3336,7 @@
         <v>950</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
         <v>8.800000000000001</v>
@@ -3372,22 +3372,22 @@
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM15" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AO15" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15" t="n">
         <v>7.6</v>
@@ -3399,7 +3399,7 @@
         <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU15" t="n">
         <v>11</v>
@@ -3411,38 +3411,38 @@
         <v>12</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG15" t="n">
         <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3473,115 +3473,115 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="T16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.95</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.96</v>
-      </c>
       <c r="X16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
         <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>210</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>370</v>
+        <v>230</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AK16" t="n">
         <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>11.5</v>
@@ -3590,19 +3590,19 @@
         <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU16" t="n">
         <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AX16" t="n">
         <v>9.4</v>
@@ -3611,32 +3611,32 @@
         <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC16" t="n">
         <v>20</v>
       </c>
       <c r="BD16" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H17" t="n">
         <v>3.1</v>
       </c>
       <c r="I17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
@@ -3694,7 +3694,7 @@
         <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
         <v>2.32</v>
@@ -3703,10 +3703,10 @@
         <v>1.69</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
         <v>1.6</v>
@@ -3718,7 +3718,7 @@
         <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X17" t="n">
         <v>22</v>
@@ -3799,7 +3799,7 @@
         <v>14.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY17" t="n">
         <v>9.800000000000001</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -3861,73 +3861,73 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
         <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
         <v>44</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AC18" t="n">
         <v>13</v>
@@ -3942,7 +3942,7 @@
         <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AH18" t="n">
         <v>60</v>
@@ -3954,7 +3954,7 @@
         <v>170</v>
       </c>
       <c r="AK18" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="n">
         <v>290</v>
@@ -3963,13 +3963,13 @@
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
         <v>600</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ18" t="n">
         <v>6.2</v>
@@ -3978,22 +3978,22 @@
         <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AU18" t="n">
         <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY18" t="n">
         <v>7</v>
@@ -4002,29 +4002,29 @@
         <v>11.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -4055,58 +4055,58 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I19" t="n">
         <v>4.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.89</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.92</v>
       </c>
       <c r="V19" t="n">
         <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X19" t="n">
         <v>29</v>
@@ -4124,7 +4124,7 @@
         <v>40</v>
       </c>
       <c r="AC19" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD19" t="n">
         <v>970</v>
@@ -4163,31 +4163,31 @@
         <v>600</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ19" t="n">
         <v>6.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AS19" t="n">
         <v>4.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AV19" t="n">
         <v>6.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY19" t="n">
         <v>5.5</v>
@@ -4199,26 +4199,26 @@
         <v>4.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.04</v>
+        <v>2.84</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G20" t="n">
         <v>2.9</v>
@@ -4258,7 +4258,7 @@
         <v>2.64</v>
       </c>
       <c r="I20" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J20" t="n">
         <v>3.4</v>
@@ -4267,7 +4267,7 @@
         <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M20" t="n">
         <v>1.07</v>
@@ -4276,28 +4276,28 @@
         <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P20" t="n">
         <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R20" t="n">
         <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U20" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
         <v>1.54</v>
@@ -4324,7 +4324,7 @@
         <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
         <v>19</v>
@@ -4339,22 +4339,22 @@
         <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AK20" t="n">
         <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
       </c>
       <c r="AN20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO20" t="n">
         <v>27</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>28</v>
       </c>
       <c r="AP20" t="n">
         <v>10.5</v>
@@ -4390,29 +4390,29 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G21" t="n">
         <v>1.55</v>
       </c>
-      <c r="G21" t="n">
-        <v>1.57</v>
-      </c>
       <c r="H21" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="I21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J21" t="n">
         <v>4.7</v>
@@ -4467,40 +4467,40 @@
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S21" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V21" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X21" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="Y21" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="Z21" t="n">
         <v>420</v>
@@ -4521,25 +4521,25 @@
         <v>480</v>
       </c>
       <c r="AF21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI21" t="n">
         <v>390</v>
       </c>
       <c r="AJ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK21" t="n">
         <v>15</v>
       </c>
-      <c r="AK21" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AL21" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
         <v>580</v>
@@ -4551,13 +4551,13 @@
         <v>700</v>
       </c>
       <c r="AP21" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AS21" t="n">
         <v>11.5</v>
@@ -4569,34 +4569,34 @@
         <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BB21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BE21" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BF21" t="n">
         <v>5.4</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="H22" t="n">
         <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
         <v>1.45</v>
@@ -4679,16 +4679,16 @@
         <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="X22" t="n">
         <v>13</v>
@@ -4697,7 +4697,7 @@
         <v>15.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -4709,13 +4709,13 @@
         <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
@@ -4724,7 +4724,7 @@
         <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>370</v>
+        <v>130</v>
       </c>
       <c r="AJ22" t="n">
         <v>110</v>
@@ -4733,16 +4733,16 @@
         <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO22" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AP22" t="n">
         <v>10.5</v>
@@ -4751,34 +4751,34 @@
         <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT22" t="n">
         <v>7.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AX22" t="n">
         <v>10.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
@@ -4787,20 +4787,20 @@
         <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.2</v>
+        <v>48</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G23" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H23" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="I23" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
         <v>3.6</v>
@@ -4864,37 +4864,37 @@
         <v>2.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
         <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X23" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Y23" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="Z23" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AA23" t="n">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB23" t="n">
         <v>13</v>
@@ -4909,22 +4909,22 @@
         <v>500</v>
       </c>
       <c r="AF23" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AG23" t="n">
         <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
         <v>500</v>
       </c>
       <c r="AJ23" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL23" t="n">
         <v>500</v>
@@ -4933,22 +4933,22 @@
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AO23" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AP23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>8.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="AT23" t="n">
         <v>10.5</v>
@@ -4960,7 +4960,7 @@
         <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX23" t="n">
         <v>15.5</v>
@@ -4969,32 +4969,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BD23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BE23" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF23" t="n">
         <v>15.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="G24" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H24" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.33</v>
@@ -5067,43 +5067,43 @@
         <v>2.74</v>
       </c>
       <c r="T24" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W24" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z24" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA24" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD24" t="n">
         <v>19.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="AF24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG24" t="n">
         <v>10</v>
@@ -5112,61 +5112,61 @@
         <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK24" t="n">
         <v>16.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AM24" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AN24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO24" t="n">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="AP24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB24" t="n">
         <v>16</v>
@@ -5178,17 +5178,17 @@
         <v>24</v>
       </c>
       <c r="BE24" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BF24" t="n">
         <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -5225,13 +5225,13 @@
         <v>2.58</v>
       </c>
       <c r="H25" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I25" t="n">
         <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
@@ -5336,13 +5336,13 @@
         <v>10</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
         <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AV25" t="n">
         <v>7</v>
@@ -5366,23 +5366,23 @@
         <v>15</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
         <v>8.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF25" t="n">
         <v>6.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -5467,10 +5467,10 @@
         <v>2.4</v>
       </c>
       <c r="X26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y26" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="Z26" t="n">
         <v>140</v>
@@ -5482,40 +5482,40 @@
         <v>10</v>
       </c>
       <c r="AC26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
         <v>500</v>
       </c>
       <c r="AE26" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AF26" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH26" t="n">
         <v>60</v>
       </c>
       <c r="AI26" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK26" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AL26" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO26" t="n">
         <v>700</v>
@@ -5527,10 +5527,10 @@
         <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="AS26" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT26" t="n">
         <v>8.6</v>
@@ -5539,10 +5539,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AW26" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AX26" t="n">
         <v>9.4</v>
@@ -5554,7 +5554,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>27</v>
+        <v>9.4</v>
       </c>
       <c r="BB26" t="n">
         <v>9.199999999999999</v>
@@ -5563,20 +5563,20 @@
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF26" t="n">
         <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="H27" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L27" t="n">
         <v>1.37</v>
@@ -5640,25 +5640,25 @@
         <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R27" t="n">
         <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U27" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="X27" t="n">
         <v>21</v>
@@ -5670,13 +5670,13 @@
         <v>34</v>
       </c>
       <c r="AA27" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
         <v>13</v>
       </c>
       <c r="AC27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
         <v>18</v>
@@ -5688,10 +5688,10 @@
         <v>18</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="n">
         <v>55</v>
@@ -5700,7 +5700,7 @@
         <v>34</v>
       </c>
       <c r="AK27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
         <v>42</v>
@@ -5721,10 +5721,10 @@
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.9</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
         <v>9.6</v>
@@ -5733,13 +5733,13 @@
         <v>7.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY27" t="n">
         <v>9.6</v>
@@ -5748,29 +5748,29 @@
         <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BC27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF27" t="n">
         <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
         <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
         <v>1.76</v>
@@ -5852,7 +5852,7 @@
         <v>1.21</v>
       </c>
       <c r="W28" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X28" t="n">
         <v>32</v>
@@ -5912,7 +5912,7 @@
         <v>9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AR28" t="n">
         <v>18.5</v>
@@ -5921,7 +5921,7 @@
         <v>9</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
@@ -5930,25 +5930,25 @@
         <v>16.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>27</v>
+        <v>8.6</v>
       </c>
       <c r="AX28" t="n">
         <v>5.8</v>
       </c>
       <c r="AY28" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AZ28" t="n">
         <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
         <v>9</v>
       </c>
       <c r="BC28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>12.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -6004,13 +6004,13 @@
         <v>4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L29" t="n">
         <v>1.5</v>
@@ -6025,16 +6025,16 @@
         <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q29" t="n">
         <v>2.34</v>
       </c>
       <c r="R29" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T29" t="n">
         <v>2</v>
@@ -6043,10 +6043,10 @@
         <v>1.84</v>
       </c>
       <c r="V29" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W29" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X29" t="n">
         <v>25</v>
@@ -6085,7 +6085,7 @@
         <v>500</v>
       </c>
       <c r="AJ29" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
         <v>65</v>
@@ -6109,10 +6109,10 @@
         <v>8.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
         <v>6.4</v>
@@ -6124,16 +6124,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AX29" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BA29" t="n">
         <v>10.5</v>
@@ -6145,7 +6145,7 @@
         <v>10.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE29" t="n">
         <v>11</v>
@@ -6154,11 +6154,11 @@
         <v>15</v>
       </c>
       <c r="BG29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
         <v>4.9</v>
       </c>
       <c r="K30" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L30" t="n">
         <v>1.29</v>
@@ -6222,7 +6222,7 @@
         <v>2.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R30" t="n">
         <v>1.6</v>
@@ -6231,7 +6231,7 @@
         <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U30" t="n">
         <v>2.12</v>
@@ -6240,13 +6240,13 @@
         <v>1.15</v>
       </c>
       <c r="W30" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="X30" t="n">
         <v>75</v>
       </c>
       <c r="Y30" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="Z30" t="n">
         <v>170</v>
@@ -6255,13 +6255,13 @@
         <v>190</v>
       </c>
       <c r="AB30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC30" t="n">
         <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AE30" t="n">
         <v>240</v>
@@ -6273,40 +6273,40 @@
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AI30" t="n">
         <v>200</v>
       </c>
       <c r="AJ30" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM30" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="AN30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO30" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AP30" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AQ30" t="n">
         <v>14.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT30" t="n">
         <v>9.199999999999999</v>
@@ -6315,19 +6315,19 @@
         <v>9.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX30" t="n">
         <v>8.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
         <v>9</v>
@@ -6339,20 +6339,20 @@
         <v>13.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG30" t="n">
         <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G31" t="n">
         <v>3.4</v>
@@ -6392,7 +6392,7 @@
         <v>2.32</v>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J31" t="n">
         <v>3.5</v>
@@ -6401,43 +6401,43 @@
         <v>3.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
         <v>1.24</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R31" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="T31" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U31" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V31" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W31" t="n">
         <v>1.41</v>
       </c>
       <c r="X31" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Y31" t="n">
         <v>13.5</v>
@@ -6446,10 +6446,10 @@
         <v>18</v>
       </c>
       <c r="AA31" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AB31" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC31" t="n">
         <v>8.800000000000001</v>
@@ -6458,7 +6458,7 @@
         <v>12.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF31" t="n">
         <v>25</v>
@@ -6467,31 +6467,31 @@
         <v>14.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI31" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ31" t="n">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c r="AK31" t="n">
         <v>90</v>
       </c>
       <c r="AL31" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM31" t="n">
         <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AO31" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>10</v>
@@ -6500,53 +6500,53 @@
         <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AT31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW31" t="n">
         <v>19</v>
       </c>
       <c r="AX31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY31" t="n">
         <v>12</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>23</v>
       </c>
       <c r="BC31" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="BD31" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BF31" t="n">
         <v>12</v>
       </c>
       <c r="BG31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -6577,49 +6577,49 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="G32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H32" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="I32" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J32" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K32" t="n">
         <v>5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M32" t="n">
         <v>1.04</v>
       </c>
       <c r="N32" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O32" t="n">
         <v>1.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R32" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S32" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="U32" t="n">
         <v>2.28</v>
@@ -6631,19 +6631,19 @@
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
         <v>12</v>
       </c>
       <c r="AA32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AC32" t="n">
         <v>11.5</v>
@@ -6655,52 +6655,52 @@
         <v>15.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AG32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH32" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ32" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AK32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL32" t="n">
         <v>65</v>
       </c>
-      <c r="AL32" t="n">
-        <v>60</v>
-      </c>
       <c r="AM32" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN32" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO32" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AP32" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ32" t="n">
         <v>10.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU32" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV32" t="n">
         <v>9</v>
@@ -6709,38 +6709,38 @@
         <v>13.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY32" t="n">
         <v>19.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB32" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BD32" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="BE32" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BF32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>1.44</v>
       </c>
       <c r="G33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H33" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J33" t="n">
         <v>5.2</v>
       </c>
       <c r="K33" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L33" t="n">
         <v>1.26</v>
@@ -6795,25 +6795,25 @@
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O33" t="n">
         <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R33" t="n">
         <v>1.74</v>
       </c>
       <c r="S33" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T33" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U33" t="n">
         <v>2.28</v>
@@ -6825,10 +6825,10 @@
         <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="Y33" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="Z33" t="n">
         <v>160</v>
@@ -6837,34 +6837,34 @@
         <v>230</v>
       </c>
       <c r="AB33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC33" t="n">
         <v>13</v>
       </c>
-      <c r="AC33" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AD33" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AE33" t="n">
         <v>240</v>
       </c>
       <c r="AF33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AI33" t="n">
         <v>200</v>
       </c>
       <c r="AJ33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK33" t="n">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="AL33" t="n">
         <v>500</v>
@@ -6873,19 +6873,19 @@
         <v>100</v>
       </c>
       <c r="AN33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AO33" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP33" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AS33" t="n">
         <v>11.5</v>
@@ -6897,44 +6897,44 @@
         <v>10.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AW33" t="n">
         <v>10.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY33" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB33" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC33" t="n">
         <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BE33" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG33" t="n">
         <v>15</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -6965,40 +6965,40 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G34" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H34" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="I34" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="J34" t="n">
         <v>3.2</v>
       </c>
       <c r="K34" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L34" t="n">
         <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O34" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P34" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R34" t="n">
         <v>1.26</v>
@@ -7007,19 +7007,19 @@
         <v>4.4</v>
       </c>
       <c r="T34" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U34" t="n">
         <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W34" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
         <v>8.800000000000001</v>
@@ -7028,10 +7028,10 @@
         <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AB34" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC34" t="n">
         <v>7.6</v>
@@ -7040,22 +7040,22 @@
         <v>12</v>
       </c>
       <c r="AE34" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG34" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH34" t="n">
         <v>20</v>
       </c>
       <c r="AI34" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AJ34" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK34" t="n">
         <v>50</v>
@@ -7067,10 +7067,10 @@
         <v>580</v>
       </c>
       <c r="AN34" t="n">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AO34" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AP34" t="n">
         <v>9.6</v>
@@ -7082,10 +7082,10 @@
         <v>12.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT34" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
@@ -7106,7 +7106,7 @@
         <v>17</v>
       </c>
       <c r="BA34" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BB34" t="n">
         <v>23</v>
@@ -7115,20 +7115,20 @@
         <v>34</v>
       </c>
       <c r="BD34" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BE34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF34" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG34" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -7162,16 +7162,16 @@
         <v>4.8</v>
       </c>
       <c r="G35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H35" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I35" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K35" t="n">
         <v>4.7</v>
@@ -7186,7 +7186,7 @@
         <v>6</v>
       </c>
       <c r="O35" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P35" t="n">
         <v>2.74</v>
@@ -7201,7 +7201,7 @@
         <v>2.3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U35" t="n">
         <v>2.48</v>
@@ -7210,10 +7210,10 @@
         <v>2.28</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X35" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y35" t="n">
         <v>15.5</v>
@@ -7234,7 +7234,7 @@
         <v>12.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF35" t="n">
         <v>46</v>
@@ -7243,10 +7243,10 @@
         <v>22</v>
       </c>
       <c r="AH35" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI35" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ35" t="n">
         <v>700</v>
@@ -7258,16 +7258,16 @@
         <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>580</v>
+        <v>250</v>
       </c>
       <c r="AN35" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AO35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AP35" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ35" t="n">
         <v>11.5</v>
@@ -7276,53 +7276,53 @@
         <v>12</v>
       </c>
       <c r="AS35" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT35" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AU35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW35" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AX35" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>13.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="BD35" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BE35" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF35" t="n">
         <v>5.5</v>
       </c>
-      <c r="BF35" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG35" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -7353,61 +7353,61 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="G36" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="I36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J36" t="n">
         <v>3.75</v>
       </c>
-      <c r="J36" t="n">
-        <v>3.6</v>
-      </c>
       <c r="K36" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M36" t="n">
         <v>1.06</v>
       </c>
       <c r="N36" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.81</v>
-      </c>
       <c r="X36" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Y36" t="n">
         <v>970</v>
@@ -7425,7 +7425,7 @@
         <v>14</v>
       </c>
       <c r="AD36" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="AE36" t="n">
         <v>500</v>
@@ -7434,10 +7434,10 @@
         <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AH36" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI36" t="n">
         <v>500</v>
@@ -7455,68 +7455,68 @@
         <v>580</v>
       </c>
       <c r="AN36" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AO36" t="n">
         <v>600</v>
       </c>
       <c r="AP36" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AQ36" t="n">
         <v>6.2</v>
       </c>
       <c r="AR36" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AT36" t="n">
         <v>5.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV36" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW36" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX36" t="n">
         <v>6.8</v>
       </c>
       <c r="AY36" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ36" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB36" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BC36" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="BF36" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG36" t="n">
         <v>4.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -7547,19 +7547,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G37" t="n">
         <v>2.74</v>
       </c>
       <c r="H37" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J37" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
         <v>3.3</v>
@@ -7574,7 +7574,7 @@
         <v>2.48</v>
       </c>
       <c r="O37" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P37" t="n">
         <v>1.49</v>
@@ -7595,7 +7595,7 @@
         <v>1.69</v>
       </c>
       <c r="V37" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W37" t="n">
         <v>1.57</v>
@@ -7607,10 +7607,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA37" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB37" t="n">
         <v>7.8</v>
@@ -7622,7 +7622,7 @@
         <v>16</v>
       </c>
       <c r="AE37" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AF37" t="n">
         <v>16</v>
@@ -7643,7 +7643,7 @@
         <v>110</v>
       </c>
       <c r="AL37" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM37" t="n">
         <v>500</v>
@@ -7676,7 +7676,7 @@
         <v>13</v>
       </c>
       <c r="AW37" t="n">
-        <v>26</v>
+        <v>9.6</v>
       </c>
       <c r="AX37" t="n">
         <v>13.5</v>
@@ -7685,10 +7685,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA37" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="BB37" t="n">
         <v>17</v>
@@ -7697,20 +7697,20 @@
         <v>18.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF37" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG37" t="n">
-        <v>22</v>
+        <v>9.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -7765,10 +7765,10 @@
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P38" t="n">
         <v>1.66</v>
@@ -7783,10 +7783,10 @@
         <v>4.7</v>
       </c>
       <c r="T38" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U38" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V38" t="n">
         <v>1.13</v>
@@ -7813,7 +7813,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AE38" t="n">
         <v>200</v>
@@ -7825,7 +7825,7 @@
         <v>12.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AI38" t="n">
         <v>190</v>
@@ -7834,10 +7834,10 @@
         <v>17</v>
       </c>
       <c r="AK38" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL38" t="n">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="AM38" t="n">
         <v>700</v>
@@ -7855,7 +7855,7 @@
         <v>14.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="AS38" t="n">
         <v>8.4</v>
@@ -7882,7 +7882,7 @@
         <v>18.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB38" t="n">
         <v>13</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -7938,16 +7938,16 @@
         <v>2.36</v>
       </c>
       <c r="G39" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H39" t="n">
         <v>3.65</v>
       </c>
       <c r="I39" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K39" t="n">
         <v>3.3</v>
@@ -7959,7 +7959,7 @@
         <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O39" t="n">
         <v>1.46</v>
@@ -7968,7 +7968,7 @@
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R39" t="n">
         <v>1.23</v>
@@ -7980,13 +7980,13 @@
         <v>1.94</v>
       </c>
       <c r="U39" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V39" t="n">
         <v>1.36</v>
       </c>
       <c r="W39" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X39" t="n">
         <v>10</v>
@@ -8001,43 +8001,43 @@
         <v>900</v>
       </c>
       <c r="AB39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC39" t="n">
         <v>7.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AE39" t="n">
         <v>370</v>
       </c>
       <c r="AF39" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AG39" t="n">
         <v>12.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI39" t="n">
         <v>500</v>
       </c>
       <c r="AJ39" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK39" t="n">
         <v>85</v>
       </c>
       <c r="AL39" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM39" t="n">
         <v>580</v>
       </c>
       <c r="AN39" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AO39" t="n">
         <v>600</v>
@@ -8052,7 +8052,7 @@
         <v>19</v>
       </c>
       <c r="AS39" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT39" t="n">
         <v>7.4</v>
@@ -8073,32 +8073,32 @@
         <v>10</v>
       </c>
       <c r="AZ39" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB39" t="n">
         <v>12</v>
       </c>
-      <c r="BA39" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC39" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE39" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BG39" t="n">
         <v>14</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G40" t="n">
         <v>2.56</v>
@@ -8150,7 +8150,7 @@
         <v>1.69</v>
       </c>
       <c r="M40" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N40" t="n">
         <v>2.32</v>
@@ -8162,19 +8162,19 @@
         <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R40" t="n">
         <v>1.14</v>
       </c>
       <c r="S40" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V40" t="n">
         <v>1.37</v>
@@ -8204,7 +8204,7 @@
         <v>18</v>
       </c>
       <c r="AE40" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AF40" t="n">
         <v>14.5</v>
@@ -8213,7 +8213,7 @@
         <v>13.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="n">
         <v>540</v>
@@ -8237,7 +8237,7 @@
         <v>600</v>
       </c>
       <c r="AP40" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ40" t="n">
         <v>7.2</v>
@@ -8249,7 +8249,7 @@
         <v>10</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU40" t="n">
         <v>6.6</v>
@@ -8267,10 +8267,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BA40" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB40" t="n">
         <v>16</v>
@@ -8279,20 +8279,20 @@
         <v>32</v>
       </c>
       <c r="BD40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE40" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>10</v>
       </c>
       <c r="BF40" t="n">
         <v>36</v>
       </c>
       <c r="BG40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -8329,10 +8329,10 @@
         <v>1.38</v>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J41" t="n">
         <v>5.7</v>
@@ -8347,55 +8347,55 @@
         <v>1.03</v>
       </c>
       <c r="N41" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O41" t="n">
         <v>1.16</v>
       </c>
       <c r="P41" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q41" t="n">
         <v>1.51</v>
       </c>
       <c r="R41" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S41" t="n">
         <v>2.24</v>
       </c>
       <c r="T41" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U41" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V41" t="n">
         <v>1.1</v>
       </c>
       <c r="W41" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="X41" t="n">
         <v>30</v>
       </c>
       <c r="Y41" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Z41" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA41" t="n">
         <v>350</v>
       </c>
       <c r="AB41" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC41" t="n">
         <v>13.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE41" t="n">
         <v>130</v>
@@ -8407,10 +8407,10 @@
         <v>10.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI41" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ41" t="n">
         <v>12</v>
@@ -8419,52 +8419,52 @@
         <v>13.5</v>
       </c>
       <c r="AL41" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM41" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN41" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO41" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP41" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AR41" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AS41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT41" t="n">
         <v>11</v>
       </c>
       <c r="AU41" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AW41" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ41" t="n">
         <v>20</v>
       </c>
       <c r="BA41" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BB41" t="n">
         <v>10.5</v>
@@ -8476,17 +8476,17 @@
         <v>25</v>
       </c>
       <c r="BE41" t="n">
-        <v>14.5</v>
+        <v>80</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BG41" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G42" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H42" t="n">
         <v>3.7</v>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K42" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L42" t="n">
         <v>1.47</v>
@@ -8559,7 +8559,7 @@
         <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U42" t="n">
         <v>1.95</v>
@@ -8568,7 +8568,7 @@
         <v>1.33</v>
       </c>
       <c r="W42" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X42" t="n">
         <v>13</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -8720,16 +8720,16 @@
         <v>8.6</v>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L43" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
@@ -8738,10 +8738,10 @@
         <v>3.2</v>
       </c>
       <c r="O43" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q43" t="n">
         <v>2.28</v>
@@ -8753,10 +8753,10 @@
         <v>4.3</v>
       </c>
       <c r="T43" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U43" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V43" t="n">
         <v>1.11</v>
@@ -8768,22 +8768,22 @@
         <v>12</v>
       </c>
       <c r="Y43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z43" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA43" t="n">
         <v>480</v>
       </c>
-      <c r="AA43" t="n">
-        <v>490</v>
-      </c>
       <c r="AB43" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC43" t="n">
         <v>9.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AE43" t="n">
         <v>240</v>
@@ -8795,7 +8795,7 @@
         <v>12</v>
       </c>
       <c r="AH43" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AI43" t="n">
         <v>540</v>
@@ -8807,16 +8807,16 @@
         <v>21</v>
       </c>
       <c r="AL43" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM43" t="n">
         <v>290</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>300</v>
       </c>
       <c r="AN43" t="n">
         <v>11</v>
       </c>
       <c r="AO43" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="AP43" t="n">
         <v>10</v>
@@ -8825,25 +8825,25 @@
         <v>18</v>
       </c>
       <c r="AR43" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS43" t="n">
         <v>10</v>
       </c>
       <c r="AT43" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU43" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV43" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX43" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY43" t="n">
         <v>9.6</v>
@@ -8852,7 +8852,7 @@
         <v>15</v>
       </c>
       <c r="BA43" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB43" t="n">
         <v>12</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G44" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I44" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J44" t="n">
         <v>3.5</v>
       </c>
       <c r="K44" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L44" t="n">
         <v>1.41</v>
@@ -8932,13 +8932,13 @@
         <v>3.75</v>
       </c>
       <c r="O44" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P44" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R44" t="n">
         <v>1.36</v>
@@ -8947,40 +8947,40 @@
         <v>3.45</v>
       </c>
       <c r="T44" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U44" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V44" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W44" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="X44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y44" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA44" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB44" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD44" t="n">
         <v>20</v>
       </c>
       <c r="AE44" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AF44" t="n">
         <v>13</v>
@@ -8995,46 +8995,46 @@
         <v>160</v>
       </c>
       <c r="AJ44" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL44" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM44" t="n">
         <v>580</v>
       </c>
       <c r="AN44" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO44" t="n">
         <v>240</v>
       </c>
       <c r="AP44" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR44" t="n">
         <v>14</v>
       </c>
       <c r="AS44" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT44" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU44" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX44" t="n">
         <v>10.5</v>
@@ -9043,10 +9043,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB44" t="n">
         <v>20</v>
@@ -9055,20 +9055,20 @@
         <v>18.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="BE44" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF44" t="n">
         <v>13</v>
       </c>
       <c r="BG44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="G45" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="H45" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="I45" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="J45" t="n">
         <v>3.2</v>
       </c>
       <c r="K45" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L45" t="n">
         <v>1.48</v>
@@ -9147,10 +9147,10 @@
         <v>1.98</v>
       </c>
       <c r="V45" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W45" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="X45" t="n">
         <v>12</v>
@@ -9174,10 +9174,10 @@
         <v>14</v>
       </c>
       <c r="AE45" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG45" t="n">
         <v>13</v>
@@ -9189,10 +9189,10 @@
         <v>55</v>
       </c>
       <c r="AJ45" t="n">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="AK45" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL45" t="n">
         <v>120</v>
@@ -9201,22 +9201,22 @@
         <v>580</v>
       </c>
       <c r="AN45" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO45" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP45" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ45" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR45" t="n">
         <v>15.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT45" t="n">
         <v>8.6</v>
@@ -9228,41 +9228,41 @@
         <v>11</v>
       </c>
       <c r="AW45" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX45" t="n">
         <v>16</v>
       </c>
       <c r="AY45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ45" t="n">
         <v>15.5</v>
       </c>
       <c r="BA45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG45" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB45" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G46" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H46" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I46" t="n">
         <v>3.7</v>
       </c>
       <c r="J46" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K46" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L46" t="n">
         <v>1.48</v>
@@ -9326,19 +9326,19 @@
         <v>1.71</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R46" t="n">
         <v>1.26</v>
       </c>
       <c r="S46" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T46" t="n">
         <v>1.88</v>
       </c>
       <c r="U46" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V46" t="n">
         <v>1.37</v>
@@ -9428,10 +9428,10 @@
         <v>11</v>
       </c>
       <c r="AY46" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ46" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BA46" t="n">
         <v>8.800000000000001</v>
@@ -9440,7 +9440,7 @@
         <v>7.6</v>
       </c>
       <c r="BC46" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="BD46" t="n">
         <v>8.4</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -9487,76 +9487,76 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="G47" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H47" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
         <v>3.2</v>
       </c>
       <c r="K47" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L47" t="n">
         <v>1.48</v>
       </c>
       <c r="M47" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O47" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P47" t="n">
         <v>1.73</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R47" t="n">
         <v>1.27</v>
       </c>
       <c r="S47" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T47" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="U47" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="V47" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W47" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X47" t="n">
         <v>11.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z47" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AA47" t="n">
         <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD47" t="n">
         <v>29</v>
@@ -9565,7 +9565,7 @@
         <v>500</v>
       </c>
       <c r="AF47" t="n">
-        <v>70</v>
+        <v>12.5</v>
       </c>
       <c r="AG47" t="n">
         <v>36</v>
@@ -9577,7 +9577,7 @@
         <v>500</v>
       </c>
       <c r="AJ47" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AK47" t="n">
         <v>150</v>
@@ -9589,7 +9589,7 @@
         <v>580</v>
       </c>
       <c r="AN47" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO47" t="n">
         <v>600</v>
@@ -9604,7 +9604,7 @@
         <v>21</v>
       </c>
       <c r="AS47" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT47" t="n">
         <v>6.8</v>
@@ -9616,7 +9616,7 @@
         <v>13</v>
       </c>
       <c r="AW47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX47" t="n">
         <v>10</v>
@@ -9625,10 +9625,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ47" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BA47" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB47" t="n">
         <v>21</v>
@@ -9637,20 +9637,20 @@
         <v>20</v>
       </c>
       <c r="BD47" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE47" t="n">
         <v>10</v>
       </c>
       <c r="BF47" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG47" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
         <v>5.8</v>
       </c>
       <c r="L48" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M48" t="n">
         <v>1.01</v>
@@ -9717,10 +9717,10 @@
         <v>1.24</v>
       </c>
       <c r="R48" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="S48" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="T48" t="n">
         <v>1.31</v>
@@ -9750,7 +9750,7 @@
         <v>30</v>
       </c>
       <c r="AC48" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AD48" t="n">
         <v>22</v>
@@ -9759,7 +9759,7 @@
         <v>40</v>
       </c>
       <c r="AF48" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG48" t="n">
         <v>12.5</v>
@@ -9774,37 +9774,37 @@
         <v>24</v>
       </c>
       <c r="AK48" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL48" t="n">
         <v>18</v>
       </c>
       <c r="AM48" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AN48" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AO48" t="n">
         <v>16.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AQ48" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AR48" t="n">
         <v>50</v>
       </c>
       <c r="AS48" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AT48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU48" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AV48" t="n">
         <v>21</v>
@@ -9813,7 +9813,7 @@
         <v>38</v>
       </c>
       <c r="AX48" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY48" t="n">
         <v>12</v>
@@ -9828,7 +9828,7 @@
         <v>23</v>
       </c>
       <c r="BC48" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD48" t="n">
         <v>17.5</v>
@@ -9837,14 +9837,14 @@
         <v>29</v>
       </c>
       <c r="BF48" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BG48" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -9875,52 +9875,52 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G49" t="n">
         <v>3.6</v>
       </c>
       <c r="H49" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I49" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J49" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L49" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="M49" t="n">
         <v>1.17</v>
       </c>
       <c r="N49" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O49" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="P49" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R49" t="n">
         <v>1.15</v>
       </c>
       <c r="S49" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="T49" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U49" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V49" t="n">
         <v>1.52</v>
@@ -9929,16 +9929,16 @@
         <v>1.39</v>
       </c>
       <c r="X49" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y49" t="n">
         <v>7.4</v>
       </c>
       <c r="Z49" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AB49" t="n">
         <v>8.4</v>
@@ -9947,25 +9947,25 @@
         <v>7.4</v>
       </c>
       <c r="AD49" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG49" t="n">
         <v>16</v>
       </c>
-      <c r="AE49" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>18</v>
-      </c>
       <c r="AH49" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AI49" t="n">
         <v>500</v>
       </c>
       <c r="AJ49" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AK49" t="n">
         <v>500</v>
@@ -9983,19 +9983,19 @@
         <v>600</v>
       </c>
       <c r="AP49" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ49" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR49" t="n">
         <v>13.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AT49" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU49" t="n">
         <v>6</v>
@@ -10004,41 +10004,41 @@
         <v>12.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AX49" t="n">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY49" t="n">
         <v>14</v>
       </c>
       <c r="AZ49" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BA49" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB49" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BC49" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BD49" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BE49" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF49" t="n">
         <v>9.4</v>
       </c>
-      <c r="BF49" t="n">
-        <v>9</v>
-      </c>
       <c r="BG49" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G50" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
         <v>2.76</v>
@@ -10084,7 +10084,7 @@
         <v>3.2</v>
       </c>
       <c r="K50" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L50" t="n">
         <v>1.53</v>
@@ -10099,7 +10099,7 @@
         <v>1.47</v>
       </c>
       <c r="P50" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q50" t="n">
         <v>2.44</v>
@@ -10111,7 +10111,7 @@
         <v>4.9</v>
       </c>
       <c r="T50" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U50" t="n">
         <v>1.9</v>
@@ -10126,7 +10126,7 @@
         <v>10.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z50" t="n">
         <v>22</v>
@@ -10138,7 +10138,7 @@
         <v>9.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD50" t="n">
         <v>13.5</v>
@@ -10147,7 +10147,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG50" t="n">
         <v>13.5</v>
@@ -10171,10 +10171,10 @@
         <v>580</v>
       </c>
       <c r="AN50" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO50" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP50" t="n">
         <v>9</v>
@@ -10183,10 +10183,10 @@
         <v>8</v>
       </c>
       <c r="AR50" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS50" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT50" t="n">
         <v>8.199999999999999</v>
@@ -10201,7 +10201,7 @@
         <v>30</v>
       </c>
       <c r="AX50" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AY50" t="n">
         <v>11.5</v>
@@ -10210,19 +10210,19 @@
         <v>17.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB50" t="n">
         <v>40</v>
       </c>
       <c r="BC50" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="BD50" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BE50" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BF50" t="n">
         <v>34</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -10263,25 +10263,25 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G51" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H51" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I51" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J51" t="n">
         <v>3.25</v>
       </c>
       <c r="K51" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L51" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M51" t="n">
         <v>1.11</v>
@@ -10299,134 +10299,134 @@
         <v>2.58</v>
       </c>
       <c r="R51" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S51" t="n">
         <v>5.3</v>
       </c>
       <c r="T51" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U51" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V51" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W51" t="n">
         <v>1.4</v>
       </c>
       <c r="X51" t="n">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y51" t="n">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z51" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AA51" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB51" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD51" t="n">
         <v>12.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AF51" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AG51" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI51" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AJ51" t="n">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="AK51" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AL51" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM51" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN51" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AO51" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AP51" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR51" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS51" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AU51" t="n">
         <v>6.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW51" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AX51" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AY51" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF51" t="n">
         <v>13</v>
       </c>
-      <c r="AZ51" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG51" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -10460,16 +10460,16 @@
         <v>1.04</v>
       </c>
       <c r="G52" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H52" t="n">
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="J52" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K52" t="n">
         <v>950</v>
@@ -10478,16 +10478,16 @@
         <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N52" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O52" t="n">
         <v>1.25</v>
       </c>
       <c r="P52" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q52" t="n">
         <v>1.25</v>
@@ -10505,10 +10505,10 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G53" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H53" t="n">
         <v>3.25</v>
       </c>
       <c r="I53" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>3.2</v>
@@ -10672,7 +10672,7 @@
         <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N53" t="n">
         <v>2.98</v>
@@ -10687,25 +10687,25 @@
         <v>2.46</v>
       </c>
       <c r="R53" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S53" t="n">
         <v>4.9</v>
       </c>
       <c r="T53" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U53" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="V53" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W53" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X53" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y53" t="n">
         <v>10.5</v>
@@ -10729,7 +10729,7 @@
         <v>50</v>
       </c>
       <c r="AF53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG53" t="n">
         <v>12.5</v>
@@ -10768,7 +10768,7 @@
         <v>19</v>
       </c>
       <c r="AS53" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT53" t="n">
         <v>7.2</v>
@@ -10792,10 +10792,10 @@
         <v>18</v>
       </c>
       <c r="BA53" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB53" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC53" t="n">
         <v>25</v>
@@ -10804,17 +10804,17 @@
         <v>40</v>
       </c>
       <c r="BE53" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF53" t="n">
         <v>26</v>
       </c>
       <c r="BG53" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -10845,19 +10845,19 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G54" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H54" t="n">
         <v>2.82</v>
       </c>
       <c r="I54" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J54" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K54" t="n">
         <v>3.25</v>
@@ -10887,13 +10887,13 @@
         <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U54" t="n">
         <v>1.76</v>
       </c>
       <c r="V54" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W54" t="n">
         <v>1.5</v>
@@ -10926,7 +10926,7 @@
         <v>18</v>
       </c>
       <c r="AG54" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH54" t="n">
         <v>25</v>
@@ -10983,32 +10983,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ54" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA54" t="n">
         <v>14</v>
       </c>
       <c r="BB54" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC54" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD54" t="n">
         <v>14</v>
       </c>
       <c r="BE54" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BF54" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG54" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -11039,13 +11039,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G55" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H55" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I55" t="n">
         <v>3</v>
@@ -11063,34 +11063,34 @@
         <v>1.05</v>
       </c>
       <c r="N55" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O55" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P55" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R55" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S55" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U55" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V55" t="n">
         <v>1.5</v>
       </c>
       <c r="W55" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X55" t="n">
         <v>21</v>
@@ -11108,7 +11108,7 @@
         <v>14.5</v>
       </c>
       <c r="AC55" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD55" t="n">
         <v>14.5</v>
@@ -11156,7 +11156,7 @@
         <v>17</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT55" t="n">
         <v>11.5</v>
@@ -11168,7 +11168,7 @@
         <v>10.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX55" t="n">
         <v>15</v>
@@ -11192,7 +11192,7 @@
         <v>6</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF55" t="n">
         <v>12.5</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -11233,76 +11233,76 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="G56" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="H56" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I56" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J56" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L56" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M56" t="n">
         <v>1.04</v>
       </c>
       <c r="N56" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O56" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P56" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R56" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S56" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T56" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U56" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V56" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W56" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="X56" t="n">
         <v>24</v>
       </c>
       <c r="Y56" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z56" t="n">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="AA56" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AB56" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC56" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD56" t="n">
         <v>25</v>
@@ -11314,19 +11314,19 @@
         <v>11</v>
       </c>
       <c r="AG56" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH56" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI56" t="n">
         <v>70</v>
       </c>
       <c r="AJ56" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK56" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL56" t="n">
         <v>27</v>
@@ -11335,7 +11335,7 @@
         <v>85</v>
       </c>
       <c r="AN56" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AO56" t="n">
         <v>70</v>
@@ -11350,31 +11350,31 @@
         <v>29</v>
       </c>
       <c r="AS56" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT56" t="n">
         <v>10.5</v>
       </c>
       <c r="AU56" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV56" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ56" t="n">
         <v>17</v>
       </c>
-      <c r="AW56" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>15</v>
-      </c>
       <c r="BA56" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB56" t="n">
         <v>13.5</v>
@@ -11386,17 +11386,17 @@
         <v>24</v>
       </c>
       <c r="BE56" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BF56" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG56" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
         <v>2.34</v>
       </c>
       <c r="H57" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I57" t="n">
         <v>3.8</v>
@@ -11478,7 +11478,7 @@
         <v>1.35</v>
       </c>
       <c r="W57" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X57" t="n">
         <v>12</v>
@@ -11505,7 +11505,7 @@
         <v>60</v>
       </c>
       <c r="AF57" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG57" t="n">
         <v>12</v>
@@ -11544,7 +11544,7 @@
         <v>20</v>
       </c>
       <c r="AS57" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT57" t="n">
         <v>6.8</v>
@@ -11568,7 +11568,7 @@
         <v>18.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB57" t="n">
         <v>27</v>
@@ -11577,20 +11577,20 @@
         <v>25</v>
       </c>
       <c r="BD57" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE57" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF57" t="n">
         <v>21</v>
       </c>
       <c r="BG57" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -11627,13 +11627,13 @@
         <v>3.3</v>
       </c>
       <c r="H58" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I58" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J58" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K58" t="n">
         <v>3.35</v>
@@ -11645,16 +11645,16 @@
         <v>1.09</v>
       </c>
       <c r="N58" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O58" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P58" t="n">
         <v>1.73</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R58" t="n">
         <v>1.27</v>
@@ -11663,7 +11663,7 @@
         <v>4.3</v>
       </c>
       <c r="T58" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U58" t="n">
         <v>1.96</v>
@@ -11684,7 +11684,7 @@
         <v>16</v>
       </c>
       <c r="AA58" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB58" t="n">
         <v>12.5</v>
@@ -11693,10 +11693,10 @@
         <v>7.4</v>
       </c>
       <c r="AD58" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE58" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF58" t="n">
         <v>21</v>
@@ -11738,7 +11738,7 @@
         <v>13.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT58" t="n">
         <v>9.4</v>
@@ -11750,10 +11750,10 @@
         <v>10.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX58" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY58" t="n">
         <v>11.5</v>
@@ -11765,7 +11765,7 @@
         <v>40</v>
       </c>
       <c r="BB58" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC58" t="n">
         <v>34</v>
@@ -11774,17 +11774,17 @@
         <v>46</v>
       </c>
       <c r="BE58" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF58" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG58" t="n">
         <v>22</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -11836,25 +11836,25 @@
         <v>1.01</v>
       </c>
       <c r="M59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N59" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="O59" t="n">
         <v>1.23</v>
       </c>
       <c r="P59" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="Q59" t="n">
         <v>1.22</v>
       </c>
       <c r="R59" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S59" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T59" t="n">
         <v>1.76</v>
@@ -11863,10 +11863,10 @@
         <v>1.11</v>
       </c>
       <c r="V59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="J2" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,25 +787,25 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.74</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.56</v>
+        <v>2.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1.08</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>1.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -817,10 +817,10 @@
         <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.34</v>
+        <v>1.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.4</v>
+        <v>610</v>
       </c>
       <c r="AB2" t="n">
         <v>1000</v>
@@ -829,10 +829,10 @@
         <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
@@ -841,7 +841,7 @@
         <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -853,7 +853,7 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -862,7 +862,7 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>1000</v>
@@ -871,10 +871,10 @@
         <v>32</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>1.19</v>
       </c>
       <c r="AT2" t="n">
         <v>1000</v>
@@ -883,44 +883,44 @@
         <v>32</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>14.5</v>
+        <v>1.24</v>
       </c>
       <c r="AX2" t="n">
         <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>1.24</v>
       </c>
       <c r="BA2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD2" t="n">
         <v>46</v>
       </c>
-      <c r="BB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>65</v>
-      </c>
       <c r="BE2" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="BF2" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="BG2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="I3" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>1.56</v>
@@ -975,43 +975,43 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
         <v>42</v>
@@ -1026,22 +1026,22 @@
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
         <v>44</v>
@@ -1050,40 +1050,40 @@
         <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
         <v>960</v>
       </c>
       <c r="AO3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1095,26 +1095,26 @@
         <v>50</v>
       </c>
       <c r="BB3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC3" t="n">
         <v>40</v>
       </c>
       <c r="BD3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE3" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BF3" t="n">
         <v>48</v>
       </c>
       <c r="BG3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G4" t="n">
         <v>3.25</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="H4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I4" t="n">
         <v>2.58</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
         <v>1.59</v>
@@ -1169,13 +1169,13 @@
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
         <v>2.64</v>
@@ -1184,7 +1184,7 @@
         <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T4" t="n">
         <v>2.1</v>
@@ -1193,25 +1193,25 @@
         <v>1.84</v>
       </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y4" t="n">
         <v>7.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA4" t="n">
         <v>40</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
         <v>7</v>
@@ -1220,10 +1220,10 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
@@ -1232,31 +1232,31 @@
         <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN4" t="n">
-        <v>990</v>
+        <v>75</v>
       </c>
       <c r="AO4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
         <v>13.5</v>
@@ -1265,7 +1265,7 @@
         <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
         <v>6.8</v>
@@ -1280,16 +1280,16 @@
         <v>19</v>
       </c>
       <c r="AY4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
         <v>23</v>
       </c>
       <c r="BA4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB4" t="n">
         <v>60</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>55</v>
       </c>
       <c r="BC4" t="n">
         <v>44</v>
@@ -1298,17 +1298,17 @@
         <v>65</v>
       </c>
       <c r="BE4" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BF4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BG4" t="n">
         <v>34</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>970</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
         <v>34</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>6.8</v>
@@ -1369,16 +1369,16 @@
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
         <v>1.63</v>
@@ -1390,7 +1390,7 @@
         <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
         <v>3.6</v>
@@ -1557,19 +1557,19 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
         <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
         <v>3.25</v>
@@ -1581,122 +1581,122 @@
         <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
         <v>18.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>95</v>
       </c>
       <c r="AN6" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
         <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>1.81</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
         <v>5.7</v>
@@ -1757,7 +1757,7 @@
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
         <v>1.81</v>
@@ -1835,10 +1835,10 @@
         <v>75</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AR7" t="n">
         <v>1.83</v>
@@ -1850,7 +1850,7 @@
         <v>3.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AV7" t="n">
         <v>4.6</v>
@@ -1862,10 +1862,10 @@
         <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BA7" t="n">
         <v>1.87</v>
@@ -1883,14 +1883,14 @@
         <v>1.88</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG7" t="n">
         <v>1.59</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -1921,37 +1921,37 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O8" t="n">
         <v>1.51</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
         <v>2.52</v>
@@ -1969,13 +1969,13 @@
         <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
         <v>11</v>
@@ -1987,19 +1987,19 @@
         <v>75</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
         <v>7.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -2008,7 +2008,7 @@
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="n">
         <v>36</v>
@@ -2020,10 +2020,10 @@
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO8" t="n">
         <v>70</v>
@@ -2032,25 +2032,25 @@
         <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AT8" t="n">
         <v>7.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AX8" t="n">
         <v>12</v>
@@ -2062,7 +2062,7 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB8" t="n">
         <v>30</v>
@@ -2074,17 +2074,17 @@
         <v>44</v>
       </c>
       <c r="BE8" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BF8" t="n">
         <v>28</v>
       </c>
       <c r="BG8" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I9" t="n">
         <v>2.68</v>
@@ -2130,49 +2130,49 @@
         <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
         <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
         <v>1.77</v>
       </c>
       <c r="V9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z9" t="n">
         <v>14.5</v>
@@ -2202,7 +2202,7 @@
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
         <v>70</v>
@@ -2223,7 +2223,7 @@
         <v>44</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>7</v>
@@ -2235,7 +2235,7 @@
         <v>36</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
         <v>6.6</v>
@@ -2247,38 +2247,38 @@
         <v>34</v>
       </c>
       <c r="AX9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY9" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BD9" t="n">
         <v>55</v>
       </c>
       <c r="BE9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BF9" t="n">
         <v>50</v>
       </c>
       <c r="BG9" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G10" t="n">
         <v>2.66</v>
@@ -2351,10 +2351,10 @@
         <v>2.96</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
         <v>1.53</v>
@@ -2444,7 +2444,7 @@
         <v>16.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="H11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I11" t="n">
         <v>6.8</v>
       </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
       <c r="J11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.29</v>
@@ -2533,7 +2533,7 @@
         <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q11" t="n">
         <v>1.54</v>
@@ -2545,16 +2545,16 @@
         <v>2.36</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
         <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X11" t="n">
         <v>36</v>
@@ -2563,7 +2563,7 @@
         <v>29</v>
       </c>
       <c r="Z11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA11" t="n">
         <v>200</v>
@@ -2575,7 +2575,7 @@
         <v>12.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
         <v>85</v>
@@ -2587,13 +2587,13 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK11" t="n">
         <v>14</v>
@@ -2605,19 +2605,19 @@
         <v>980</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ11" t="n">
         <v>24</v>
       </c>
       <c r="AR11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS11" t="n">
         <v>46</v>
@@ -2629,19 +2629,19 @@
         <v>11.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW11" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
         <v>55</v>
@@ -2656,17 +2656,17 @@
         <v>24</v>
       </c>
       <c r="BE11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG11" t="n">
         <v>55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G12" t="n">
         <v>3.2</v>
       </c>
-      <c r="G12" t="n">
-        <v>3.35</v>
-      </c>
       <c r="H12" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J12" t="n">
         <v>3.25</v>
@@ -2745,88 +2745,88 @@
         <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
         <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA12" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AB12" t="n">
         <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AL12" t="n">
         <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AO12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS12" t="n">
         <v>34</v>
       </c>
-      <c r="AP12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>32</v>
-      </c>
       <c r="AT12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AX12" t="n">
         <v>18</v>
@@ -2838,29 +2838,29 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BC12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD12" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF12" t="n">
         <v>36</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
@@ -2915,16 +2915,16 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
         <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R13" t="n">
         <v>1.23</v>
@@ -2936,13 +2936,13 @@
         <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X13" t="n">
         <v>9.6</v>
@@ -2969,7 +2969,7 @@
         <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
         <v>11.5</v>
@@ -2993,7 +2993,7 @@
         <v>160</v>
       </c>
       <c r="AN13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO13" t="n">
         <v>80</v>
@@ -3017,10 +3017,10 @@
         <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3032,7 +3032,7 @@
         <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -3044,17 +3044,17 @@
         <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BF13" t="n">
         <v>22</v>
       </c>
       <c r="BG13" t="n">
-        <v>60</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
         <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
@@ -3118,61 +3118,61 @@
         <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R14" t="n">
         <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U14" t="n">
         <v>1.89</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X14" t="n">
         <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC14" t="n">
         <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
         <v>85</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="n">
         <v>25</v>
@@ -3187,22 +3187,22 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>110</v>
       </c>
       <c r="AP14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AR14" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AT14" t="n">
         <v>6.6</v>
@@ -3214,41 +3214,41 @@
         <v>4.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY14" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB14" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB14" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC14" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 18:35:36</t>
+          <t>2026-05-06 19:03:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH11"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,75 +743,75 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Charlotte Independence</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Boise Cutthroats FC</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.32</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>670</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
+        <v>70</v>
       </c>
       <c r="I2" t="n">
-        <v>670</v>
+        <v>900</v>
       </c>
       <c r="J2" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.04</v>
       </c>
-      <c r="N2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.23</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.74</v>
+        <v>15.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>1.04</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -865,69 +865,69 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,114 +937,114 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fort Wayne FC</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portland Hearts of Pine</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.95</v>
+        <v>860</v>
       </c>
       <c r="H3" t="n">
-        <v>2.84</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3</v>
+        <v>860</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.78</v>
+        <v>1.09</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1059,69 +1059,69 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>400</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>El Paso Locomotive FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="G4" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1169,34 +1169,34 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.73</v>
+        <v>2.66</v>
       </c>
       <c r="S4" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1211,111 +1211,111 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>2.96</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>5.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>13.5</v>
+        <v>420</v>
       </c>
       <c r="AL4" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="AO4" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AP4" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>7.2</v>
+        <v>2.66</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
         <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>CONCACAF Champions League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.46</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
         <v>3.6</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="O5" t="n">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="X5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="Y5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC5" t="n">
         <v>11</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AD5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>420</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>260</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>300</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>65</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>320</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>150</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF5" t="n">
         <v>22</v>
       </c>
-      <c r="AA5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>30</v>
-      </c>
       <c r="BG5" t="n">
-        <v>60</v>
+        <v>12.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1519,135 +1519,135 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I6" t="n">
         <v>2.64</v>
       </c>
-      <c r="I6" t="n">
-        <v>2.66</v>
-      </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="K6" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="P6" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="S6" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="U6" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AH6" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AM6" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
         <v>44</v>
@@ -1656,54 +1656,54 @@
         <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AX6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AZ6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BA6" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BB6" t="n">
+        <v>85</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>130</v>
+      </c>
+      <c r="BE6" t="n">
         <v>65</v>
       </c>
-      <c r="BC6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>85</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>42</v>
-      </c>
       <c r="BF6" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="BG6" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Paso Locomotive FC</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="H7" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>2.98</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.96</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.26</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>1.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="S7" t="n">
-        <v>2.88</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.63</v>
+        <v>2.58</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
         <v>21</v>
       </c>
-      <c r="AA7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AW7" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AX7" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="BA7" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="BB7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC7" t="n">
         <v>30</v>
       </c>
-      <c r="BC7" t="n">
-        <v>22</v>
-      </c>
       <c r="BD7" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BE7" t="n">
-        <v>14.5</v>
+        <v>240</v>
       </c>
       <c r="BF7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="BG7" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CONCACAF Champions League</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,766 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>23:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>CD Marathon</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.6</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="Q8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS8" t="n">
         <v>5.1</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="AT8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC8" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
+      <c r="BD8" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF8" t="n">
         <v>16</v>
       </c>
-      <c r="AK8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>980</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>6</v>
-      </c>
       <c r="BG8" t="n">
-        <v>46</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Univ Catolica (Chile)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Cruzeiro MG</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-05-06 21:20:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Nacional (Uru)</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="X10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2026-05-06 21:20:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>23:15:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CD Olimpia</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CD Marathon</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="X11" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
